--- a/research/traditional_assets/database/data/estonia/estonia_electrical_equipment.xlsx
+++ b/research/traditional_assets/database/data/estonia/estonia_electrical_equipment.xlsx
@@ -8,6 +8,8 @@
   </bookViews>
   <sheets>
     <sheet name="earnings_debt" sheetId="1" r:id="rId1"/>
+    <sheet name="cost_capital" sheetId="2" r:id="rId2"/>
+    <sheet name="tlse_hae1t" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -588,43 +590,46 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.133</v>
+        <v>0.121</v>
+      </c>
+      <c r="E2">
+        <v>0.0296</v>
       </c>
       <c r="G2">
-        <v>0.05495169082125604</v>
+        <v>0.007631578947368421</v>
       </c>
       <c r="H2">
-        <v>0.04263285024154589</v>
+        <v>-0.004029038112522686</v>
       </c>
       <c r="I2">
-        <v>-0.007246376811594203</v>
+        <v>0.02722323049001815</v>
       </c>
       <c r="J2">
-        <v>-0.007246376811594203</v>
+        <v>0.02315262757132143</v>
       </c>
       <c r="K2">
-        <v>-2.09</v>
+        <v>2.65</v>
       </c>
       <c r="L2">
-        <v>-0.0126207729468599</v>
+        <v>0.01202359346642468</v>
       </c>
       <c r="M2">
-        <v>2.47</v>
+        <v>0.967</v>
       </c>
       <c r="N2">
-        <v>0.02522982635342186</v>
+        <v>0.009517716535433072</v>
       </c>
       <c r="O2">
-        <v>-1.181818181818182</v>
+        <v>0.3649056603773585</v>
       </c>
       <c r="P2">
-        <v>2.47</v>
+        <v>0.967</v>
       </c>
       <c r="Q2">
-        <v>0.02522982635342186</v>
+        <v>0.009517716535433072</v>
       </c>
       <c r="R2">
-        <v>-1.181818181818182</v>
+        <v>0.3649056603773585</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -633,73 +638,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>0.494</v>
+        <v>0.631</v>
       </c>
       <c r="V2">
-        <v>0.005045965270684371</v>
+        <v>0.006210629921259843</v>
       </c>
       <c r="W2">
-        <v>-0.02193074501573977</v>
+        <v>0.03291925465838509</v>
       </c>
       <c r="X2">
-        <v>0.1395886466277241</v>
+        <v>0.1233013844573242</v>
       </c>
       <c r="Y2">
-        <v>-0.1615193916434639</v>
+        <v>-0.0903821297989391</v>
       </c>
       <c r="Z2">
-        <v>1.346998535871157</v>
+        <v>1.929846067632173</v>
       </c>
       <c r="AA2">
-        <v>-0.009760858955588092</v>
+        <v>0.0446810072738669</v>
       </c>
       <c r="AB2">
-        <v>0.1166283318190353</v>
+        <v>0.09798201593452706</v>
       </c>
       <c r="AC2">
-        <v>-0.1263891907746234</v>
+        <v>-0.05330100866066016</v>
       </c>
       <c r="AD2">
-        <v>34.2</v>
+        <v>46.1</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>34.2</v>
+        <v>46.1</v>
       </c>
       <c r="AG2">
-        <v>33.706</v>
+        <v>45.469</v>
       </c>
       <c r="AH2">
-        <v>0.25889477668433</v>
+        <v>0.3121191604603927</v>
       </c>
       <c r="AI2">
-        <v>0.2986899563318778</v>
+        <v>0.3179310344827586</v>
       </c>
       <c r="AJ2">
-        <v>0.2561129431788824</v>
+        <v>0.3091678055878533</v>
       </c>
       <c r="AK2">
-        <v>0.2956511060821361</v>
+        <v>0.3149498853632012</v>
       </c>
       <c r="AL2">
-        <v>0.163</v>
+        <v>1.69</v>
       </c>
       <c r="AM2">
-        <v>0.034</v>
+        <v>1.564</v>
       </c>
       <c r="AN2">
-        <v>16.76470588235294</v>
+        <v>4.873150105708245</v>
       </c>
       <c r="AO2">
-        <v>-7.361963190184048</v>
+        <v>3.550295857988166</v>
       </c>
       <c r="AP2">
-        <v>16.52254901960784</v>
+        <v>4.806448202959831</v>
       </c>
       <c r="AQ2">
-        <v>-35.29411764705882</v>
+        <v>3.836317135549872</v>
       </c>
     </row>
     <row r="3">
@@ -719,43 +724,46 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.133</v>
+        <v>0.121</v>
+      </c>
+      <c r="E3">
+        <v>0.0296</v>
       </c>
       <c r="G3">
-        <v>0.05495169082125604</v>
+        <v>0.007631578947368421</v>
       </c>
       <c r="H3">
-        <v>0.04263285024154589</v>
+        <v>-0.004029038112522686</v>
       </c>
       <c r="I3">
-        <v>-0.007246376811594203</v>
+        <v>0.02722323049001815</v>
       </c>
       <c r="J3">
-        <v>-0.007246376811594203</v>
+        <v>0.02315262757132143</v>
       </c>
       <c r="K3">
-        <v>-2.09</v>
+        <v>2.65</v>
       </c>
       <c r="L3">
-        <v>-0.0126207729468599</v>
+        <v>0.01202359346642468</v>
       </c>
       <c r="M3">
-        <v>2.47</v>
+        <v>0.967</v>
       </c>
       <c r="N3">
-        <v>0.02522982635342186</v>
+        <v>0.009517716535433072</v>
       </c>
       <c r="O3">
-        <v>-1.181818181818182</v>
+        <v>0.3649056603773585</v>
       </c>
       <c r="P3">
-        <v>2.47</v>
+        <v>0.967</v>
       </c>
       <c r="Q3">
-        <v>0.02522982635342186</v>
+        <v>0.009517716535433072</v>
       </c>
       <c r="R3">
-        <v>-1.181818181818182</v>
+        <v>0.3649056603773585</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -764,73 +772,8845 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>0.494</v>
+        <v>0.631</v>
       </c>
       <c r="V3">
-        <v>0.005045965270684371</v>
+        <v>0.006210629921259843</v>
       </c>
       <c r="W3">
-        <v>-0.02193074501573977</v>
+        <v>0.03291925465838509</v>
       </c>
       <c r="X3">
-        <v>0.1395886466277241</v>
+        <v>0.1233013844573242</v>
       </c>
       <c r="Y3">
-        <v>-0.1615193916434639</v>
+        <v>-0.0903821297989391</v>
       </c>
       <c r="Z3">
-        <v>1.346998535871157</v>
+        <v>1.929846067632173</v>
       </c>
       <c r="AA3">
-        <v>-0.009760858955588092</v>
+        <v>0.0446810072738669</v>
       </c>
       <c r="AB3">
-        <v>0.1166283318190353</v>
+        <v>0.09798201593452706</v>
       </c>
       <c r="AC3">
-        <v>-0.1263891907746234</v>
+        <v>-0.05330100866066016</v>
       </c>
       <c r="AD3">
-        <v>34.2</v>
+        <v>46.1</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>34.2</v>
+        <v>46.1</v>
       </c>
       <c r="AG3">
-        <v>33.706</v>
+        <v>45.469</v>
       </c>
       <c r="AH3">
-        <v>0.25889477668433</v>
+        <v>0.3121191604603927</v>
       </c>
       <c r="AI3">
-        <v>0.2986899563318778</v>
+        <v>0.3179310344827586</v>
       </c>
       <c r="AJ3">
-        <v>0.2561129431788824</v>
+        <v>0.3091678055878533</v>
       </c>
       <c r="AK3">
-        <v>0.2956511060821361</v>
+        <v>0.3149498853632012</v>
       </c>
       <c r="AL3">
-        <v>0.163</v>
+        <v>1.69</v>
       </c>
       <c r="AM3">
-        <v>0.034</v>
+        <v>1.564</v>
       </c>
       <c r="AN3">
-        <v>16.76470588235294</v>
+        <v>4.873150105708245</v>
       </c>
       <c r="AO3">
-        <v>-7.361963190184048</v>
+        <v>3.550295857988166</v>
       </c>
       <c r="AP3">
-        <v>16.52254901960784</v>
+        <v>4.806448202959831</v>
       </c>
       <c r="AQ3">
-        <v>-35.29411764705882</v>
+        <v>3.836317135549872</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:AY2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>company_name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>exchange_ticker</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>industry_group</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>current_interest_coverage</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_interest_coverage</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>current_debt_ebitda</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_ebitda</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>current_debt_capital</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_capital</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>current_equity_value</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_equity_value</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>current_enterprise_value</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_enterprise_value</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>current_debt</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>current_cost_capital</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_capital</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>current_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>current_debt_rating</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_rating</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>current_cost_equity</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_equity</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>current_beta</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_beta</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_mv_debt</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_coverage_ratio</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_debt</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_interest_expense</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_depreciation</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_ebitda</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>country_default_spread</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>risk_free</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>market_capitalization</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_risk_premium</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>reported_debt_rating</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>marginal_tax_rate</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_max_percentage</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_method</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_drop_ebitda</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>reported_capital_spending</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>reported_interest_expense</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>reported_bv_debt</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>reported_cash</t>
+        </is>
+      </c>
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_ev_implied_growth</t>
+        </is>
+      </c>
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>flag_bankruptcy</t>
+        </is>
+      </c>
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>flag_refinanced</t>
+        </is>
+      </c>
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
+          <t>rating_firm_type</t>
+        </is>
+      </c>
+      <c r="AY1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio_limit</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>AS Harju Elekter (TLSE:HAE1T)</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>TLSE:HAE1T</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Electrical Equipment</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Estonia</t>
+        </is>
+      </c>
+      <c r="E2">
+        <v>3.55029585798817</v>
+      </c>
+      <c r="F2">
+        <v>4.63613875982706</v>
+      </c>
+      <c r="G2">
+        <v>4.87315010570824</v>
+      </c>
+      <c r="H2">
+        <v>3.74714587737843</v>
+      </c>
+      <c r="I2">
+        <v>0.312119160460393</v>
+      </c>
+      <c r="J2">
+        <v>0.24</v>
+      </c>
+      <c r="K2">
+        <v>101.6</v>
+      </c>
+      <c r="L2">
+        <v>111.510494336863</v>
+      </c>
+      <c r="M2">
+        <v>147.069</v>
+      </c>
+      <c r="N2">
+        <v>146.327494336863</v>
+      </c>
+      <c r="O2">
+        <v>46.1</v>
+      </c>
+      <c r="P2">
+        <v>35.448</v>
+      </c>
+      <c r="Q2">
+        <v>0.0979820159345271</v>
+      </c>
+      <c r="R2">
+        <v>0.0982819171948488</v>
+      </c>
+      <c r="S2">
+        <v>0.0421805443094471</v>
+      </c>
+      <c r="T2">
+        <v>0.04072</v>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="W2">
+        <v>0.123301384457324</v>
+      </c>
+      <c r="X2">
+        <v>0.116459364730064</v>
+      </c>
+      <c r="Y2">
+        <v>1.50055196376091</v>
+      </c>
+      <c r="Z2">
+        <v>1.37905329005556</v>
+      </c>
+      <c r="AA2">
+        <v>46.1</v>
+      </c>
+      <c r="AB2">
+        <v>0.05272568038680883</v>
+      </c>
+      <c r="AC2">
+        <v>3.550295857988166</v>
+      </c>
+      <c r="AD2">
+        <v>46.1</v>
+      </c>
+      <c r="AE2">
+        <v>1.69</v>
+      </c>
+      <c r="AF2">
+        <v>3.460000000000001</v>
+      </c>
+      <c r="AG2">
+        <v>9.460000000000001</v>
+      </c>
+      <c r="AH2">
+        <v>0</v>
+      </c>
+      <c r="AI2">
+        <v>0.0388</v>
+      </c>
+      <c r="AJ2">
+        <v>101.6</v>
+      </c>
+      <c r="AK2">
+        <v>0.05631353428476683</v>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="AM2">
+        <v>0.2</v>
+      </c>
+      <c r="AN2">
+        <v>0</v>
+      </c>
+      <c r="AO2">
+        <v>2</v>
+      </c>
+      <c r="AQ2">
+        <v>16.36</v>
+      </c>
+      <c r="AR2">
+        <v>1.69</v>
+      </c>
+      <c r="AS2">
+        <v>46.1</v>
+      </c>
+      <c r="AT2">
+        <v>0.631</v>
+      </c>
+      <c r="AV2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AW2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AX2">
+        <v>1</v>
+      </c>
+      <c r="AY2">
+        <v>10000000</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:Z101"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>debt_capital</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>cost_capital</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>equity_value</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>enterprise_value</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>debt_issued</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>debt</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>marketcap</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>drop_ebitda</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ebitda</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>depreciation</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>ebit</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>interest_expense</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>taxable_income</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>taxes</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>net_income</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>operating_cash_flow</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>debt_equity</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>cost_equity</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>beta</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>tax_rate</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>debt_rating</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_error</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2">
+        <v>0.1007969718433285</v>
+      </c>
+      <c r="C2">
+        <v>141.0223714281123</v>
+      </c>
+      <c r="D2">
+        <v>140.3913714281123</v>
+      </c>
+      <c r="E2">
+        <v>-46.1</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>0.631</v>
+      </c>
+      <c r="H2">
+        <v>101.6</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>11.825</v>
+      </c>
+      <c r="K2">
+        <v>3.460000000000001</v>
+      </c>
+      <c r="L2">
+        <v>8.365</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>8.365</v>
+      </c>
+      <c r="O2">
+        <v>1.673</v>
+      </c>
+      <c r="P2">
+        <v>6.692</v>
+      </c>
+      <c r="Q2">
+        <v>10.152</v>
+      </c>
+      <c r="R2">
+        <v>0</v>
+      </c>
+      <c r="S2">
+        <v>0.1007969718433285</v>
+      </c>
+      <c r="T2">
+        <v>1.100924895422504</v>
+      </c>
+      <c r="U2">
+        <v>0.0447</v>
+      </c>
+      <c r="V2">
+        <v>0.2</v>
+      </c>
+      <c r="W2">
+        <v>0.03576000000000001</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y2">
+        <v>10000000</v>
+      </c>
+      <c r="Z2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3">
+        <v>0.01</v>
+      </c>
+      <c r="B3">
+        <v>0.1006425778996419</v>
+      </c>
+      <c r="C3">
+        <v>139.8958674493089</v>
+      </c>
+      <c r="D3">
+        <v>140.7418674493089</v>
+      </c>
+      <c r="E3">
+        <v>-44.623</v>
+      </c>
+      <c r="F3">
+        <v>1.477</v>
+      </c>
+      <c r="G3">
+        <v>0.631</v>
+      </c>
+      <c r="H3">
+        <v>101.6</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>11.825</v>
+      </c>
+      <c r="K3">
+        <v>3.460000000000001</v>
+      </c>
+      <c r="L3">
+        <v>8.365</v>
+      </c>
+      <c r="M3">
+        <v>0.06602189999999999</v>
+      </c>
+      <c r="N3">
+        <v>8.298978099999999</v>
+      </c>
+      <c r="O3">
+        <v>1.65979562</v>
+      </c>
+      <c r="P3">
+        <v>6.63918248</v>
+      </c>
+      <c r="Q3">
+        <v>10.09918248</v>
+      </c>
+      <c r="R3">
+        <v>0.0101010101010101</v>
+      </c>
+      <c r="S3">
+        <v>0.1012979574743857</v>
+      </c>
+      <c r="T3">
+        <v>1.109821258213797</v>
+      </c>
+      <c r="U3">
+        <v>0.0447</v>
+      </c>
+      <c r="V3">
+        <v>0.2</v>
+      </c>
+      <c r="W3">
+        <v>0.03576000000000001</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y3">
+        <v>126.7003827517839</v>
+      </c>
+      <c r="Z3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4">
+        <v>0.02</v>
+      </c>
+      <c r="B4">
+        <v>0.1004881839559552</v>
+      </c>
+      <c r="C4">
+        <v>138.77111792199</v>
+      </c>
+      <c r="D4">
+        <v>141.09411792199</v>
+      </c>
+      <c r="E4">
+        <v>-43.146</v>
+      </c>
+      <c r="F4">
+        <v>2.954</v>
+      </c>
+      <c r="G4">
+        <v>0.631</v>
+      </c>
+      <c r="H4">
+        <v>101.6</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>11.825</v>
+      </c>
+      <c r="K4">
+        <v>3.460000000000001</v>
+      </c>
+      <c r="L4">
+        <v>8.365</v>
+      </c>
+      <c r="M4">
+        <v>0.1320438</v>
+      </c>
+      <c r="N4">
+        <v>8.2329562</v>
+      </c>
+      <c r="O4">
+        <v>1.64659124</v>
+      </c>
+      <c r="P4">
+        <v>6.58636496</v>
+      </c>
+      <c r="Q4">
+        <v>10.04636496</v>
+      </c>
+      <c r="R4">
+        <v>0.02040816326530612</v>
+      </c>
+      <c r="S4">
+        <v>0.1018091673019951</v>
+      </c>
+      <c r="T4">
+        <v>1.118899179429402</v>
+      </c>
+      <c r="U4">
+        <v>0.0447</v>
+      </c>
+      <c r="V4">
+        <v>0.2</v>
+      </c>
+      <c r="W4">
+        <v>0.03576000000000001</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y4">
+        <v>63.35019137589195</v>
+      </c>
+      <c r="Z4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5">
+        <v>0.03</v>
+      </c>
+      <c r="B5">
+        <v>0.1003337900122686</v>
+      </c>
+      <c r="C5">
+        <v>137.6481360523965</v>
+      </c>
+      <c r="D5">
+        <v>141.4481360523965</v>
+      </c>
+      <c r="E5">
+        <v>-41.669</v>
+      </c>
+      <c r="F5">
+        <v>4.430999999999999</v>
+      </c>
+      <c r="G5">
+        <v>0.631</v>
+      </c>
+      <c r="H5">
+        <v>101.6</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>11.825</v>
+      </c>
+      <c r="K5">
+        <v>3.460000000000001</v>
+      </c>
+      <c r="L5">
+        <v>8.365</v>
+      </c>
+      <c r="M5">
+        <v>0.1980657</v>
+      </c>
+      <c r="N5">
+        <v>8.166934299999999</v>
+      </c>
+      <c r="O5">
+        <v>1.63338686</v>
+      </c>
+      <c r="P5">
+        <v>6.53354744</v>
+      </c>
+      <c r="Q5">
+        <v>9.99354744</v>
+      </c>
+      <c r="R5">
+        <v>0.03092783505154639</v>
+      </c>
+      <c r="S5">
+        <v>0.1023309175384212</v>
+      </c>
+      <c r="T5">
+        <v>1.128164274278319</v>
+      </c>
+      <c r="U5">
+        <v>0.0447</v>
+      </c>
+      <c r="V5">
+        <v>0.2</v>
+      </c>
+      <c r="W5">
+        <v>0.03576000000000001</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y5">
+        <v>42.23346091726129</v>
+      </c>
+      <c r="Z5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6">
+        <v>0.04</v>
+      </c>
+      <c r="B6">
+        <v>0.1001793960685819</v>
+      </c>
+      <c r="C6">
+        <v>136.5269351796452</v>
+      </c>
+      <c r="D6">
+        <v>141.8039351796452</v>
+      </c>
+      <c r="E6">
+        <v>-40.192</v>
+      </c>
+      <c r="F6">
+        <v>5.907999999999999</v>
+      </c>
+      <c r="G6">
+        <v>0.631</v>
+      </c>
+      <c r="H6">
+        <v>101.6</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>11.825</v>
+      </c>
+      <c r="K6">
+        <v>3.460000000000001</v>
+      </c>
+      <c r="L6">
+        <v>8.365</v>
+      </c>
+      <c r="M6">
+        <v>0.2640876</v>
+      </c>
+      <c r="N6">
+        <v>8.1009124</v>
+      </c>
+      <c r="O6">
+        <v>1.62018248</v>
+      </c>
+      <c r="P6">
+        <v>6.48072992</v>
+      </c>
+      <c r="Q6">
+        <v>9.940729920000001</v>
+      </c>
+      <c r="R6">
+        <v>0.04166666666666667</v>
+      </c>
+      <c r="S6">
+        <v>0.1028635375714395</v>
+      </c>
+      <c r="T6">
+        <v>1.137622391936588</v>
+      </c>
+      <c r="U6">
+        <v>0.0447</v>
+      </c>
+      <c r="V6">
+        <v>0.2</v>
+      </c>
+      <c r="W6">
+        <v>0.03576000000000001</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y6">
+        <v>31.67509568794597</v>
+      </c>
+      <c r="Z6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7">
+        <v>0.05</v>
+      </c>
+      <c r="B7">
+        <v>0.1000250021248952</v>
+      </c>
+      <c r="C7">
+        <v>135.4075287774047</v>
+      </c>
+      <c r="D7">
+        <v>142.1615287774047</v>
+      </c>
+      <c r="E7">
+        <v>-38.715</v>
+      </c>
+      <c r="F7">
+        <v>7.385</v>
+      </c>
+      <c r="G7">
+        <v>0.631</v>
+      </c>
+      <c r="H7">
+        <v>101.6</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>11.825</v>
+      </c>
+      <c r="K7">
+        <v>3.460000000000001</v>
+      </c>
+      <c r="L7">
+        <v>8.365</v>
+      </c>
+      <c r="M7">
+        <v>0.3301095</v>
+      </c>
+      <c r="N7">
+        <v>8.034890499999999</v>
+      </c>
+      <c r="O7">
+        <v>1.6069781</v>
+      </c>
+      <c r="P7">
+        <v>6.427912399999999</v>
+      </c>
+      <c r="Q7">
+        <v>9.887912400000001</v>
+      </c>
+      <c r="R7">
+        <v>0.05263157894736843</v>
+      </c>
+      <c r="S7">
+        <v>0.1034073706577845</v>
+      </c>
+      <c r="T7">
+        <v>1.147279627861347</v>
+      </c>
+      <c r="U7">
+        <v>0.0447</v>
+      </c>
+      <c r="V7">
+        <v>0.2</v>
+      </c>
+      <c r="W7">
+        <v>0.03576000000000001</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y7">
+        <v>25.34007655035677</v>
+      </c>
+      <c r="Z7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8">
+        <v>0.06</v>
+      </c>
+      <c r="B8">
+        <v>0.0998706081812086</v>
+      </c>
+      <c r="C8">
+        <v>134.2899304555956</v>
+      </c>
+      <c r="D8">
+        <v>142.5209304555956</v>
+      </c>
+      <c r="E8">
+        <v>-37.238</v>
+      </c>
+      <c r="F8">
+        <v>8.861999999999998</v>
+      </c>
+      <c r="G8">
+        <v>0.631</v>
+      </c>
+      <c r="H8">
+        <v>101.6</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>11.825</v>
+      </c>
+      <c r="K8">
+        <v>3.460000000000001</v>
+      </c>
+      <c r="L8">
+        <v>8.365</v>
+      </c>
+      <c r="M8">
+        <v>0.3961314</v>
+      </c>
+      <c r="N8">
+        <v>7.9688686</v>
+      </c>
+      <c r="O8">
+        <v>1.59377372</v>
+      </c>
+      <c r="P8">
+        <v>6.375094880000001</v>
+      </c>
+      <c r="Q8">
+        <v>9.835094880000002</v>
+      </c>
+      <c r="R8">
+        <v>0.06382978723404255</v>
+      </c>
+      <c r="S8">
+        <v>0.1039627746608602</v>
+      </c>
+      <c r="T8">
+        <v>1.157142336890888</v>
+      </c>
+      <c r="U8">
+        <v>0.0447</v>
+      </c>
+      <c r="V8">
+        <v>0.2</v>
+      </c>
+      <c r="W8">
+        <v>0.03576000000000001</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y8">
+        <v>21.11673045863065</v>
+      </c>
+      <c r="Z8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="B9">
+        <v>0.09971621423752194</v>
+      </c>
+      <c r="C9">
+        <v>133.1741539621177</v>
+      </c>
+      <c r="D9">
+        <v>142.8821539621177</v>
+      </c>
+      <c r="E9">
+        <v>-35.761</v>
+      </c>
+      <c r="F9">
+        <v>10.339</v>
+      </c>
+      <c r="G9">
+        <v>0.631</v>
+      </c>
+      <c r="H9">
+        <v>101.6</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>11.825</v>
+      </c>
+      <c r="K9">
+        <v>3.460000000000001</v>
+      </c>
+      <c r="L9">
+        <v>8.365</v>
+      </c>
+      <c r="M9">
+        <v>0.4621533</v>
+      </c>
+      <c r="N9">
+        <v>7.9028467</v>
+      </c>
+      <c r="O9">
+        <v>1.58056934</v>
+      </c>
+      <c r="P9">
+        <v>6.32227736</v>
+      </c>
+      <c r="Q9">
+        <v>9.782277360000002</v>
+      </c>
+      <c r="R9">
+        <v>0.07526881720430109</v>
+      </c>
+      <c r="S9">
+        <v>0.1045301228360451</v>
+      </c>
+      <c r="T9">
+        <v>1.167217147189881</v>
+      </c>
+      <c r="U9">
+        <v>0.0447</v>
+      </c>
+      <c r="V9">
+        <v>0.2</v>
+      </c>
+      <c r="W9">
+        <v>0.03576000000000001</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y9">
+        <v>18.10005467882627</v>
+      </c>
+      <c r="Z9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10">
+        <v>0.08</v>
+      </c>
+      <c r="B10">
+        <v>0.0995618202938353</v>
+      </c>
+      <c r="C10">
+        <v>132.0602131846028</v>
+      </c>
+      <c r="D10">
+        <v>143.2452131846028</v>
+      </c>
+      <c r="E10">
+        <v>-34.28400000000001</v>
+      </c>
+      <c r="F10">
+        <v>11.816</v>
+      </c>
+      <c r="G10">
+        <v>0.631</v>
+      </c>
+      <c r="H10">
+        <v>101.6</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>11.825</v>
+      </c>
+      <c r="K10">
+        <v>3.460000000000001</v>
+      </c>
+      <c r="L10">
+        <v>8.365</v>
+      </c>
+      <c r="M10">
+        <v>0.5281752</v>
+      </c>
+      <c r="N10">
+        <v>7.8368248</v>
+      </c>
+      <c r="O10">
+        <v>1.56736496</v>
+      </c>
+      <c r="P10">
+        <v>6.269459840000001</v>
+      </c>
+      <c r="Q10">
+        <v>9.729459840000001</v>
+      </c>
+      <c r="R10">
+        <v>0.08695652173913043</v>
+      </c>
+      <c r="S10">
+        <v>0.1051098046672123</v>
+      </c>
+      <c r="T10">
+        <v>1.17751097510407</v>
+      </c>
+      <c r="U10">
+        <v>0.0447</v>
+      </c>
+      <c r="V10">
+        <v>0.2</v>
+      </c>
+      <c r="W10">
+        <v>0.03576000000000001</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y10">
+        <v>15.83754784397299</v>
+      </c>
+      <c r="Z10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11">
+        <v>0.09</v>
+      </c>
+      <c r="B11">
+        <v>0.09940742635014863</v>
+      </c>
+      <c r="C11">
+        <v>130.9481221521942</v>
+      </c>
+      <c r="D11">
+        <v>143.6101221521942</v>
+      </c>
+      <c r="E11">
+        <v>-32.807</v>
+      </c>
+      <c r="F11">
+        <v>13.293</v>
+      </c>
+      <c r="G11">
+        <v>0.631</v>
+      </c>
+      <c r="H11">
+        <v>101.6</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>11.825</v>
+      </c>
+      <c r="K11">
+        <v>3.460000000000001</v>
+      </c>
+      <c r="L11">
+        <v>8.365</v>
+      </c>
+      <c r="M11">
+        <v>0.5941971</v>
+      </c>
+      <c r="N11">
+        <v>7.770802900000001</v>
+      </c>
+      <c r="O11">
+        <v>1.55416058</v>
+      </c>
+      <c r="P11">
+        <v>6.21664232</v>
+      </c>
+      <c r="Q11">
+        <v>9.676642320000001</v>
+      </c>
+      <c r="R11">
+        <v>0.0989010989010989</v>
+      </c>
+      <c r="S11">
+        <v>0.1057022267584051</v>
+      </c>
+      <c r="T11">
+        <v>1.188031040994395</v>
+      </c>
+      <c r="U11">
+        <v>0.0447</v>
+      </c>
+      <c r="V11">
+        <v>0.2</v>
+      </c>
+      <c r="W11">
+        <v>0.03576000000000001</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y11">
+        <v>14.07782030575376</v>
+      </c>
+      <c r="Z11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12">
+        <v>0.1</v>
+      </c>
+      <c r="B12">
+        <v>0.09934103240646198</v>
+      </c>
+      <c r="C12">
+        <v>129.6286160366557</v>
+      </c>
+      <c r="D12">
+        <v>143.7676160366557</v>
+      </c>
+      <c r="E12">
+        <v>-31.33</v>
+      </c>
+      <c r="F12">
+        <v>14.77</v>
+      </c>
+      <c r="G12">
+        <v>0.631</v>
+      </c>
+      <c r="H12">
+        <v>101.6</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>11.825</v>
+      </c>
+      <c r="K12">
+        <v>3.460000000000001</v>
+      </c>
+      <c r="L12">
+        <v>8.365</v>
+      </c>
+      <c r="M12">
+        <v>0.676466</v>
+      </c>
+      <c r="N12">
+        <v>7.688534000000001</v>
+      </c>
+      <c r="O12">
+        <v>1.5377068</v>
+      </c>
+      <c r="P12">
+        <v>6.1508272</v>
+      </c>
+      <c r="Q12">
+        <v>9.610827200000001</v>
+      </c>
+      <c r="R12">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="S12">
+        <v>0.1063078137849578</v>
+      </c>
+      <c r="T12">
+        <v>1.198784886126727</v>
+      </c>
+      <c r="U12">
+        <v>0.0458</v>
+      </c>
+      <c r="V12">
+        <v>0.2</v>
+      </c>
+      <c r="W12">
+        <v>0.03664</v>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y12">
+        <v>12.36573604586188</v>
+      </c>
+      <c r="Z12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13">
+        <v>0.11</v>
+      </c>
+      <c r="B13">
+        <v>0.09919543846277531</v>
+      </c>
+      <c r="C13">
+        <v>128.498193439287</v>
+      </c>
+      <c r="D13">
+        <v>144.114193439287</v>
+      </c>
+      <c r="E13">
+        <v>-29.853</v>
+      </c>
+      <c r="F13">
+        <v>16.247</v>
+      </c>
+      <c r="G13">
+        <v>0.631</v>
+      </c>
+      <c r="H13">
+        <v>101.6</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>11.825</v>
+      </c>
+      <c r="K13">
+        <v>3.460000000000001</v>
+      </c>
+      <c r="L13">
+        <v>8.365</v>
+      </c>
+      <c r="M13">
+        <v>0.7441126</v>
+      </c>
+      <c r="N13">
+        <v>7.6208874</v>
+      </c>
+      <c r="O13">
+        <v>1.52417748</v>
+      </c>
+      <c r="P13">
+        <v>6.09670992</v>
+      </c>
+      <c r="Q13">
+        <v>9.556709920000001</v>
+      </c>
+      <c r="R13">
+        <v>0.1235955056179775</v>
+      </c>
+      <c r="S13">
+        <v>0.1069270095087363</v>
+      </c>
+      <c r="T13">
+        <v>1.209780390700235</v>
+      </c>
+      <c r="U13">
+        <v>0.0458</v>
+      </c>
+      <c r="V13">
+        <v>0.2</v>
+      </c>
+      <c r="W13">
+        <v>0.03664</v>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y13">
+        <v>11.2415782235108</v>
+      </c>
+      <c r="Z13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14">
+        <v>0.12</v>
+      </c>
+      <c r="B14">
+        <v>0.09904984451908866</v>
+      </c>
+      <c r="C14">
+        <v>127.3694458527418</v>
+      </c>
+      <c r="D14">
+        <v>144.4624458527418</v>
+      </c>
+      <c r="E14">
+        <v>-28.376</v>
+      </c>
+      <c r="F14">
+        <v>17.724</v>
+      </c>
+      <c r="G14">
+        <v>0.631</v>
+      </c>
+      <c r="H14">
+        <v>101.6</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>11.825</v>
+      </c>
+      <c r="K14">
+        <v>3.460000000000001</v>
+      </c>
+      <c r="L14">
+        <v>8.365</v>
+      </c>
+      <c r="M14">
+        <v>0.8117591999999999</v>
+      </c>
+      <c r="N14">
+        <v>7.5532408</v>
+      </c>
+      <c r="O14">
+        <v>1.51064816</v>
+      </c>
+      <c r="P14">
+        <v>6.042592640000001</v>
+      </c>
+      <c r="Q14">
+        <v>9.502592640000001</v>
+      </c>
+      <c r="R14">
+        <v>0.1363636363636364</v>
+      </c>
+      <c r="S14">
+        <v>0.1075602778626008</v>
+      </c>
+      <c r="T14">
+        <v>1.22102579310496</v>
+      </c>
+      <c r="U14">
+        <v>0.0458</v>
+      </c>
+      <c r="V14">
+        <v>0.2</v>
+      </c>
+      <c r="W14">
+        <v>0.03664</v>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y14">
+        <v>10.30478003821823</v>
+      </c>
+      <c r="Z14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15">
+        <v>0.13</v>
+      </c>
+      <c r="B15">
+        <v>0.09913305057540199</v>
+      </c>
+      <c r="C15">
+        <v>125.6932159067977</v>
+      </c>
+      <c r="D15">
+        <v>144.2632159067977</v>
+      </c>
+      <c r="E15">
+        <v>-26.899</v>
+      </c>
+      <c r="F15">
+        <v>19.201</v>
+      </c>
+      <c r="G15">
+        <v>0.631</v>
+      </c>
+      <c r="H15">
+        <v>101.6</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>11.825</v>
+      </c>
+      <c r="K15">
+        <v>3.460000000000001</v>
+      </c>
+      <c r="L15">
+        <v>8.365</v>
+      </c>
+      <c r="M15">
+        <v>0.921648</v>
+      </c>
+      <c r="N15">
+        <v>7.443352</v>
+      </c>
+      <c r="O15">
+        <v>1.4886704</v>
+      </c>
+      <c r="P15">
+        <v>5.9546816</v>
+      </c>
+      <c r="Q15">
+        <v>9.414681600000002</v>
+      </c>
+      <c r="R15">
+        <v>0.1494252873563219</v>
+      </c>
+      <c r="S15">
+        <v>0.1082081041096575</v>
+      </c>
+      <c r="T15">
+        <v>1.232529710507493</v>
+      </c>
+      <c r="U15">
+        <v>0.048</v>
+      </c>
+      <c r="V15">
+        <v>0.2</v>
+      </c>
+      <c r="W15">
+        <v>0.0384</v>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y15">
+        <v>9.076133187507596</v>
+      </c>
+      <c r="Z15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16">
+        <v>0.14</v>
+      </c>
+      <c r="B16">
+        <v>0.09900505663171534</v>
+      </c>
+      <c r="C16">
+        <v>124.522914695336</v>
+      </c>
+      <c r="D16">
+        <v>144.569914695336</v>
+      </c>
+      <c r="E16">
+        <v>-25.422</v>
+      </c>
+      <c r="F16">
+        <v>20.678</v>
+      </c>
+      <c r="G16">
+        <v>0.631</v>
+      </c>
+      <c r="H16">
+        <v>101.6</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>11.825</v>
+      </c>
+      <c r="K16">
+        <v>3.460000000000001</v>
+      </c>
+      <c r="L16">
+        <v>8.365</v>
+      </c>
+      <c r="M16">
+        <v>0.9925440000000001</v>
+      </c>
+      <c r="N16">
+        <v>7.372456</v>
+      </c>
+      <c r="O16">
+        <v>1.4744912</v>
+      </c>
+      <c r="P16">
+        <v>5.8979648</v>
+      </c>
+      <c r="Q16">
+        <v>9.357964800000001</v>
+      </c>
+      <c r="R16">
+        <v>0.1627906976744186</v>
+      </c>
+      <c r="S16">
+        <v>0.1088709960833899</v>
+      </c>
+      <c r="T16">
+        <v>1.244301160872877</v>
+      </c>
+      <c r="U16">
+        <v>0.048</v>
+      </c>
+      <c r="V16">
+        <v>0.2</v>
+      </c>
+      <c r="W16">
+        <v>0.0384</v>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y16">
+        <v>8.42783795982848</v>
+      </c>
+      <c r="Z16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17">
+        <v>0.15</v>
+      </c>
+      <c r="B17">
+        <v>0.09887706268802869</v>
+      </c>
+      <c r="C17">
+        <v>123.3539203249785</v>
+      </c>
+      <c r="D17">
+        <v>144.8779203249785</v>
+      </c>
+      <c r="E17">
+        <v>-23.945</v>
+      </c>
+      <c r="F17">
+        <v>22.155</v>
+      </c>
+      <c r="G17">
+        <v>0.631</v>
+      </c>
+      <c r="H17">
+        <v>101.6</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>11.825</v>
+      </c>
+      <c r="K17">
+        <v>3.460000000000001</v>
+      </c>
+      <c r="L17">
+        <v>8.365</v>
+      </c>
+      <c r="M17">
+        <v>1.06344</v>
+      </c>
+      <c r="N17">
+        <v>7.30156</v>
+      </c>
+      <c r="O17">
+        <v>1.460312</v>
+      </c>
+      <c r="P17">
+        <v>5.841248</v>
+      </c>
+      <c r="Q17">
+        <v>9.301248000000001</v>
+      </c>
+      <c r="R17">
+        <v>0.1764705882352941</v>
+      </c>
+      <c r="S17">
+        <v>0.1095494855153279</v>
+      </c>
+      <c r="T17">
+        <v>1.256349586540976</v>
+      </c>
+      <c r="U17">
+        <v>0.048</v>
+      </c>
+      <c r="V17">
+        <v>0.2</v>
+      </c>
+      <c r="W17">
+        <v>0.0384</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y17">
+        <v>7.865982095839916</v>
+      </c>
+      <c r="Z17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18">
+        <v>0.16</v>
+      </c>
+      <c r="B18">
+        <v>0.09894106874434203</v>
+      </c>
+      <c r="C18">
+        <v>121.7227317726217</v>
+      </c>
+      <c r="D18">
+        <v>144.7237317726217</v>
+      </c>
+      <c r="E18">
+        <v>-22.468</v>
+      </c>
+      <c r="F18">
+        <v>23.632</v>
+      </c>
+      <c r="G18">
+        <v>0.631</v>
+      </c>
+      <c r="H18">
+        <v>101.6</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>11.825</v>
+      </c>
+      <c r="K18">
+        <v>3.460000000000001</v>
+      </c>
+      <c r="L18">
+        <v>8.365</v>
+      </c>
+      <c r="M18">
+        <v>1.169784</v>
+      </c>
+      <c r="N18">
+        <v>7.195216</v>
+      </c>
+      <c r="O18">
+        <v>1.4390432</v>
+      </c>
+      <c r="P18">
+        <v>5.7561728</v>
+      </c>
+      <c r="Q18">
+        <v>9.216172800000001</v>
+      </c>
+      <c r="R18">
+        <v>0.1904761904761905</v>
+      </c>
+      <c r="S18">
+        <v>0.11024412945755</v>
+      </c>
+      <c r="T18">
+        <v>1.268684879486886</v>
+      </c>
+      <c r="U18">
+        <v>0.0495</v>
+      </c>
+      <c r="V18">
+        <v>0.2</v>
+      </c>
+      <c r="W18">
+        <v>0.0396</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y18">
+        <v>7.150892814399924</v>
+      </c>
+      <c r="Z18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19">
+        <v>0.17</v>
+      </c>
+      <c r="B19">
+        <v>0.09882507480065537</v>
+      </c>
+      <c r="C19">
+        <v>120.5253995023015</v>
+      </c>
+      <c r="D19">
+        <v>145.0033995023015</v>
+      </c>
+      <c r="E19">
+        <v>-20.991</v>
+      </c>
+      <c r="F19">
+        <v>25.109</v>
+      </c>
+      <c r="G19">
+        <v>0.631</v>
+      </c>
+      <c r="H19">
+        <v>101.6</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>11.825</v>
+      </c>
+      <c r="K19">
+        <v>3.460000000000001</v>
+      </c>
+      <c r="L19">
+        <v>8.365</v>
+      </c>
+      <c r="M19">
+        <v>1.2428955</v>
+      </c>
+      <c r="N19">
+        <v>7.122104500000001</v>
+      </c>
+      <c r="O19">
+        <v>1.4244209</v>
+      </c>
+      <c r="P19">
+        <v>5.6976836</v>
+      </c>
+      <c r="Q19">
+        <v>9.157683600000002</v>
+      </c>
+      <c r="R19">
+        <v>0.2048192771084338</v>
+      </c>
+      <c r="S19">
+        <v>0.1109555118080185</v>
+      </c>
+      <c r="T19">
+        <v>1.281317408407397</v>
+      </c>
+      <c r="U19">
+        <v>0.0495</v>
+      </c>
+      <c r="V19">
+        <v>0.2</v>
+      </c>
+      <c r="W19">
+        <v>0.0396</v>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y19">
+        <v>6.730252060611694</v>
+      </c>
+      <c r="Z19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20">
+        <v>0.18</v>
+      </c>
+      <c r="B20">
+        <v>0.09870908085696871</v>
+      </c>
+      <c r="C20">
+        <v>119.3291501984505</v>
+      </c>
+      <c r="D20">
+        <v>145.2841501984505</v>
+      </c>
+      <c r="E20">
+        <v>-19.514</v>
+      </c>
+      <c r="F20">
+        <v>26.586</v>
+      </c>
+      <c r="G20">
+        <v>0.631</v>
+      </c>
+      <c r="H20">
+        <v>101.6</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>11.825</v>
+      </c>
+      <c r="K20">
+        <v>3.460000000000001</v>
+      </c>
+      <c r="L20">
+        <v>8.365</v>
+      </c>
+      <c r="M20">
+        <v>1.316007</v>
+      </c>
+      <c r="N20">
+        <v>7.048993</v>
+      </c>
+      <c r="O20">
+        <v>1.4097986</v>
+      </c>
+      <c r="P20">
+        <v>5.6391944</v>
+      </c>
+      <c r="Q20">
+        <v>9.099194400000002</v>
+      </c>
+      <c r="R20">
+        <v>0.2195121951219512</v>
+      </c>
+      <c r="S20">
+        <v>0.1116842449475228</v>
+      </c>
+      <c r="T20">
+        <v>1.294258047789383</v>
+      </c>
+      <c r="U20">
+        <v>0.0495</v>
+      </c>
+      <c r="V20">
+        <v>0.2</v>
+      </c>
+      <c r="W20">
+        <v>0.0396</v>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y20">
+        <v>6.356349168355488</v>
+      </c>
+      <c r="Z20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21">
+        <v>0.19</v>
+      </c>
+      <c r="B21">
+        <v>0.09880588691328207</v>
+      </c>
+      <c r="C21">
+        <v>117.6177667679402</v>
+      </c>
+      <c r="D21">
+        <v>145.0497667679402</v>
+      </c>
+      <c r="E21">
+        <v>-18.037</v>
+      </c>
+      <c r="F21">
+        <v>28.063</v>
+      </c>
+      <c r="G21">
+        <v>0.631</v>
+      </c>
+      <c r="H21">
+        <v>101.6</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>11.825</v>
+      </c>
+      <c r="K21">
+        <v>3.460000000000001</v>
+      </c>
+      <c r="L21">
+        <v>8.365</v>
+      </c>
+      <c r="M21">
+        <v>1.4284067</v>
+      </c>
+      <c r="N21">
+        <v>6.9365933</v>
+      </c>
+      <c r="O21">
+        <v>1.38731866</v>
+      </c>
+      <c r="P21">
+        <v>5.54927464</v>
+      </c>
+      <c r="Q21">
+        <v>9.009274640000001</v>
+      </c>
+      <c r="R21">
+        <v>0.2345679012345679</v>
+      </c>
+      <c r="S21">
+        <v>0.1124309714978791</v>
+      </c>
+      <c r="T21">
+        <v>1.307518209131419</v>
+      </c>
+      <c r="U21">
+        <v>0.0509</v>
+      </c>
+      <c r="V21">
+        <v>0.2</v>
+      </c>
+      <c r="W21">
+        <v>0.04072000000000001</v>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y21">
+        <v>5.856175275571026</v>
+      </c>
+      <c r="Z21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22">
+        <v>0.2</v>
+      </c>
+      <c r="B22">
+        <v>0.09870109296959541</v>
+      </c>
+      <c r="C22">
+        <v>116.3945240257278</v>
+      </c>
+      <c r="D22">
+        <v>145.3035240257278</v>
+      </c>
+      <c r="E22">
+        <v>-16.56</v>
+      </c>
+      <c r="F22">
+        <v>29.54</v>
+      </c>
+      <c r="G22">
+        <v>0.631</v>
+      </c>
+      <c r="H22">
+        <v>101.6</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>11.825</v>
+      </c>
+      <c r="K22">
+        <v>3.460000000000001</v>
+      </c>
+      <c r="L22">
+        <v>8.365</v>
+      </c>
+      <c r="M22">
+        <v>1.503586</v>
+      </c>
+      <c r="N22">
+        <v>6.861414</v>
+      </c>
+      <c r="O22">
+        <v>1.3722828</v>
+      </c>
+      <c r="P22">
+        <v>5.4891312</v>
+      </c>
+      <c r="Q22">
+        <v>8.9491312</v>
+      </c>
+      <c r="R22">
+        <v>0.25</v>
+      </c>
+      <c r="S22">
+        <v>0.1131963662119942</v>
+      </c>
+      <c r="T22">
+        <v>1.321109874507005</v>
+      </c>
+      <c r="U22">
+        <v>0.0509</v>
+      </c>
+      <c r="V22">
+        <v>0.2</v>
+      </c>
+      <c r="W22">
+        <v>0.04072000000000001</v>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y22">
+        <v>5.563366511792474</v>
+      </c>
+      <c r="Z22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23">
+        <v>0.21</v>
+      </c>
+      <c r="B23">
+        <v>0.09859629902590875</v>
+      </c>
+      <c r="C23">
+        <v>115.1721707105941</v>
+      </c>
+      <c r="D23">
+        <v>145.5581707105941</v>
+      </c>
+      <c r="E23">
+        <v>-15.08300000000001</v>
+      </c>
+      <c r="F23">
+        <v>31.017</v>
+      </c>
+      <c r="G23">
+        <v>0.631</v>
+      </c>
+      <c r="H23">
+        <v>101.6</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>11.825</v>
+      </c>
+      <c r="K23">
+        <v>3.460000000000001</v>
+      </c>
+      <c r="L23">
+        <v>8.365</v>
+      </c>
+      <c r="M23">
+        <v>1.5787653</v>
+      </c>
+      <c r="N23">
+        <v>6.786234700000001</v>
+      </c>
+      <c r="O23">
+        <v>1.35724694</v>
+      </c>
+      <c r="P23">
+        <v>5.42898776</v>
+      </c>
+      <c r="Q23">
+        <v>8.888987760000001</v>
+      </c>
+      <c r="R23">
+        <v>0.2658227848101266</v>
+      </c>
+      <c r="S23">
+        <v>0.1139811380074794</v>
+      </c>
+      <c r="T23">
+        <v>1.33504563267691</v>
+      </c>
+      <c r="U23">
+        <v>0.0509</v>
+      </c>
+      <c r="V23">
+        <v>0.2</v>
+      </c>
+      <c r="W23">
+        <v>0.04072000000000001</v>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y23">
+        <v>5.298444296945215</v>
+      </c>
+      <c r="Z23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24">
+        <v>0.22</v>
+      </c>
+      <c r="B24">
+        <v>0.0984915050822221</v>
+      </c>
+      <c r="C24">
+        <v>113.9507115069531</v>
+      </c>
+      <c r="D24">
+        <v>145.8137115069531</v>
+      </c>
+      <c r="E24">
+        <v>-13.606</v>
+      </c>
+      <c r="F24">
+        <v>32.494</v>
+      </c>
+      <c r="G24">
+        <v>0.631</v>
+      </c>
+      <c r="H24">
+        <v>101.6</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <v>11.825</v>
+      </c>
+      <c r="K24">
+        <v>3.460000000000001</v>
+      </c>
+      <c r="L24">
+        <v>8.365</v>
+      </c>
+      <c r="M24">
+        <v>1.6539446</v>
+      </c>
+      <c r="N24">
+        <v>6.7110554</v>
+      </c>
+      <c r="O24">
+        <v>1.34221108</v>
+      </c>
+      <c r="P24">
+        <v>5.36884432</v>
+      </c>
+      <c r="Q24">
+        <v>8.828844320000002</v>
+      </c>
+      <c r="R24">
+        <v>0.282051282051282</v>
+      </c>
+      <c r="S24">
+        <v>0.114786032156695</v>
+      </c>
+      <c r="T24">
+        <v>1.349338717979377</v>
+      </c>
+      <c r="U24">
+        <v>0.0509</v>
+      </c>
+      <c r="V24">
+        <v>0.2</v>
+      </c>
+      <c r="W24">
+        <v>0.04072000000000001</v>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y24">
+        <v>5.057605919811341</v>
+      </c>
+      <c r="Z24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25">
+        <v>0.23</v>
+      </c>
+      <c r="B25">
+        <v>0.09838671113853543</v>
+      </c>
+      <c r="C25">
+        <v>112.7301511321722</v>
+      </c>
+      <c r="D25">
+        <v>146.0701511321722</v>
+      </c>
+      <c r="E25">
+        <v>-12.129</v>
+      </c>
+      <c r="F25">
+        <v>33.971</v>
+      </c>
+      <c r="G25">
+        <v>0.631</v>
+      </c>
+      <c r="H25">
+        <v>101.6</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <v>11.825</v>
+      </c>
+      <c r="K25">
+        <v>3.460000000000001</v>
+      </c>
+      <c r="L25">
+        <v>8.365</v>
+      </c>
+      <c r="M25">
+        <v>1.7291239</v>
+      </c>
+      <c r="N25">
+        <v>6.635876100000001</v>
+      </c>
+      <c r="O25">
+        <v>1.32717522</v>
+      </c>
+      <c r="P25">
+        <v>5.308700880000001</v>
+      </c>
+      <c r="Q25">
+        <v>8.768700880000001</v>
+      </c>
+      <c r="R25">
+        <v>0.2987012987012987</v>
+      </c>
+      <c r="S25">
+        <v>0.1156118326474486</v>
+      </c>
+      <c r="T25">
+        <v>1.364003052250739</v>
+      </c>
+      <c r="U25">
+        <v>0.0509</v>
+      </c>
+      <c r="V25">
+        <v>0.2</v>
+      </c>
+      <c r="W25">
+        <v>0.04072000000000001</v>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y25">
+        <v>4.837710010254327</v>
+      </c>
+      <c r="Z25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26">
+        <v>0.24</v>
+      </c>
+      <c r="B26">
+        <v>0.09828191719484877</v>
+      </c>
+      <c r="C26">
+        <v>111.5104943368625</v>
+      </c>
+      <c r="D26">
+        <v>146.3274943368625</v>
+      </c>
+      <c r="E26">
+        <v>-10.65200000000001</v>
+      </c>
+      <c r="F26">
+        <v>35.44799999999999</v>
+      </c>
+      <c r="G26">
+        <v>0.631</v>
+      </c>
+      <c r="H26">
+        <v>101.6</v>
+      </c>
+      <c r="I26">
+        <v>0</v>
+      </c>
+      <c r="J26">
+        <v>11.825</v>
+      </c>
+      <c r="K26">
+        <v>3.460000000000001</v>
+      </c>
+      <c r="L26">
+        <v>8.365</v>
+      </c>
+      <c r="M26">
+        <v>1.8043032</v>
+      </c>
+      <c r="N26">
+        <v>6.560696800000001</v>
+      </c>
+      <c r="O26">
+        <v>1.31213936</v>
+      </c>
+      <c r="P26">
+        <v>5.248557440000001</v>
+      </c>
+      <c r="Q26">
+        <v>8.708557440000002</v>
+      </c>
+      <c r="R26">
+        <v>0.3157894736842105</v>
+      </c>
+      <c r="S26">
+        <v>0.1164593647300642</v>
+      </c>
+      <c r="T26">
+        <v>1.379053290055558</v>
+      </c>
+      <c r="U26">
+        <v>0.0509</v>
+      </c>
+      <c r="V26">
+        <v>0.2</v>
+      </c>
+      <c r="W26">
+        <v>0.04072000000000001</v>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y26">
+        <v>4.636138759827063</v>
+      </c>
+      <c r="Z26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27">
+        <v>0.25</v>
+      </c>
+      <c r="B27">
+        <v>0.09869712325116212</v>
+      </c>
+      <c r="C27">
+        <v>109.0191541055453</v>
+      </c>
+      <c r="D27">
+        <v>145.3131541055453</v>
+      </c>
+      <c r="E27">
+        <v>-9.175000000000004</v>
+      </c>
+      <c r="F27">
+        <v>36.925</v>
+      </c>
+      <c r="G27">
+        <v>0.631</v>
+      </c>
+      <c r="H27">
+        <v>101.6</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+      <c r="J27">
+        <v>11.825</v>
+      </c>
+      <c r="K27">
+        <v>3.460000000000001</v>
+      </c>
+      <c r="L27">
+        <v>8.365</v>
+      </c>
+      <c r="M27">
+        <v>1.9754875</v>
+      </c>
+      <c r="N27">
+        <v>6.3895125</v>
+      </c>
+      <c r="O27">
+        <v>1.2779025</v>
+      </c>
+      <c r="P27">
+        <v>5.111610000000001</v>
+      </c>
+      <c r="Q27">
+        <v>8.571610000000002</v>
+      </c>
+      <c r="R27">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="S27">
+        <v>0.1173294976682162</v>
+      </c>
+      <c r="T27">
+        <v>1.394504867535172</v>
+      </c>
+      <c r="U27">
+        <v>0.0535</v>
+      </c>
+      <c r="V27">
+        <v>0.2</v>
+      </c>
+      <c r="W27">
+        <v>0.0428</v>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>Baa2/BBB</t>
+        </is>
+      </c>
+      <c r="Y27">
+        <v>4.234397838508217</v>
+      </c>
+      <c r="Z27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28">
+        <v>0.26</v>
+      </c>
+      <c r="B28">
+        <v>0.09861312930747546</v>
+      </c>
+      <c r="C28">
+        <v>107.7462133986167</v>
+      </c>
+      <c r="D28">
+        <v>145.5172133986167</v>
+      </c>
+      <c r="E28">
+        <v>-7.698</v>
+      </c>
+      <c r="F28">
+        <v>38.402</v>
+      </c>
+      <c r="G28">
+        <v>0.631</v>
+      </c>
+      <c r="H28">
+        <v>101.6</v>
+      </c>
+      <c r="I28">
+        <v>0</v>
+      </c>
+      <c r="J28">
+        <v>11.825</v>
+      </c>
+      <c r="K28">
+        <v>3.460000000000001</v>
+      </c>
+      <c r="L28">
+        <v>8.365</v>
+      </c>
+      <c r="M28">
+        <v>2.054507</v>
+      </c>
+      <c r="N28">
+        <v>6.310493</v>
+      </c>
+      <c r="O28">
+        <v>1.2620986</v>
+      </c>
+      <c r="P28">
+        <v>5.0483944</v>
+      </c>
+      <c r="Q28">
+        <v>8.5083944</v>
+      </c>
+      <c r="R28">
+        <v>0.3513513513513514</v>
+      </c>
+      <c r="S28">
+        <v>0.1182231477128047</v>
+      </c>
+      <c r="T28">
+        <v>1.410374055216938</v>
+      </c>
+      <c r="U28">
+        <v>0.0535</v>
+      </c>
+      <c r="V28">
+        <v>0.2</v>
+      </c>
+      <c r="W28">
+        <v>0.0428</v>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>Baa2/BBB</t>
+        </is>
+      </c>
+      <c r="Y28">
+        <v>4.071536383180977</v>
+      </c>
+      <c r="Z28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29">
+        <v>0.27</v>
+      </c>
+      <c r="B29">
+        <v>0.0991123353637888</v>
+      </c>
+      <c r="C29">
+        <v>105.0647653567979</v>
+      </c>
+      <c r="D29">
+        <v>144.3127653567979</v>
+      </c>
+      <c r="E29">
+        <v>-6.221000000000004</v>
+      </c>
+      <c r="F29">
+        <v>39.879</v>
+      </c>
+      <c r="G29">
+        <v>0.631</v>
+      </c>
+      <c r="H29">
+        <v>101.6</v>
+      </c>
+      <c r="I29">
+        <v>0</v>
+      </c>
+      <c r="J29">
+        <v>11.825</v>
+      </c>
+      <c r="K29">
+        <v>3.460000000000001</v>
+      </c>
+      <c r="L29">
+        <v>8.365</v>
+      </c>
+      <c r="M29">
+        <v>2.2411998</v>
+      </c>
+      <c r="N29">
+        <v>6.1238002</v>
+      </c>
+      <c r="O29">
+        <v>1.22476004</v>
+      </c>
+      <c r="P29">
+        <v>4.89904016</v>
+      </c>
+      <c r="Q29">
+        <v>8.359040160000001</v>
+      </c>
+      <c r="R29">
+        <v>0.3698630136986302</v>
+      </c>
+      <c r="S29">
+        <v>0.1191412813202586</v>
+      </c>
+      <c r="T29">
+        <v>1.426678015163958</v>
+      </c>
+      <c r="U29">
+        <v>0.0562</v>
+      </c>
+      <c r="V29">
+        <v>0.2</v>
+      </c>
+      <c r="W29">
+        <v>0.04496</v>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y29">
+        <v>3.732375846187386</v>
+      </c>
+      <c r="Z29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30">
+        <v>0.28</v>
+      </c>
+      <c r="B30">
+        <v>0.09904994142010214</v>
+      </c>
+      <c r="C30">
+        <v>103.7372135113141</v>
+      </c>
+      <c r="D30">
+        <v>144.462213511314</v>
+      </c>
+      <c r="E30">
+        <v>-4.744</v>
+      </c>
+      <c r="F30">
+        <v>41.356</v>
+      </c>
+      <c r="G30">
+        <v>0.631</v>
+      </c>
+      <c r="H30">
+        <v>101.6</v>
+      </c>
+      <c r="I30">
+        <v>0</v>
+      </c>
+      <c r="J30">
+        <v>11.825</v>
+      </c>
+      <c r="K30">
+        <v>3.460000000000001</v>
+      </c>
+      <c r="L30">
+        <v>8.365</v>
+      </c>
+      <c r="M30">
+        <v>2.3242072</v>
+      </c>
+      <c r="N30">
+        <v>6.0407928</v>
+      </c>
+      <c r="O30">
+        <v>1.20815856</v>
+      </c>
+      <c r="P30">
+        <v>4.83263424</v>
+      </c>
+      <c r="Q30">
+        <v>8.292634240000002</v>
+      </c>
+      <c r="R30">
+        <v>0.388888888888889</v>
+      </c>
+      <c r="S30">
+        <v>0.1200849186390308</v>
+      </c>
+      <c r="T30">
+        <v>1.443434862887284</v>
+      </c>
+      <c r="U30">
+        <v>0.0562</v>
+      </c>
+      <c r="V30">
+        <v>0.2</v>
+      </c>
+      <c r="W30">
+        <v>0.04496</v>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y30">
+        <v>3.599076708823551</v>
+      </c>
+      <c r="Z30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31">
+        <v>0.29</v>
+      </c>
+      <c r="B31">
+        <v>0.1000779474764155</v>
+      </c>
+      <c r="C31">
+        <v>99.83669842123669</v>
+      </c>
+      <c r="D31">
+        <v>142.0386984212367</v>
+      </c>
+      <c r="E31">
+        <v>-3.26700000000001</v>
+      </c>
+      <c r="F31">
+        <v>42.83299999999999</v>
+      </c>
+      <c r="G31">
+        <v>0.631</v>
+      </c>
+      <c r="H31">
+        <v>101.6</v>
+      </c>
+      <c r="I31">
+        <v>0</v>
+      </c>
+      <c r="J31">
+        <v>11.825</v>
+      </c>
+      <c r="K31">
+        <v>3.460000000000001</v>
+      </c>
+      <c r="L31">
+        <v>8.365</v>
+      </c>
+      <c r="M31">
+        <v>2.6085297</v>
+      </c>
+      <c r="N31">
+        <v>5.7564703</v>
+      </c>
+      <c r="O31">
+        <v>1.15129406</v>
+      </c>
+      <c r="P31">
+        <v>4.60517624</v>
+      </c>
+      <c r="Q31">
+        <v>8.065176240000001</v>
+      </c>
+      <c r="R31">
+        <v>0.4084507042253521</v>
+      </c>
+      <c r="S31">
+        <v>0.121055137290726</v>
+      </c>
+      <c r="T31">
+        <v>1.46066373449014</v>
+      </c>
+      <c r="U31">
+        <v>0.0609</v>
+      </c>
+      <c r="V31">
+        <v>0.2</v>
+      </c>
+      <c r="W31">
+        <v>0.04872000000000001</v>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>Ba2/BB</t>
+        </is>
+      </c>
+      <c r="Y31">
+        <v>3.20678733310953</v>
+      </c>
+      <c r="Z31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32">
+        <v>0.3</v>
+      </c>
+      <c r="B32">
+        <v>0.1000531535327288</v>
+      </c>
+      <c r="C32">
+        <v>98.41719259560762</v>
+      </c>
+      <c r="D32">
+        <v>142.0961925956076</v>
+      </c>
+      <c r="E32">
+        <v>-1.790000000000006</v>
+      </c>
+      <c r="F32">
+        <v>44.31</v>
+      </c>
+      <c r="G32">
+        <v>0.631</v>
+      </c>
+      <c r="H32">
+        <v>101.6</v>
+      </c>
+      <c r="I32">
+        <v>0</v>
+      </c>
+      <c r="J32">
+        <v>11.825</v>
+      </c>
+      <c r="K32">
+        <v>3.460000000000001</v>
+      </c>
+      <c r="L32">
+        <v>8.365</v>
+      </c>
+      <c r="M32">
+        <v>2.698479</v>
+      </c>
+      <c r="N32">
+        <v>5.666521</v>
+      </c>
+      <c r="O32">
+        <v>1.1333042</v>
+      </c>
+      <c r="P32">
+        <v>4.5332168</v>
+      </c>
+      <c r="Q32">
+        <v>7.993216800000001</v>
+      </c>
+      <c r="R32">
+        <v>0.4285714285714286</v>
+      </c>
+      <c r="S32">
+        <v>0.1220530764753269</v>
+      </c>
+      <c r="T32">
+        <v>1.478384859567363</v>
+      </c>
+      <c r="U32">
+        <v>0.0609</v>
+      </c>
+      <c r="V32">
+        <v>0.2</v>
+      </c>
+      <c r="W32">
+        <v>0.04872000000000001</v>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>Ba2/BB</t>
+        </is>
+      </c>
+      <c r="Y32">
+        <v>3.099894422005878</v>
+      </c>
+      <c r="Z32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33">
+        <v>0.31</v>
+      </c>
+      <c r="B33">
+        <v>0.1023347595890422</v>
+      </c>
+      <c r="C33">
+        <v>91.83735541321715</v>
+      </c>
+      <c r="D33">
+        <v>136.9933554132172</v>
+      </c>
+      <c r="E33">
+        <v>-0.3130000000000024</v>
+      </c>
+      <c r="F33">
+        <v>45.787</v>
+      </c>
+      <c r="G33">
+        <v>0.631</v>
+      </c>
+      <c r="H33">
+        <v>101.6</v>
+      </c>
+      <c r="I33">
+        <v>0</v>
+      </c>
+      <c r="J33">
+        <v>11.825</v>
+      </c>
+      <c r="K33">
+        <v>3.460000000000001</v>
+      </c>
+      <c r="L33">
+        <v>8.365</v>
+      </c>
+      <c r="M33">
+        <v>3.2142474</v>
+      </c>
+      <c r="N33">
+        <v>5.150752600000001</v>
+      </c>
+      <c r="O33">
+        <v>1.03015052</v>
+      </c>
+      <c r="P33">
+        <v>4.12060208</v>
+      </c>
+      <c r="Q33">
+        <v>7.580602080000001</v>
+      </c>
+      <c r="R33">
+        <v>0.4492753623188406</v>
+      </c>
+      <c r="S33">
+        <v>0.1230799414333945</v>
+      </c>
+      <c r="T33">
+        <v>1.496619640443926</v>
+      </c>
+      <c r="U33">
+        <v>0.0702</v>
+      </c>
+      <c r="V33">
+        <v>0.2</v>
+      </c>
+      <c r="W33">
+        <v>0.05616</v>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>B1/B+</t>
+        </is>
+      </c>
+      <c r="Y33">
+        <v>2.602475465951999</v>
+      </c>
+      <c r="Z33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34">
+        <v>0.32</v>
+      </c>
+      <c r="B34">
+        <v>0.1023843656453555</v>
+      </c>
+      <c r="C34">
+        <v>90.25347850984308</v>
+      </c>
+      <c r="D34">
+        <v>136.8864785098431</v>
+      </c>
+      <c r="E34">
+        <v>1.163999999999994</v>
+      </c>
+      <c r="F34">
+        <v>47.264</v>
+      </c>
+      <c r="G34">
+        <v>0.631</v>
+      </c>
+      <c r="H34">
+        <v>101.6</v>
+      </c>
+      <c r="I34">
+        <v>0</v>
+      </c>
+      <c r="J34">
+        <v>11.825</v>
+      </c>
+      <c r="K34">
+        <v>3.460000000000001</v>
+      </c>
+      <c r="L34">
+        <v>8.365</v>
+      </c>
+      <c r="M34">
+        <v>3.317932799999999</v>
+      </c>
+      <c r="N34">
+        <v>5.047067200000001</v>
+      </c>
+      <c r="O34">
+        <v>1.00941344</v>
+      </c>
+      <c r="P34">
+        <v>4.03765376</v>
+      </c>
+      <c r="Q34">
+        <v>7.497653760000001</v>
+      </c>
+      <c r="R34">
+        <v>0.4705882352941177</v>
+      </c>
+      <c r="S34">
+        <v>0.1241370083019934</v>
+      </c>
+      <c r="T34">
+        <v>1.515390738405094</v>
+      </c>
+      <c r="U34">
+        <v>0.0702</v>
+      </c>
+      <c r="V34">
+        <v>0.2</v>
+      </c>
+      <c r="W34">
+        <v>0.05616</v>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>B1/B+</t>
+        </is>
+      </c>
+      <c r="Y34">
+        <v>2.521148107640999</v>
+      </c>
+      <c r="Z34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35">
+        <v>0.33</v>
+      </c>
+      <c r="B35">
+        <v>0.1036747717016688</v>
+      </c>
+      <c r="C35">
+        <v>86.05370760424672</v>
+      </c>
+      <c r="D35">
+        <v>134.1637076042467</v>
+      </c>
+      <c r="E35">
+        <v>2.640999999999998</v>
+      </c>
+      <c r="F35">
+        <v>48.741</v>
+      </c>
+      <c r="G35">
+        <v>0.631</v>
+      </c>
+      <c r="H35">
+        <v>101.6</v>
+      </c>
+      <c r="I35">
+        <v>0</v>
+      </c>
+      <c r="J35">
+        <v>11.825</v>
+      </c>
+      <c r="K35">
+        <v>3.460000000000001</v>
+      </c>
+      <c r="L35">
+        <v>8.365</v>
+      </c>
+      <c r="M35">
+        <v>3.6507009</v>
+      </c>
+      <c r="N35">
+        <v>4.7142991</v>
+      </c>
+      <c r="O35">
+        <v>0.94285982</v>
+      </c>
+      <c r="P35">
+        <v>3.77143928</v>
+      </c>
+      <c r="Q35">
+        <v>7.231439280000001</v>
+      </c>
+      <c r="R35">
+        <v>0.4925373134328359</v>
+      </c>
+      <c r="S35">
+        <v>0.1252256294054759</v>
+      </c>
+      <c r="T35">
+        <v>1.534722167648685</v>
+      </c>
+      <c r="U35">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V35">
+        <v>0.2</v>
+      </c>
+      <c r="W35">
+        <v>0.05992</v>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y35">
+        <v>2.29134082170358</v>
+      </c>
+      <c r="Z35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36">
+        <v>0.34</v>
+      </c>
+      <c r="B36">
+        <v>0.1037619777579822</v>
+      </c>
+      <c r="C36">
+        <v>84.39660397679671</v>
+      </c>
+      <c r="D36">
+        <v>133.9836039767967</v>
+      </c>
+      <c r="E36">
+        <v>4.117999999999995</v>
+      </c>
+      <c r="F36">
+        <v>50.218</v>
+      </c>
+      <c r="G36">
+        <v>0.631</v>
+      </c>
+      <c r="H36">
+        <v>101.6</v>
+      </c>
+      <c r="I36">
+        <v>0</v>
+      </c>
+      <c r="J36">
+        <v>11.825</v>
+      </c>
+      <c r="K36">
+        <v>3.460000000000001</v>
+      </c>
+      <c r="L36">
+        <v>8.365</v>
+      </c>
+      <c r="M36">
+        <v>3.761328199999999</v>
+      </c>
+      <c r="N36">
+        <v>4.603671800000001</v>
+      </c>
+      <c r="O36">
+        <v>0.9207343600000002</v>
+      </c>
+      <c r="P36">
+        <v>3.682937440000001</v>
+      </c>
+      <c r="Q36">
+        <v>7.142937440000002</v>
+      </c>
+      <c r="R36">
+        <v>0.5151515151515152</v>
+      </c>
+      <c r="S36">
+        <v>0.1263472390272458</v>
+      </c>
+      <c r="T36">
+        <v>1.554639397778446</v>
+      </c>
+      <c r="U36">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V36">
+        <v>0.2</v>
+      </c>
+      <c r="W36">
+        <v>0.05992</v>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y36">
+        <v>2.223948444594652</v>
+      </c>
+      <c r="Z36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37">
+        <v>0.35</v>
+      </c>
+      <c r="B37">
+        <v>0.1038491838142955</v>
+      </c>
+      <c r="C37">
+        <v>82.73998324939723</v>
+      </c>
+      <c r="D37">
+        <v>133.8039832493972</v>
+      </c>
+      <c r="E37">
+        <v>5.594999999999999</v>
+      </c>
+      <c r="F37">
+        <v>51.695</v>
+      </c>
+      <c r="G37">
+        <v>0.631</v>
+      </c>
+      <c r="H37">
+        <v>101.6</v>
+      </c>
+      <c r="I37">
+        <v>0</v>
+      </c>
+      <c r="J37">
+        <v>11.825</v>
+      </c>
+      <c r="K37">
+        <v>3.460000000000001</v>
+      </c>
+      <c r="L37">
+        <v>8.365</v>
+      </c>
+      <c r="M37">
+        <v>3.8719555</v>
+      </c>
+      <c r="N37">
+        <v>4.4930445</v>
+      </c>
+      <c r="O37">
+        <v>0.8986089</v>
+      </c>
+      <c r="P37">
+        <v>3.5944356</v>
+      </c>
+      <c r="Q37">
+        <v>7.054435600000001</v>
+      </c>
+      <c r="R37">
+        <v>0.5384615384615385</v>
+      </c>
+      <c r="S37">
+        <v>0.1275033597143008</v>
+      </c>
+      <c r="T37">
+        <v>1.575169465758352</v>
+      </c>
+      <c r="U37">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V37">
+        <v>0.2</v>
+      </c>
+      <c r="W37">
+        <v>0.05992</v>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y37">
+        <v>2.160407060463376</v>
+      </c>
+      <c r="Z37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38">
+        <v>0.36</v>
+      </c>
+      <c r="B38">
+        <v>0.1039363898706089</v>
+      </c>
+      <c r="C38">
+        <v>81.08384348249609</v>
+      </c>
+      <c r="D38">
+        <v>133.6248434824961</v>
+      </c>
+      <c r="E38">
+        <v>7.071999999999996</v>
+      </c>
+      <c r="F38">
+        <v>53.172</v>
+      </c>
+      <c r="G38">
+        <v>0.631</v>
+      </c>
+      <c r="H38">
+        <v>101.6</v>
+      </c>
+      <c r="I38">
+        <v>0</v>
+      </c>
+      <c r="J38">
+        <v>11.825</v>
+      </c>
+      <c r="K38">
+        <v>3.460000000000001</v>
+      </c>
+      <c r="L38">
+        <v>8.365</v>
+      </c>
+      <c r="M38">
+        <v>3.982582799999999</v>
+      </c>
+      <c r="N38">
+        <v>4.382417200000001</v>
+      </c>
+      <c r="O38">
+        <v>0.8764834400000002</v>
+      </c>
+      <c r="P38">
+        <v>3.50593376</v>
+      </c>
+      <c r="Q38">
+        <v>6.965933760000001</v>
+      </c>
+      <c r="R38">
+        <v>0.5625</v>
+      </c>
+      <c r="S38">
+        <v>0.1286956091728264</v>
+      </c>
+      <c r="T38">
+        <v>1.596341098362631</v>
+      </c>
+      <c r="U38">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V38">
+        <v>0.2</v>
+      </c>
+      <c r="W38">
+        <v>0.05992</v>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y38">
+        <v>2.100395753228282</v>
+      </c>
+      <c r="Z38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39">
+        <v>0.37</v>
+      </c>
+      <c r="B39">
+        <v>0.1040235959269222</v>
+      </c>
+      <c r="C39">
+        <v>79.4281827469143</v>
+      </c>
+      <c r="D39">
+        <v>133.4461827469143</v>
+      </c>
+      <c r="E39">
+        <v>8.548999999999992</v>
+      </c>
+      <c r="F39">
+        <v>54.64899999999999</v>
+      </c>
+      <c r="G39">
+        <v>0.631</v>
+      </c>
+      <c r="H39">
+        <v>101.6</v>
+      </c>
+      <c r="I39">
+        <v>0</v>
+      </c>
+      <c r="J39">
+        <v>11.825</v>
+      </c>
+      <c r="K39">
+        <v>3.460000000000001</v>
+      </c>
+      <c r="L39">
+        <v>8.365</v>
+      </c>
+      <c r="M39">
+        <v>4.093210099999999</v>
+      </c>
+      <c r="N39">
+        <v>4.271789900000001</v>
+      </c>
+      <c r="O39">
+        <v>0.8543579800000002</v>
+      </c>
+      <c r="P39">
+        <v>3.417431920000001</v>
+      </c>
+      <c r="Q39">
+        <v>6.877431920000001</v>
+      </c>
+      <c r="R39">
+        <v>0.5873015873015873</v>
+      </c>
+      <c r="S39">
+        <v>0.1299257078205115</v>
+      </c>
+      <c r="T39">
+        <v>1.618184846287681</v>
+      </c>
+      <c r="U39">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V39">
+        <v>0.2</v>
+      </c>
+      <c r="W39">
+        <v>0.05992</v>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y39">
+        <v>2.043628300438328</v>
+      </c>
+      <c r="Z39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40">
+        <v>0.38</v>
+      </c>
+      <c r="B40">
+        <v>0.1090660019832356</v>
+      </c>
+      <c r="C40">
+        <v>68.37486103964713</v>
+      </c>
+      <c r="D40">
+        <v>123.8698610396471</v>
+      </c>
+      <c r="E40">
+        <v>10.026</v>
+      </c>
+      <c r="F40">
+        <v>56.126</v>
+      </c>
+      <c r="G40">
+        <v>0.631</v>
+      </c>
+      <c r="H40">
+        <v>101.6</v>
+      </c>
+      <c r="I40">
+        <v>0</v>
+      </c>
+      <c r="J40">
+        <v>11.825</v>
+      </c>
+      <c r="K40">
+        <v>3.460000000000001</v>
+      </c>
+      <c r="L40">
+        <v>8.365</v>
+      </c>
+      <c r="M40">
+        <v>5.1186912</v>
+      </c>
+      <c r="N40">
+        <v>3.2463088</v>
+      </c>
+      <c r="O40">
+        <v>0.6492617600000001</v>
+      </c>
+      <c r="P40">
+        <v>2.597047040000001</v>
+      </c>
+      <c r="Q40">
+        <v>6.057047040000001</v>
+      </c>
+      <c r="R40">
+        <v>0.6129032258064516</v>
+      </c>
+      <c r="S40">
+        <v>0.1311954870697348</v>
+      </c>
+      <c r="T40">
+        <v>1.640733231242571</v>
+      </c>
+      <c r="U40">
+        <v>0.0912</v>
+      </c>
+      <c r="V40">
+        <v>0.2</v>
+      </c>
+      <c r="W40">
+        <v>0.07296000000000001</v>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y40">
+        <v>1.634206806614941</v>
+      </c>
+      <c r="Z40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41">
+        <v>0.39</v>
+      </c>
+      <c r="B41">
+        <v>0.1092836080395489</v>
+      </c>
+      <c r="C41">
+        <v>66.51543407958296</v>
+      </c>
+      <c r="D41">
+        <v>123.487434079583</v>
+      </c>
+      <c r="E41">
+        <v>11.50299999999999</v>
+      </c>
+      <c r="F41">
+        <v>57.60299999999999</v>
+      </c>
+      <c r="G41">
+        <v>0.631</v>
+      </c>
+      <c r="H41">
+        <v>101.6</v>
+      </c>
+      <c r="I41">
+        <v>0</v>
+      </c>
+      <c r="J41">
+        <v>11.825</v>
+      </c>
+      <c r="K41">
+        <v>3.460000000000001</v>
+      </c>
+      <c r="L41">
+        <v>8.365</v>
+      </c>
+      <c r="M41">
+        <v>5.2533936</v>
+      </c>
+      <c r="N41">
+        <v>3.1116064</v>
+      </c>
+      <c r="O41">
+        <v>0.6223212800000001</v>
+      </c>
+      <c r="P41">
+        <v>2.48928512</v>
+      </c>
+      <c r="Q41">
+        <v>5.949285120000001</v>
+      </c>
+      <c r="R41">
+        <v>0.639344262295082</v>
+      </c>
+      <c r="S41">
+        <v>0.13250689842549</v>
+      </c>
+      <c r="T41">
+        <v>1.664020907507457</v>
+      </c>
+      <c r="U41">
+        <v>0.0912</v>
+      </c>
+      <c r="V41">
+        <v>0.2</v>
+      </c>
+      <c r="W41">
+        <v>0.07296000000000001</v>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y41">
+        <v>1.592304067983789</v>
+      </c>
+      <c r="Z41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42">
+        <v>0.4</v>
+      </c>
+      <c r="B42">
+        <v>0.1095012140958623</v>
+      </c>
+      <c r="C42">
+        <v>64.65836120703118</v>
+      </c>
+      <c r="D42">
+        <v>123.1073612070312</v>
+      </c>
+      <c r="E42">
+        <v>12.98</v>
+      </c>
+      <c r="F42">
+        <v>59.08</v>
+      </c>
+      <c r="G42">
+        <v>0.631</v>
+      </c>
+      <c r="H42">
+        <v>101.6</v>
+      </c>
+      <c r="I42">
+        <v>0</v>
+      </c>
+      <c r="J42">
+        <v>11.825</v>
+      </c>
+      <c r="K42">
+        <v>3.460000000000001</v>
+      </c>
+      <c r="L42">
+        <v>8.365</v>
+      </c>
+      <c r="M42">
+        <v>5.388096</v>
+      </c>
+      <c r="N42">
+        <v>2.976904</v>
+      </c>
+      <c r="O42">
+        <v>0.5953808</v>
+      </c>
+      <c r="P42">
+        <v>2.3815232</v>
+      </c>
+      <c r="Q42">
+        <v>5.841523200000001</v>
+      </c>
+      <c r="R42">
+        <v>0.6666666666666667</v>
+      </c>
+      <c r="S42">
+        <v>0.1338620234931038</v>
+      </c>
+      <c r="T42">
+        <v>1.68808483964784</v>
+      </c>
+      <c r="U42">
+        <v>0.0912</v>
+      </c>
+      <c r="V42">
+        <v>0.2</v>
+      </c>
+      <c r="W42">
+        <v>0.07296000000000001</v>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y42">
+        <v>1.552496466284194</v>
+      </c>
+      <c r="Z42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43">
+        <v>0.41</v>
+      </c>
+      <c r="B43">
+        <v>0.1097188201521756</v>
+      </c>
+      <c r="C43">
+        <v>62.80362075227006</v>
+      </c>
+      <c r="D43">
+        <v>122.7296207522701</v>
+      </c>
+      <c r="E43">
+        <v>14.457</v>
+      </c>
+      <c r="F43">
+        <v>60.557</v>
+      </c>
+      <c r="G43">
+        <v>0.631</v>
+      </c>
+      <c r="H43">
+        <v>101.6</v>
+      </c>
+      <c r="I43">
+        <v>0</v>
+      </c>
+      <c r="J43">
+        <v>11.825</v>
+      </c>
+      <c r="K43">
+        <v>3.460000000000001</v>
+      </c>
+      <c r="L43">
+        <v>8.365</v>
+      </c>
+      <c r="M43">
+        <v>5.5227984</v>
+      </c>
+      <c r="N43">
+        <v>2.8422016</v>
+      </c>
+      <c r="O43">
+        <v>0.56844032</v>
+      </c>
+      <c r="P43">
+        <v>2.27376128</v>
+      </c>
+      <c r="Q43">
+        <v>5.733761280000001</v>
+      </c>
+      <c r="R43">
+        <v>0.6949152542372882</v>
+      </c>
+      <c r="S43">
+        <v>0.1352630850036874</v>
+      </c>
+      <c r="T43">
+        <v>1.712964498301456</v>
+      </c>
+      <c r="U43">
+        <v>0.0912</v>
+      </c>
+      <c r="V43">
+        <v>0.2</v>
+      </c>
+      <c r="W43">
+        <v>0.07296000000000001</v>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y43">
+        <v>1.514630698813848</v>
+      </c>
+      <c r="Z43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44">
+        <v>0.42</v>
+      </c>
+      <c r="B44">
+        <v>0.1344616627240233</v>
+      </c>
+      <c r="C44">
+        <v>29.58266399148717</v>
+      </c>
+      <c r="D44">
+        <v>90.98566399148716</v>
+      </c>
+      <c r="E44">
+        <v>15.93399999999999</v>
+      </c>
+      <c r="F44">
+        <v>62.03399999999999</v>
+      </c>
+      <c r="G44">
+        <v>0.631</v>
+      </c>
+      <c r="H44">
+        <v>101.6</v>
+      </c>
+      <c r="I44">
+        <v>0</v>
+      </c>
+      <c r="J44">
+        <v>11.825</v>
+      </c>
+      <c r="K44">
+        <v>3.460000000000001</v>
+      </c>
+      <c r="L44">
+        <v>8.365</v>
+      </c>
+      <c r="M44">
+        <v>9.7145244</v>
+      </c>
+      <c r="N44">
+        <v>-1.3495244</v>
+      </c>
+      <c r="O44">
+        <v>-0.26990488</v>
+      </c>
+      <c r="P44">
+        <v>-1.07961952</v>
+      </c>
+      <c r="Q44">
+        <v>2.380380480000001</v>
+      </c>
+      <c r="R44">
+        <v>0.7241379310344827</v>
+      </c>
+      <c r="S44">
+        <v>0.137959787831091</v>
+      </c>
+      <c r="T44">
+        <v>1.760851793276885</v>
+      </c>
+      <c r="U44">
+        <v>0.1566</v>
+      </c>
+      <c r="V44">
+        <v>0.1722163567781043</v>
+      </c>
+      <c r="W44">
+        <v>0.1296309185285489</v>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y44">
+        <v>0.8610817838905217</v>
+      </c>
+      <c r="Z44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45">
+        <v>0.43</v>
+      </c>
+      <c r="B45">
+        <v>0.1356396627240233</v>
+      </c>
+      <c r="C45">
+        <v>26.9988745916994</v>
+      </c>
+      <c r="D45">
+        <v>89.8788745916994</v>
+      </c>
+      <c r="E45">
+        <v>17.41099999999999</v>
+      </c>
+      <c r="F45">
+        <v>63.511</v>
+      </c>
+      <c r="G45">
+        <v>0.631</v>
+      </c>
+      <c r="H45">
+        <v>101.6</v>
+      </c>
+      <c r="I45">
+        <v>0</v>
+      </c>
+      <c r="J45">
+        <v>11.825</v>
+      </c>
+      <c r="K45">
+        <v>3.460000000000001</v>
+      </c>
+      <c r="L45">
+        <v>8.365</v>
+      </c>
+      <c r="M45">
+        <v>9.9458226</v>
+      </c>
+      <c r="N45">
+        <v>-1.580822599999999</v>
+      </c>
+      <c r="O45">
+        <v>-0.3161645199999999</v>
+      </c>
+      <c r="P45">
+        <v>-1.26465808</v>
+      </c>
+      <c r="Q45">
+        <v>2.195341920000002</v>
+      </c>
+      <c r="R45">
+        <v>0.7543859649122806</v>
+      </c>
+      <c r="S45">
+        <v>0.1396994332316365</v>
+      </c>
+      <c r="T45">
+        <v>1.79174393000104</v>
+      </c>
+      <c r="U45">
+        <v>0.1566</v>
+      </c>
+      <c r="V45">
+        <v>0.1682113252251252</v>
+      </c>
+      <c r="W45">
+        <v>0.1302581064697454</v>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y45">
+        <v>0.8410566261256259</v>
+      </c>
+      <c r="Z45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46">
+        <v>0.44</v>
+      </c>
+      <c r="B46">
+        <v>0.1368176627240233</v>
+      </c>
+      <c r="C46">
+        <v>24.4416885178167</v>
+      </c>
+      <c r="D46">
+        <v>88.7986885178167</v>
+      </c>
+      <c r="E46">
+        <v>18.888</v>
+      </c>
+      <c r="F46">
+        <v>64.988</v>
+      </c>
+      <c r="G46">
+        <v>0.631</v>
+      </c>
+      <c r="H46">
+        <v>101.6</v>
+      </c>
+      <c r="I46">
+        <v>0</v>
+      </c>
+      <c r="J46">
+        <v>11.825</v>
+      </c>
+      <c r="K46">
+        <v>3.460000000000001</v>
+      </c>
+      <c r="L46">
+        <v>8.365</v>
+      </c>
+      <c r="M46">
+        <v>10.1771208</v>
+      </c>
+      <c r="N46">
+        <v>-1.812120800000001</v>
+      </c>
+      <c r="O46">
+        <v>-0.3624241600000002</v>
+      </c>
+      <c r="P46">
+        <v>-1.44969664</v>
+      </c>
+      <c r="Q46">
+        <v>2.01030336</v>
+      </c>
+      <c r="R46">
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="S46">
+        <v>0.1415012088250585</v>
+      </c>
+      <c r="T46">
+        <v>1.823739357322488</v>
+      </c>
+      <c r="U46">
+        <v>0.1566</v>
+      </c>
+      <c r="V46">
+        <v>0.1643883405609178</v>
+      </c>
+      <c r="W46">
+        <v>0.1308567858681603</v>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y46">
+        <v>0.8219417028045888</v>
+      </c>
+      <c r="Z46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47">
+        <v>0.45</v>
+      </c>
+      <c r="B47">
+        <v>0.1379956627240233</v>
+      </c>
+      <c r="C47">
+        <v>21.91015798491412</v>
+      </c>
+      <c r="D47">
+        <v>87.74415798491412</v>
+      </c>
+      <c r="E47">
+        <v>20.365</v>
+      </c>
+      <c r="F47">
+        <v>66.465</v>
+      </c>
+      <c r="G47">
+        <v>0.631</v>
+      </c>
+      <c r="H47">
+        <v>101.6</v>
+      </c>
+      <c r="I47">
+        <v>0</v>
+      </c>
+      <c r="J47">
+        <v>11.825</v>
+      </c>
+      <c r="K47">
+        <v>3.460000000000001</v>
+      </c>
+      <c r="L47">
+        <v>8.365</v>
+      </c>
+      <c r="M47">
+        <v>10.408419</v>
+      </c>
+      <c r="N47">
+        <v>-2.043419000000002</v>
+      </c>
+      <c r="O47">
+        <v>-0.4086838000000004</v>
+      </c>
+      <c r="P47">
+        <v>-1.634735200000001</v>
+      </c>
+      <c r="Q47">
+        <v>1.825264799999999</v>
+      </c>
+      <c r="R47">
+        <v>0.8181818181818181</v>
+      </c>
+      <c r="S47">
+        <v>0.1433685035309687</v>
+      </c>
+      <c r="T47">
+        <v>1.856898254728351</v>
+      </c>
+      <c r="U47">
+        <v>0.1566</v>
+      </c>
+      <c r="V47">
+        <v>0.1607352663262307</v>
+      </c>
+      <c r="W47">
+        <v>0.1314288572933123</v>
+      </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y47">
+        <v>0.8036763316311535</v>
+      </c>
+      <c r="Z47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48">
+        <v>0.46</v>
+      </c>
+      <c r="B48">
+        <v>0.1643067364493472</v>
+      </c>
+      <c r="C48">
+        <v>2.038583518074418</v>
+      </c>
+      <c r="D48">
+        <v>69.34958351807441</v>
+      </c>
+      <c r="E48">
+        <v>21.84199999999999</v>
+      </c>
+      <c r="F48">
+        <v>67.94199999999999</v>
+      </c>
+      <c r="G48">
+        <v>0.631</v>
+      </c>
+      <c r="H48">
+        <v>101.6</v>
+      </c>
+      <c r="I48">
+        <v>0</v>
+      </c>
+      <c r="J48">
+        <v>11.825</v>
+      </c>
+      <c r="K48">
+        <v>3.460000000000001</v>
+      </c>
+      <c r="L48">
+        <v>8.365</v>
+      </c>
+      <c r="M48">
+        <v>14.1862896</v>
+      </c>
+      <c r="N48">
+        <v>-5.8212896</v>
+      </c>
+      <c r="O48">
+        <v>-1.16425792</v>
+      </c>
+      <c r="P48">
+        <v>-4.65703168</v>
+      </c>
+      <c r="Q48">
+        <v>-1.197031679999999</v>
+      </c>
+      <c r="R48">
+        <v>0.8518518518518519</v>
+      </c>
+      <c r="S48">
+        <v>0.1473810197543643</v>
+      </c>
+      <c r="T48">
+        <v>1.92815139616865</v>
+      </c>
+      <c r="U48">
+        <v>0.2088</v>
+      </c>
+      <c r="V48">
+        <v>0.1179307660545715</v>
+      </c>
+      <c r="W48">
+        <v>0.1841760560478055</v>
+      </c>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y48">
+        <v>0.5896538302728573</v>
+      </c>
+      <c r="Z48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49">
+        <v>0.47</v>
+      </c>
+      <c r="B49">
+        <v>0.1660067364493473</v>
+      </c>
+      <c r="C49">
+        <v>-0.3652093175210069</v>
+      </c>
+      <c r="D49">
+        <v>68.42279068247899</v>
+      </c>
+      <c r="E49">
+        <v>23.319</v>
+      </c>
+      <c r="F49">
+        <v>69.419</v>
+      </c>
+      <c r="G49">
+        <v>0.631</v>
+      </c>
+      <c r="H49">
+        <v>101.6</v>
+      </c>
+      <c r="I49">
+        <v>0</v>
+      </c>
+      <c r="J49">
+        <v>11.825</v>
+      </c>
+      <c r="K49">
+        <v>3.460000000000001</v>
+      </c>
+      <c r="L49">
+        <v>8.365</v>
+      </c>
+      <c r="M49">
+        <v>14.4946872</v>
+      </c>
+      <c r="N49">
+        <v>-6.129687199999999</v>
+      </c>
+      <c r="O49">
+        <v>-1.22593744</v>
+      </c>
+      <c r="P49">
+        <v>-4.903749759999999</v>
+      </c>
+      <c r="Q49">
+        <v>-1.443749759999998</v>
+      </c>
+      <c r="R49">
+        <v>0.8867924528301887</v>
+      </c>
+      <c r="S49">
+        <v>0.1494297182402957</v>
+      </c>
+      <c r="T49">
+        <v>1.9645316111907</v>
+      </c>
+      <c r="U49">
+        <v>0.2088</v>
+      </c>
+      <c r="V49">
+        <v>0.1154216008193678</v>
+      </c>
+      <c r="W49">
+        <v>0.184699969748916</v>
+      </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y49">
+        <v>0.577108004096839</v>
+      </c>
+      <c r="Z49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50">
+        <v>0.48</v>
+      </c>
+      <c r="B50">
+        <v>0.1677067364493472</v>
+      </c>
+      <c r="C50">
+        <v>-2.744557382208185</v>
+      </c>
+      <c r="D50">
+        <v>67.5204426177918</v>
+      </c>
+      <c r="E50">
+        <v>24.79599999999999</v>
+      </c>
+      <c r="F50">
+        <v>70.89599999999999</v>
+      </c>
+      <c r="G50">
+        <v>0.631</v>
+      </c>
+      <c r="H50">
+        <v>101.6</v>
+      </c>
+      <c r="I50">
+        <v>0</v>
+      </c>
+      <c r="J50">
+        <v>11.825</v>
+      </c>
+      <c r="K50">
+        <v>3.460000000000001</v>
+      </c>
+      <c r="L50">
+        <v>8.365</v>
+      </c>
+      <c r="M50">
+        <v>14.8030848</v>
+      </c>
+      <c r="N50">
+        <v>-6.438084799999999</v>
+      </c>
+      <c r="O50">
+        <v>-1.28761696</v>
+      </c>
+      <c r="P50">
+        <v>-5.150467839999999</v>
+      </c>
+      <c r="Q50">
+        <v>-1.690467839999998</v>
+      </c>
+      <c r="R50">
+        <v>0.923076923076923</v>
+      </c>
+      <c r="S50">
+        <v>0.1515572128218398</v>
+      </c>
+      <c r="T50">
+        <v>2.002311065252059</v>
+      </c>
+      <c r="U50">
+        <v>0.2088</v>
+      </c>
+      <c r="V50">
+        <v>0.113016984135631</v>
+      </c>
+      <c r="W50">
+        <v>0.1852020537124802</v>
+      </c>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y50">
+        <v>0.565084920678155</v>
+      </c>
+      <c r="Z50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51">
+        <v>0.49</v>
+      </c>
+      <c r="B51">
+        <v>0.1694067364493472</v>
+      </c>
+      <c r="C51">
+        <v>-5.100415208157798</v>
+      </c>
+      <c r="D51">
+        <v>66.64158479184219</v>
+      </c>
+      <c r="E51">
+        <v>26.27299999999999</v>
+      </c>
+      <c r="F51">
+        <v>72.37299999999999</v>
+      </c>
+      <c r="G51">
+        <v>0.631</v>
+      </c>
+      <c r="H51">
+        <v>101.6</v>
+      </c>
+      <c r="I51">
+        <v>0</v>
+      </c>
+      <c r="J51">
+        <v>11.825</v>
+      </c>
+      <c r="K51">
+        <v>3.460000000000001</v>
+      </c>
+      <c r="L51">
+        <v>8.365</v>
+      </c>
+      <c r="M51">
+        <v>15.1114824</v>
+      </c>
+      <c r="N51">
+        <v>-6.746482399999998</v>
+      </c>
+      <c r="O51">
+        <v>-1.34929648</v>
+      </c>
+      <c r="P51">
+        <v>-5.397185919999998</v>
+      </c>
+      <c r="Q51">
+        <v>-1.937185919999997</v>
+      </c>
+      <c r="R51">
+        <v>0.9607843137254901</v>
+      </c>
+      <c r="S51">
+        <v>0.1537681385634445</v>
+      </c>
+      <c r="T51">
+        <v>2.041572066531511</v>
+      </c>
+      <c r="U51">
+        <v>0.2088</v>
+      </c>
+      <c r="V51">
+        <v>0.1107105150716385</v>
+      </c>
+      <c r="W51">
+        <v>0.1856836444530419</v>
+      </c>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y51">
+        <v>0.5535525753581927</v>
+      </c>
+      <c r="Z51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52">
+        <v>0.5</v>
+      </c>
+      <c r="B52">
+        <v>0.1711067364493473</v>
+      </c>
+      <c r="C52">
+        <v>-7.433688268672043</v>
+      </c>
+      <c r="D52">
+        <v>65.78531173132795</v>
+      </c>
+      <c r="E52">
+        <v>27.74999999999999</v>
+      </c>
+      <c r="F52">
+        <v>73.84999999999999</v>
+      </c>
+      <c r="G52">
+        <v>0.631</v>
+      </c>
+      <c r="H52">
+        <v>101.6</v>
+      </c>
+      <c r="I52">
+        <v>0</v>
+      </c>
+      <c r="J52">
+        <v>11.825</v>
+      </c>
+      <c r="K52">
+        <v>3.460000000000001</v>
+      </c>
+      <c r="L52">
+        <v>8.365</v>
+      </c>
+      <c r="M52">
+        <v>15.41988</v>
+      </c>
+      <c r="N52">
+        <v>-7.054879999999999</v>
+      </c>
+      <c r="O52">
+        <v>-1.410976</v>
+      </c>
+      <c r="P52">
+        <v>-5.643903999999999</v>
+      </c>
+      <c r="Q52">
+        <v>-2.183903999999998</v>
+      </c>
+      <c r="R52">
+        <v>1</v>
+      </c>
+      <c r="S52">
+        <v>0.1560675013347134</v>
+      </c>
+      <c r="T52">
+        <v>2.082403507862142</v>
+      </c>
+      <c r="U52">
+        <v>0.2088</v>
+      </c>
+      <c r="V52">
+        <v>0.1084963047702058</v>
+      </c>
+      <c r="W52">
+        <v>0.186145971563981</v>
+      </c>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y52">
+        <v>0.5424815238510288</v>
+      </c>
+      <c r="Z52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53">
+        <v>0.51</v>
+      </c>
+      <c r="B53">
+        <v>0.1728067364493472</v>
+      </c>
+      <c r="C53">
+        <v>-9.745236089971527</v>
+      </c>
+      <c r="D53">
+        <v>64.95076391002847</v>
+      </c>
+      <c r="E53">
+        <v>29.227</v>
+      </c>
+      <c r="F53">
+        <v>75.327</v>
+      </c>
+      <c r="G53">
+        <v>0.631</v>
+      </c>
+      <c r="H53">
+        <v>101.6</v>
+      </c>
+      <c r="I53">
+        <v>0</v>
+      </c>
+      <c r="J53">
+        <v>11.825</v>
+      </c>
+      <c r="K53">
+        <v>3.460000000000001</v>
+      </c>
+      <c r="L53">
+        <v>8.365</v>
+      </c>
+      <c r="M53">
+        <v>15.7282776</v>
+      </c>
+      <c r="N53">
+        <v>-7.3632776</v>
+      </c>
+      <c r="O53">
+        <v>-1.47265552</v>
+      </c>
+      <c r="P53">
+        <v>-5.89062208</v>
+      </c>
+      <c r="Q53">
+        <v>-2.430622079999999</v>
+      </c>
+      <c r="R53">
+        <v>1.040816326530612</v>
+      </c>
+      <c r="S53">
+        <v>0.1584607156476668</v>
+      </c>
+      <c r="T53">
+        <v>2.124901538634838</v>
+      </c>
+      <c r="U53">
+        <v>0.2088</v>
+      </c>
+      <c r="V53">
+        <v>0.1063689262452998</v>
+      </c>
+      <c r="W53">
+        <v>0.1865901681999814</v>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y53">
+        <v>0.5318446312264987</v>
+      </c>
+      <c r="Z53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54">
+        <v>0.52</v>
+      </c>
+      <c r="B54">
+        <v>0.1745067364493472</v>
+      </c>
+      <c r="C54">
+        <v>-12.03587512909368</v>
+      </c>
+      <c r="D54">
+        <v>64.13712487090632</v>
+      </c>
+      <c r="E54">
+        <v>30.704</v>
+      </c>
+      <c r="F54">
+        <v>76.804</v>
+      </c>
+      <c r="G54">
+        <v>0.631</v>
+      </c>
+      <c r="H54">
+        <v>101.6</v>
+      </c>
+      <c r="I54">
+        <v>0</v>
+      </c>
+      <c r="J54">
+        <v>11.825</v>
+      </c>
+      <c r="K54">
+        <v>3.460000000000001</v>
+      </c>
+      <c r="L54">
+        <v>8.365</v>
+      </c>
+      <c r="M54">
+        <v>16.0366752</v>
+      </c>
+      <c r="N54">
+        <v>-7.671675200000001</v>
+      </c>
+      <c r="O54">
+        <v>-1.53433504</v>
+      </c>
+      <c r="P54">
+        <v>-6.137340160000001</v>
+      </c>
+      <c r="Q54">
+        <v>-2.67734016</v>
+      </c>
+      <c r="R54">
+        <v>1.083333333333333</v>
+      </c>
+      <c r="S54">
+        <v>0.1609536472236598</v>
+      </c>
+      <c r="T54">
+        <v>2.169170320689731</v>
+      </c>
+      <c r="U54">
+        <v>0.2088</v>
+      </c>
+      <c r="V54">
+        <v>0.1043233699713517</v>
+      </c>
+      <c r="W54">
+        <v>0.1870172803499818</v>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y54">
+        <v>0.5216168498567584</v>
+      </c>
+      <c r="Z54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55">
+        <v>0.53</v>
+      </c>
+      <c r="B55">
+        <v>0.1762067364493473</v>
+      </c>
+      <c r="C55">
+        <v>-14.30638143815833</v>
+      </c>
+      <c r="D55">
+        <v>63.34361856184167</v>
+      </c>
+      <c r="E55">
+        <v>32.18099999999999</v>
+      </c>
+      <c r="F55">
+        <v>78.28099999999999</v>
+      </c>
+      <c r="G55">
+        <v>0.631</v>
+      </c>
+      <c r="H55">
+        <v>101.6</v>
+      </c>
+      <c r="I55">
+        <v>0</v>
+      </c>
+      <c r="J55">
+        <v>11.825</v>
+      </c>
+      <c r="K55">
+        <v>3.460000000000001</v>
+      </c>
+      <c r="L55">
+        <v>8.365</v>
+      </c>
+      <c r="M55">
+        <v>16.3450728</v>
+      </c>
+      <c r="N55">
+        <v>-7.9800728</v>
+      </c>
+      <c r="O55">
+        <v>-1.59601456</v>
+      </c>
+      <c r="P55">
+        <v>-6.38405824</v>
+      </c>
+      <c r="Q55">
+        <v>-2.924058239999999</v>
+      </c>
+      <c r="R55">
+        <v>1.127659574468085</v>
+      </c>
+      <c r="S55">
+        <v>0.163552660994376</v>
+      </c>
+      <c r="T55">
+        <v>2.215322880704406</v>
+      </c>
+      <c r="U55">
+        <v>0.2088</v>
+      </c>
+      <c r="V55">
+        <v>0.1023550045001941</v>
+      </c>
+      <c r="W55">
+        <v>0.1874282750603595</v>
+      </c>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y55">
+        <v>0.5117750225009705</v>
+      </c>
+      <c r="Z55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56">
+        <v>0.54</v>
+      </c>
+      <c r="B56">
+        <v>0.1779067364493473</v>
+      </c>
+      <c r="C56">
+        <v>-16.55749313327628</v>
+      </c>
+      <c r="D56">
+        <v>62.56950686672371</v>
+      </c>
+      <c r="E56">
+        <v>33.65799999999999</v>
+      </c>
+      <c r="F56">
+        <v>79.758</v>
+      </c>
+      <c r="G56">
+        <v>0.631</v>
+      </c>
+      <c r="H56">
+        <v>101.6</v>
+      </c>
+      <c r="I56">
+        <v>0</v>
+      </c>
+      <c r="J56">
+        <v>11.825</v>
+      </c>
+      <c r="K56">
+        <v>3.460000000000001</v>
+      </c>
+      <c r="L56">
+        <v>8.365</v>
+      </c>
+      <c r="M56">
+        <v>16.6534704</v>
+      </c>
+      <c r="N56">
+        <v>-8.2884704</v>
+      </c>
+      <c r="O56">
+        <v>-1.65769408</v>
+      </c>
+      <c r="P56">
+        <v>-6.63077632</v>
+      </c>
+      <c r="Q56">
+        <v>-3.170776319999999</v>
+      </c>
+      <c r="R56">
+        <v>1.173913043478261</v>
+      </c>
+      <c r="S56">
+        <v>0.166264675363819</v>
+      </c>
+      <c r="T56">
+        <v>2.263482073763198</v>
+      </c>
+      <c r="U56">
+        <v>0.2088</v>
+      </c>
+      <c r="V56">
+        <v>0.1004595414538942</v>
+      </c>
+      <c r="W56">
+        <v>0.1878240477444269</v>
+      </c>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y56">
+        <v>0.502297707269471</v>
+      </c>
+      <c r="Z56">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57">
+        <v>0.55</v>
+      </c>
+      <c r="B57">
+        <v>0.1965292516724593</v>
+      </c>
+      <c r="C57">
+        <v>-25.4218457122883</v>
+      </c>
+      <c r="D57">
+        <v>55.1821542877117</v>
+      </c>
+      <c r="E57">
+        <v>35.135</v>
+      </c>
+      <c r="F57">
+        <v>81.235</v>
+      </c>
+      <c r="G57">
+        <v>0.631</v>
+      </c>
+      <c r="H57">
+        <v>101.6</v>
+      </c>
+      <c r="I57">
+        <v>0</v>
+      </c>
+      <c r="J57">
+        <v>11.825</v>
+      </c>
+      <c r="K57">
+        <v>3.460000000000001</v>
+      </c>
+      <c r="L57">
+        <v>8.365</v>
+      </c>
+      <c r="M57">
+        <v>19.398918</v>
+      </c>
+      <c r="N57">
+        <v>-11.033918</v>
+      </c>
+      <c r="O57">
+        <v>-2.206783600000001</v>
+      </c>
+      <c r="P57">
+        <v>-8.827134400000002</v>
+      </c>
+      <c r="Q57">
+        <v>-5.367134400000001</v>
+      </c>
+      <c r="R57">
+        <v>1.222222222222223</v>
+      </c>
+      <c r="S57">
+        <v>0.170036146423264</v>
+      </c>
+      <c r="T57">
+        <v>2.330454802563585</v>
+      </c>
+      <c r="U57">
+        <v>0.2388</v>
+      </c>
+      <c r="V57">
+        <v>0.08624192338974782</v>
+      </c>
+      <c r="W57">
+        <v>0.2182054286945282</v>
+      </c>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y57">
+        <v>0.431209616948739</v>
+      </c>
+      <c r="Z57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="B58">
+        <v>0.1985292516724593</v>
+      </c>
+      <c r="C58">
+        <v>-27.58979184406969</v>
+      </c>
+      <c r="D58">
+        <v>54.49120815593032</v>
+      </c>
+      <c r="E58">
+        <v>36.612</v>
+      </c>
+      <c r="F58">
+        <v>82.712</v>
+      </c>
+      <c r="G58">
+        <v>0.631</v>
+      </c>
+      <c r="H58">
+        <v>101.6</v>
+      </c>
+      <c r="I58">
+        <v>0</v>
+      </c>
+      <c r="J58">
+        <v>11.825</v>
+      </c>
+      <c r="K58">
+        <v>3.460000000000001</v>
+      </c>
+      <c r="L58">
+        <v>8.365</v>
+      </c>
+      <c r="M58">
+        <v>19.7516256</v>
+      </c>
+      <c r="N58">
+        <v>-11.3866256</v>
+      </c>
+      <c r="O58">
+        <v>-2.27732512</v>
+      </c>
+      <c r="P58">
+        <v>-9.10930048</v>
+      </c>
+      <c r="Q58">
+        <v>-5.649300479999999</v>
+      </c>
+      <c r="R58">
+        <v>1.272727272727273</v>
+      </c>
+      <c r="S58">
+        <v>0.1730187861147017</v>
+      </c>
+      <c r="T58">
+        <v>2.383419684440029</v>
+      </c>
+      <c r="U58">
+        <v>0.2388</v>
+      </c>
+      <c r="V58">
+        <v>0.08470188904350233</v>
+      </c>
+      <c r="W58">
+        <v>0.2185731888964117</v>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y58">
+        <v>0.4235094452175117</v>
+      </c>
+      <c r="Z58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59">
+        <v>0.5700000000000001</v>
+      </c>
+      <c r="B59">
+        <v>0.2005292516724593</v>
+      </c>
+      <c r="C59">
+        <v>-29.7406490169983</v>
+      </c>
+      <c r="D59">
+        <v>53.81735098300171</v>
+      </c>
+      <c r="E59">
+        <v>38.08900000000001</v>
+      </c>
+      <c r="F59">
+        <v>84.18900000000001</v>
+      </c>
+      <c r="G59">
+        <v>0.631</v>
+      </c>
+      <c r="H59">
+        <v>101.6</v>
+      </c>
+      <c r="I59">
+        <v>0</v>
+      </c>
+      <c r="J59">
+        <v>11.825</v>
+      </c>
+      <c r="K59">
+        <v>3.460000000000001</v>
+      </c>
+      <c r="L59">
+        <v>8.365</v>
+      </c>
+      <c r="M59">
+        <v>20.1043332</v>
+      </c>
+      <c r="N59">
+        <v>-11.7393332</v>
+      </c>
+      <c r="O59">
+        <v>-2.347866640000001</v>
+      </c>
+      <c r="P59">
+        <v>-9.391466560000001</v>
+      </c>
+      <c r="Q59">
+        <v>-5.93146656</v>
+      </c>
+      <c r="R59">
+        <v>1.325581395348838</v>
+      </c>
+      <c r="S59">
+        <v>0.1761401532336483</v>
+      </c>
+      <c r="T59">
+        <v>2.438848049194449</v>
+      </c>
+      <c r="U59">
+        <v>0.2388</v>
+      </c>
+      <c r="V59">
+        <v>0.08321589099010754</v>
+      </c>
+      <c r="W59">
+        <v>0.2189280452315623</v>
+      </c>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y59">
+        <v>0.4160794549505377</v>
+      </c>
+      <c r="Z59">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60">
+        <v>0.58</v>
+      </c>
+      <c r="B60">
+        <v>0.2025292516724593</v>
+      </c>
+      <c r="C60">
+        <v>-31.8750434707476</v>
+      </c>
+      <c r="D60">
+        <v>53.15995652925238</v>
+      </c>
+      <c r="E60">
+        <v>39.56599999999998</v>
+      </c>
+      <c r="F60">
+        <v>85.66599999999998</v>
+      </c>
+      <c r="G60">
+        <v>0.631</v>
+      </c>
+      <c r="H60">
+        <v>101.6</v>
+      </c>
+      <c r="I60">
+        <v>0</v>
+      </c>
+      <c r="J60">
+        <v>11.825</v>
+      </c>
+      <c r="K60">
+        <v>3.460000000000001</v>
+      </c>
+      <c r="L60">
+        <v>8.365</v>
+      </c>
+      <c r="M60">
+        <v>20.4570408</v>
+      </c>
+      <c r="N60">
+        <v>-12.0920408</v>
+      </c>
+      <c r="O60">
+        <v>-2.41840816</v>
+      </c>
+      <c r="P60">
+        <v>-9.673632639999997</v>
+      </c>
+      <c r="Q60">
+        <v>-6.213632639999997</v>
+      </c>
+      <c r="R60">
+        <v>1.380952380952381</v>
+      </c>
+      <c r="S60">
+        <v>0.1794101568820684</v>
+      </c>
+      <c r="T60">
+        <v>2.496915859889554</v>
+      </c>
+      <c r="U60">
+        <v>0.2388</v>
+      </c>
+      <c r="V60">
+        <v>0.08178113424889881</v>
+      </c>
+      <c r="W60">
+        <v>0.219270665141363</v>
+      </c>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y60">
+        <v>0.4089056712444941</v>
+      </c>
+      <c r="Z60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61">
+        <v>0.59</v>
+      </c>
+      <c r="B61">
+        <v>0.2045292516724593</v>
+      </c>
+      <c r="C61">
+        <v>-33.99357121546119</v>
+      </c>
+      <c r="D61">
+        <v>52.5184287845388</v>
+      </c>
+      <c r="E61">
+        <v>41.04299999999999</v>
+      </c>
+      <c r="F61">
+        <v>87.14299999999999</v>
+      </c>
+      <c r="G61">
+        <v>0.631</v>
+      </c>
+      <c r="H61">
+        <v>101.6</v>
+      </c>
+      <c r="I61">
+        <v>0</v>
+      </c>
+      <c r="J61">
+        <v>11.825</v>
+      </c>
+      <c r="K61">
+        <v>3.460000000000001</v>
+      </c>
+      <c r="L61">
+        <v>8.365</v>
+      </c>
+      <c r="M61">
+        <v>20.8097484</v>
+      </c>
+      <c r="N61">
+        <v>-12.4447484</v>
+      </c>
+      <c r="O61">
+        <v>-2.488949679999999</v>
+      </c>
+      <c r="P61">
+        <v>-9.955798719999997</v>
+      </c>
+      <c r="Q61">
+        <v>-6.495798719999996</v>
+      </c>
+      <c r="R61">
+        <v>1.439024390243902</v>
+      </c>
+      <c r="S61">
+        <v>0.1828396729035823</v>
+      </c>
+      <c r="T61">
+        <v>2.557816246716128</v>
+      </c>
+      <c r="U61">
+        <v>0.2388</v>
+      </c>
+      <c r="V61">
+        <v>0.08039501332942595</v>
+      </c>
+      <c r="W61">
+        <v>0.2196016708169331</v>
+      </c>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y61">
+        <v>0.4019750666471298</v>
+      </c>
+      <c r="Z61">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62">
+        <v>0.6</v>
+      </c>
+      <c r="B62">
+        <v>0.2065292516724593</v>
+      </c>
+      <c r="C62">
+        <v>-36.0967998340339</v>
+      </c>
+      <c r="D62">
+        <v>51.89220016596609</v>
+      </c>
+      <c r="E62">
+        <v>42.51999999999999</v>
+      </c>
+      <c r="F62">
+        <v>88.61999999999999</v>
+      </c>
+      <c r="G62">
+        <v>0.631</v>
+      </c>
+      <c r="H62">
+        <v>101.6</v>
+      </c>
+      <c r="I62">
+        <v>0</v>
+      </c>
+      <c r="J62">
+        <v>11.825</v>
+      </c>
+      <c r="K62">
+        <v>3.460000000000001</v>
+      </c>
+      <c r="L62">
+        <v>8.365</v>
+      </c>
+      <c r="M62">
+        <v>21.162456</v>
+      </c>
+      <c r="N62">
+        <v>-12.797456</v>
+      </c>
+      <c r="O62">
+        <v>-2.5594912</v>
+      </c>
+      <c r="P62">
+        <v>-10.2379648</v>
+      </c>
+      <c r="Q62">
+        <v>-6.777964799999998</v>
+      </c>
+      <c r="R62">
+        <v>1.5</v>
+      </c>
+      <c r="S62">
+        <v>0.1864406647261719</v>
+      </c>
+      <c r="T62">
+        <v>2.621761652884032</v>
+      </c>
+      <c r="U62">
+        <v>0.2388</v>
+      </c>
+      <c r="V62">
+        <v>0.07905509644060218</v>
+      </c>
+      <c r="W62">
+        <v>0.2199216429699842</v>
+      </c>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y62">
+        <v>0.3952754822030109</v>
+      </c>
+      <c r="Z62">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63">
+        <v>0.61</v>
+      </c>
+      <c r="B63">
+        <v>0.2085292516724593</v>
+      </c>
+      <c r="C63">
+        <v>-38.18527015697043</v>
+      </c>
+      <c r="D63">
+        <v>51.28072984302956</v>
+      </c>
+      <c r="E63">
+        <v>43.99699999999999</v>
+      </c>
+      <c r="F63">
+        <v>90.09699999999999</v>
+      </c>
+      <c r="G63">
+        <v>0.631</v>
+      </c>
+      <c r="H63">
+        <v>101.6</v>
+      </c>
+      <c r="I63">
+        <v>0</v>
+      </c>
+      <c r="J63">
+        <v>11.825</v>
+      </c>
+      <c r="K63">
+        <v>3.460000000000001</v>
+      </c>
+      <c r="L63">
+        <v>8.365</v>
+      </c>
+      <c r="M63">
+        <v>21.5151636</v>
+      </c>
+      <c r="N63">
+        <v>-13.1501636</v>
+      </c>
+      <c r="O63">
+        <v>-2.63003272</v>
+      </c>
+      <c r="P63">
+        <v>-10.52013088</v>
+      </c>
+      <c r="Q63">
+        <v>-7.060130879999999</v>
+      </c>
+      <c r="R63">
+        <v>1.564102564102564</v>
+      </c>
+      <c r="S63">
+        <v>0.1902263227960737</v>
+      </c>
+      <c r="T63">
+        <v>2.688986310650289</v>
+      </c>
+      <c r="U63">
+        <v>0.2388</v>
+      </c>
+      <c r="V63">
+        <v>0.07775911125305132</v>
+      </c>
+      <c r="W63">
+        <v>0.2202311242327714</v>
+      </c>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y63">
+        <v>0.3887955562652565</v>
+      </c>
+      <c r="Z63">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64">
+        <v>0.62</v>
+      </c>
+      <c r="B64">
+        <v>0.2105292516724593</v>
+      </c>
+      <c r="C64">
+        <v>-40.25949782020904</v>
+      </c>
+      <c r="D64">
+        <v>50.68350217979096</v>
+      </c>
+      <c r="E64">
+        <v>45.474</v>
+      </c>
+      <c r="F64">
+        <v>91.574</v>
+      </c>
+      <c r="G64">
+        <v>0.631</v>
+      </c>
+      <c r="H64">
+        <v>101.6</v>
+      </c>
+      <c r="I64">
+        <v>0</v>
+      </c>
+      <c r="J64">
+        <v>11.825</v>
+      </c>
+      <c r="K64">
+        <v>3.460000000000001</v>
+      </c>
+      <c r="L64">
+        <v>8.365</v>
+      </c>
+      <c r="M64">
+        <v>21.8678712</v>
+      </c>
+      <c r="N64">
+        <v>-13.5028712</v>
+      </c>
+      <c r="O64">
+        <v>-2.70057424</v>
+      </c>
+      <c r="P64">
+        <v>-10.80229696</v>
+      </c>
+      <c r="Q64">
+        <v>-7.342296959999999</v>
+      </c>
+      <c r="R64">
+        <v>1.631578947368421</v>
+      </c>
+      <c r="S64">
+        <v>0.1942112260275494</v>
+      </c>
+      <c r="T64">
+        <v>2.759749108298982</v>
+      </c>
+      <c r="U64">
+        <v>0.2388</v>
+      </c>
+      <c r="V64">
+        <v>0.07650493203929243</v>
+      </c>
+      <c r="W64">
+        <v>0.220530622229017</v>
+      </c>
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y64">
+        <v>0.3825246601964621</v>
+      </c>
+      <c r="Z64">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65">
+        <v>0.63</v>
+      </c>
+      <c r="B65">
+        <v>0.2125292516724593</v>
+      </c>
+      <c r="C65">
+        <v>-42.31997471534178</v>
+      </c>
+      <c r="D65">
+        <v>50.10002528465821</v>
+      </c>
+      <c r="E65">
+        <v>46.95099999999999</v>
+      </c>
+      <c r="F65">
+        <v>93.05099999999999</v>
+      </c>
+      <c r="G65">
+        <v>0.631</v>
+      </c>
+      <c r="H65">
+        <v>101.6</v>
+      </c>
+      <c r="I65">
+        <v>0</v>
+      </c>
+      <c r="J65">
+        <v>11.825</v>
+      </c>
+      <c r="K65">
+        <v>3.460000000000001</v>
+      </c>
+      <c r="L65">
+        <v>8.365</v>
+      </c>
+      <c r="M65">
+        <v>22.2205788</v>
+      </c>
+      <c r="N65">
+        <v>-13.8555788</v>
+      </c>
+      <c r="O65">
+        <v>-2.77111576</v>
+      </c>
+      <c r="P65">
+        <v>-11.08446304</v>
+      </c>
+      <c r="Q65">
+        <v>-7.624463039999998</v>
+      </c>
+      <c r="R65">
+        <v>1.702702702702703</v>
+      </c>
+      <c r="S65">
+        <v>0.1984115294336994</v>
+      </c>
+      <c r="T65">
+        <v>2.834336922036791</v>
+      </c>
+      <c r="U65">
+        <v>0.2388</v>
+      </c>
+      <c r="V65">
+        <v>0.07529056803866874</v>
+      </c>
+      <c r="W65">
+        <v>0.2208206123523659</v>
+      </c>
+      <c r="X65" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y65">
+        <v>0.3764528401933437</v>
+      </c>
+      <c r="Z65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66">
+        <v>0.64</v>
+      </c>
+      <c r="B66">
+        <v>0.2145292516724593</v>
+      </c>
+      <c r="C66">
+        <v>-44.36717034080361</v>
+      </c>
+      <c r="D66">
+        <v>49.52982965919638</v>
+      </c>
+      <c r="E66">
+        <v>48.42799999999999</v>
+      </c>
+      <c r="F66">
+        <v>94.52799999999999</v>
+      </c>
+      <c r="G66">
+        <v>0.631</v>
+      </c>
+      <c r="H66">
+        <v>101.6</v>
+      </c>
+      <c r="I66">
+        <v>0</v>
+      </c>
+      <c r="J66">
+        <v>11.825</v>
+      </c>
+      <c r="K66">
+        <v>3.460000000000001</v>
+      </c>
+      <c r="L66">
+        <v>8.365</v>
+      </c>
+      <c r="M66">
+        <v>22.5732864</v>
+      </c>
+      <c r="N66">
+        <v>-14.2082864</v>
+      </c>
+      <c r="O66">
+        <v>-2.84165728</v>
+      </c>
+      <c r="P66">
+        <v>-11.36662912</v>
+      </c>
+      <c r="Q66">
+        <v>-7.90662912</v>
+      </c>
+      <c r="R66">
+        <v>1.777777777777778</v>
+      </c>
+      <c r="S66">
+        <v>0.2028451830290799</v>
+      </c>
+      <c r="T66">
+        <v>2.91306850320448</v>
+      </c>
+      <c r="U66">
+        <v>0.2388</v>
+      </c>
+      <c r="V66">
+        <v>0.07411415291306454</v>
+      </c>
+      <c r="W66">
+        <v>0.2211015402843602</v>
+      </c>
+      <c r="X66" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y66">
+        <v>0.3705707645653227</v>
+      </c>
+      <c r="Z66">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67">
+        <v>0.65</v>
+      </c>
+      <c r="B67">
+        <v>0.2165292516724593</v>
+      </c>
+      <c r="C67">
+        <v>-46.4015330618314</v>
+      </c>
+      <c r="D67">
+        <v>48.97246693816859</v>
+      </c>
+      <c r="E67">
+        <v>49.90499999999999</v>
+      </c>
+      <c r="F67">
+        <v>96.005</v>
+      </c>
+      <c r="G67">
+        <v>0.631</v>
+      </c>
+      <c r="H67">
+        <v>101.6</v>
+      </c>
+      <c r="I67">
+        <v>0</v>
+      </c>
+      <c r="J67">
+        <v>11.825</v>
+      </c>
+      <c r="K67">
+        <v>3.460000000000001</v>
+      </c>
+      <c r="L67">
+        <v>8.365</v>
+      </c>
+      <c r="M67">
+        <v>22.925994</v>
+      </c>
+      <c r="N67">
+        <v>-14.560994</v>
+      </c>
+      <c r="O67">
+        <v>-2.9121988</v>
+      </c>
+      <c r="P67">
+        <v>-11.6487952</v>
+      </c>
+      <c r="Q67">
+        <v>-8.188795199999998</v>
+      </c>
+      <c r="R67">
+        <v>1.857142857142857</v>
+      </c>
+      <c r="S67">
+        <v>0.2075321882584822</v>
+      </c>
+      <c r="T67">
+        <v>2.996299031867466</v>
+      </c>
+      <c r="U67">
+        <v>0.2388</v>
+      </c>
+      <c r="V67">
+        <v>0.07297393517594046</v>
+      </c>
+      <c r="W67">
+        <v>0.2213738242799854</v>
+      </c>
+      <c r="X67" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y67">
+        <v>0.3648696758797023</v>
+      </c>
+      <c r="Z67">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68">
+        <v>0.66</v>
+      </c>
+      <c r="B68">
+        <v>0.2185292516724593</v>
+      </c>
+      <c r="C68">
+        <v>-48.42349128629913</v>
+      </c>
+      <c r="D68">
+        <v>48.42750871370087</v>
+      </c>
+      <c r="E68">
+        <v>51.382</v>
+      </c>
+      <c r="F68">
+        <v>97.482</v>
+      </c>
+      <c r="G68">
+        <v>0.631</v>
+      </c>
+      <c r="H68">
+        <v>101.6</v>
+      </c>
+      <c r="I68">
+        <v>0</v>
+      </c>
+      <c r="J68">
+        <v>11.825</v>
+      </c>
+      <c r="K68">
+        <v>3.460000000000001</v>
+      </c>
+      <c r="L68">
+        <v>8.365</v>
+      </c>
+      <c r="M68">
+        <v>23.2787016</v>
+      </c>
+      <c r="N68">
+        <v>-14.9137016</v>
+      </c>
+      <c r="O68">
+        <v>-2.98274032</v>
+      </c>
+      <c r="P68">
+        <v>-11.93096128</v>
+      </c>
+      <c r="Q68">
+        <v>-8.470961280000001</v>
+      </c>
+      <c r="R68">
+        <v>1.941176470588236</v>
+      </c>
+      <c r="S68">
+        <v>0.2124948996778493</v>
+      </c>
+      <c r="T68">
+        <v>3.084425473981214</v>
+      </c>
+      <c r="U68">
+        <v>0.2388</v>
+      </c>
+      <c r="V68">
+        <v>0.07186826949145651</v>
+      </c>
+      <c r="W68">
+        <v>0.2216378572454402</v>
+      </c>
+      <c r="X68" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y68">
+        <v>0.3593413474572825</v>
+      </c>
+      <c r="Z68">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69">
+        <v>0.67</v>
+      </c>
+      <c r="B69">
+        <v>0.2205292516724593</v>
+      </c>
+      <c r="C69">
+        <v>-50.43345456291005</v>
+      </c>
+      <c r="D69">
+        <v>47.89454543708995</v>
+      </c>
+      <c r="E69">
+        <v>52.859</v>
+      </c>
+      <c r="F69">
+        <v>98.959</v>
+      </c>
+      <c r="G69">
+        <v>0.631</v>
+      </c>
+      <c r="H69">
+        <v>101.6</v>
+      </c>
+      <c r="I69">
+        <v>0</v>
+      </c>
+      <c r="J69">
+        <v>11.825</v>
+      </c>
+      <c r="K69">
+        <v>3.460000000000001</v>
+      </c>
+      <c r="L69">
+        <v>8.365</v>
+      </c>
+      <c r="M69">
+        <v>23.6314092</v>
+      </c>
+      <c r="N69">
+        <v>-15.2664092</v>
+      </c>
+      <c r="O69">
+        <v>-3.05328184</v>
+      </c>
+      <c r="P69">
+        <v>-12.21312736</v>
+      </c>
+      <c r="Q69">
+        <v>-8.753127359999999</v>
+      </c>
+      <c r="R69">
+        <v>2.030303030303031</v>
+      </c>
+      <c r="S69">
+        <v>0.217758381486269</v>
+      </c>
+      <c r="T69">
+        <v>3.177892912586706</v>
+      </c>
+      <c r="U69">
+        <v>0.2388</v>
+      </c>
+      <c r="V69">
+        <v>0.07079560875277806</v>
+      </c>
+      <c r="W69">
+        <v>0.2218940086298366</v>
+      </c>
+      <c r="X69" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y69">
+        <v>0.3539780437638903</v>
+      </c>
+      <c r="Z69">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70">
+        <v>0.68</v>
+      </c>
+      <c r="B70">
+        <v>0.2225292516724593</v>
+      </c>
+      <c r="C70">
+        <v>-52.4318146076619</v>
+      </c>
+      <c r="D70">
+        <v>47.37318539233809</v>
+      </c>
+      <c r="E70">
+        <v>54.33599999999999</v>
+      </c>
+      <c r="F70">
+        <v>100.436</v>
+      </c>
+      <c r="G70">
+        <v>0.631</v>
+      </c>
+      <c r="H70">
+        <v>101.6</v>
+      </c>
+      <c r="I70">
+        <v>0</v>
+      </c>
+      <c r="J70">
+        <v>11.825</v>
+      </c>
+      <c r="K70">
+        <v>3.460000000000001</v>
+      </c>
+      <c r="L70">
+        <v>8.365</v>
+      </c>
+      <c r="M70">
+        <v>23.9841168</v>
+      </c>
+      <c r="N70">
+        <v>-15.6191168</v>
+      </c>
+      <c r="O70">
+        <v>-3.12382336</v>
+      </c>
+      <c r="P70">
+        <v>-12.49529344</v>
+      </c>
+      <c r="Q70">
+        <v>-9.035293439999998</v>
+      </c>
+      <c r="R70">
+        <v>2.125</v>
+      </c>
+      <c r="S70">
+        <v>0.2233508309077149</v>
+      </c>
+      <c r="T70">
+        <v>3.277202066105041</v>
+      </c>
+      <c r="U70">
+        <v>0.2388</v>
+      </c>
+      <c r="V70">
+        <v>0.06975449685935486</v>
+      </c>
+      <c r="W70">
+        <v>0.2221426261499861</v>
+      </c>
+      <c r="X70" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y70">
+        <v>0.3487724842967743</v>
+      </c>
+      <c r="Z70">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71">
+        <v>0.6900000000000001</v>
+      </c>
+      <c r="B71">
+        <v>0.2245292516724593</v>
+      </c>
+      <c r="C71">
+        <v>-54.4189462639923</v>
+      </c>
+      <c r="D71">
+        <v>46.8630537360077</v>
+      </c>
+      <c r="E71">
+        <v>55.813</v>
+      </c>
+      <c r="F71">
+        <v>101.913</v>
+      </c>
+      <c r="G71">
+        <v>0.631</v>
+      </c>
+      <c r="H71">
+        <v>101.6</v>
+      </c>
+      <c r="I71">
+        <v>0</v>
+      </c>
+      <c r="J71">
+        <v>11.825</v>
+      </c>
+      <c r="K71">
+        <v>3.460000000000001</v>
+      </c>
+      <c r="L71">
+        <v>8.365</v>
+      </c>
+      <c r="M71">
+        <v>24.3368244</v>
+      </c>
+      <c r="N71">
+        <v>-15.9718244</v>
+      </c>
+      <c r="O71">
+        <v>-3.19436488</v>
+      </c>
+      <c r="P71">
+        <v>-12.77745952</v>
+      </c>
+      <c r="Q71">
+        <v>-9.31745952</v>
+      </c>
+      <c r="R71">
+        <v>2.225806451612904</v>
+      </c>
+      <c r="S71">
+        <v>0.2293040835176412</v>
+      </c>
+      <c r="T71">
+        <v>3.382918261785849</v>
+      </c>
+      <c r="U71">
+        <v>0.2388</v>
+      </c>
+      <c r="V71">
+        <v>0.06874356212226276</v>
+      </c>
+      <c r="W71">
+        <v>0.2223840373652037</v>
+      </c>
+      <c r="X71" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y71">
+        <v>0.3437178106113138</v>
+      </c>
+      <c r="Z71">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72">
+        <v>0.7000000000000001</v>
+      </c>
+      <c r="B72">
+        <v>0.2265292516724593</v>
+      </c>
+      <c r="C72">
+        <v>-56.39520840154956</v>
+      </c>
+      <c r="D72">
+        <v>46.36379159845044</v>
+      </c>
+      <c r="E72">
+        <v>57.29</v>
+      </c>
+      <c r="F72">
+        <v>103.39</v>
+      </c>
+      <c r="G72">
+        <v>0.631</v>
+      </c>
+      <c r="H72">
+        <v>101.6</v>
+      </c>
+      <c r="I72">
+        <v>0</v>
+      </c>
+      <c r="J72">
+        <v>11.825</v>
+      </c>
+      <c r="K72">
+        <v>3.460000000000001</v>
+      </c>
+      <c r="L72">
+        <v>8.365</v>
+      </c>
+      <c r="M72">
+        <v>24.689532</v>
+      </c>
+      <c r="N72">
+        <v>-16.324532</v>
+      </c>
+      <c r="O72">
+        <v>-3.2649064</v>
+      </c>
+      <c r="P72">
+        <v>-13.0596256</v>
+      </c>
+      <c r="Q72">
+        <v>-9.599625599999998</v>
+      </c>
+      <c r="R72">
+        <v>2.333333333333334</v>
+      </c>
+      <c r="S72">
+        <v>0.2356542196348959</v>
+      </c>
+      <c r="T72">
+        <v>3.495682203845377</v>
+      </c>
+      <c r="U72">
+        <v>0.2388</v>
+      </c>
+      <c r="V72">
+        <v>0.06776151123480187</v>
+      </c>
+      <c r="W72">
+        <v>0.2226185511171293</v>
+      </c>
+      <c r="X72" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y72">
+        <v>0.3388075561740094</v>
+      </c>
+      <c r="Z72">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73">
+        <v>0.71</v>
+      </c>
+      <c r="B73">
+        <v>0.2285292516724593</v>
+      </c>
+      <c r="C73">
+        <v>-58.36094475811823</v>
+      </c>
+      <c r="D73">
+        <v>45.87505524188176</v>
+      </c>
+      <c r="E73">
+        <v>58.76699999999999</v>
+      </c>
+      <c r="F73">
+        <v>104.867</v>
+      </c>
+      <c r="G73">
+        <v>0.631</v>
+      </c>
+      <c r="H73">
+        <v>101.6</v>
+      </c>
+      <c r="I73">
+        <v>0</v>
+      </c>
+      <c r="J73">
+        <v>11.825</v>
+      </c>
+      <c r="K73">
+        <v>3.460000000000001</v>
+      </c>
+      <c r="L73">
+        <v>8.365</v>
+      </c>
+      <c r="M73">
+        <v>25.0422396</v>
+      </c>
+      <c r="N73">
+        <v>-16.6772396</v>
+      </c>
+      <c r="O73">
+        <v>-3.33544792</v>
+      </c>
+      <c r="P73">
+        <v>-13.34179168</v>
+      </c>
+      <c r="Q73">
+        <v>-9.881791679999999</v>
+      </c>
+      <c r="R73">
+        <v>2.448275862068965</v>
+      </c>
+      <c r="S73">
+        <v>0.2424422961740302</v>
+      </c>
+      <c r="T73">
+        <v>3.616222969495217</v>
+      </c>
+      <c r="U73">
+        <v>0.2388</v>
+      </c>
+      <c r="V73">
+        <v>0.06680712375262156</v>
+      </c>
+      <c r="W73">
+        <v>0.222846458847874</v>
+      </c>
+      <c r="X73" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y73">
+        <v>0.3340356187631077</v>
+      </c>
+      <c r="Z73">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74">
+        <v>0.72</v>
+      </c>
+      <c r="B74">
+        <v>0.2305292516724593</v>
+      </c>
+      <c r="C74">
+        <v>-60.31648472884999</v>
+      </c>
+      <c r="D74">
+        <v>45.39651527115001</v>
+      </c>
+      <c r="E74">
+        <v>60.24399999999999</v>
+      </c>
+      <c r="F74">
+        <v>106.344</v>
+      </c>
+      <c r="G74">
+        <v>0.631</v>
+      </c>
+      <c r="H74">
+        <v>101.6</v>
+      </c>
+      <c r="I74">
+        <v>0</v>
+      </c>
+      <c r="J74">
+        <v>11.825</v>
+      </c>
+      <c r="K74">
+        <v>3.460000000000001</v>
+      </c>
+      <c r="L74">
+        <v>8.365</v>
+      </c>
+      <c r="M74">
+        <v>25.3949472</v>
+      </c>
+      <c r="N74">
+        <v>-17.0299472</v>
+      </c>
+      <c r="O74">
+        <v>-3.405989440000001</v>
+      </c>
+      <c r="P74">
+        <v>-13.62395776</v>
+      </c>
+      <c r="Q74">
+        <v>-10.16395776</v>
+      </c>
+      <c r="R74">
+        <v>2.571428571428571</v>
+      </c>
+      <c r="S74">
+        <v>0.2497152353231027</v>
+      </c>
+      <c r="T74">
+        <v>3.745373789834331</v>
+      </c>
+      <c r="U74">
+        <v>0.2388</v>
+      </c>
+      <c r="V74">
+        <v>0.06587924703383514</v>
+      </c>
+      <c r="W74">
+        <v>0.2230680358083202</v>
+      </c>
+      <c r="X74" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y74">
+        <v>0.3293962351691756</v>
+      </c>
+      <c r="Z74">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75">
+        <v>0.73</v>
+      </c>
+      <c r="B75">
+        <v>0.2325292516724593</v>
+      </c>
+      <c r="C75">
+        <v>-62.26214410660781</v>
+      </c>
+      <c r="D75">
+        <v>44.92785589339217</v>
+      </c>
+      <c r="E75">
+        <v>61.72099999999998</v>
+      </c>
+      <c r="F75">
+        <v>107.821</v>
+      </c>
+      <c r="G75">
+        <v>0.631</v>
+      </c>
+      <c r="H75">
+        <v>101.6</v>
+      </c>
+      <c r="I75">
+        <v>0</v>
+      </c>
+      <c r="J75">
+        <v>11.825</v>
+      </c>
+      <c r="K75">
+        <v>3.460000000000001</v>
+      </c>
+      <c r="L75">
+        <v>8.365</v>
+      </c>
+      <c r="M75">
+        <v>25.7476548</v>
+      </c>
+      <c r="N75">
+        <v>-17.3826548</v>
+      </c>
+      <c r="O75">
+        <v>-3.47653096</v>
+      </c>
+      <c r="P75">
+        <v>-13.90612384</v>
+      </c>
+      <c r="Q75">
+        <v>-10.44612384</v>
+      </c>
+      <c r="R75">
+        <v>2.703703703703703</v>
+      </c>
+      <c r="S75">
+        <v>0.2575269107054398</v>
+      </c>
+      <c r="T75">
+        <v>3.884091337605973</v>
+      </c>
+      <c r="U75">
+        <v>0.2388</v>
+      </c>
+      <c r="V75">
+        <v>0.0649767915950155</v>
+      </c>
+      <c r="W75">
+        <v>0.2232835421671103</v>
+      </c>
+      <c r="X75" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y75">
+        <v>0.3248839579750774</v>
+      </c>
+      <c r="Z75">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76">
+        <v>0.74</v>
+      </c>
+      <c r="B76">
+        <v>0.2345292516724593</v>
+      </c>
+      <c r="C76">
+        <v>-64.19822577692015</v>
+      </c>
+      <c r="D76">
+        <v>44.46877422307983</v>
+      </c>
+      <c r="E76">
+        <v>63.19799999999999</v>
+      </c>
+      <c r="F76">
+        <v>109.298</v>
+      </c>
+      <c r="G76">
+        <v>0.631</v>
+      </c>
+      <c r="H76">
+        <v>101.6</v>
+      </c>
+      <c r="I76">
+        <v>0</v>
+      </c>
+      <c r="J76">
+        <v>11.825</v>
+      </c>
+      <c r="K76">
+        <v>3.460000000000001</v>
+      </c>
+      <c r="L76">
+        <v>8.365</v>
+      </c>
+      <c r="M76">
+        <v>26.1003624</v>
+      </c>
+      <c r="N76">
+        <v>-17.7353624</v>
+      </c>
+      <c r="O76">
+        <v>-3.54707248</v>
+      </c>
+      <c r="P76">
+        <v>-14.18828992</v>
+      </c>
+      <c r="Q76">
+        <v>-10.72828992</v>
+      </c>
+      <c r="R76">
+        <v>2.846153846153846</v>
+      </c>
+      <c r="S76">
+        <v>0.2659394841941106</v>
+      </c>
+      <c r="T76">
+        <v>4.033479465975434</v>
+      </c>
+      <c r="U76">
+        <v>0.2388</v>
+      </c>
+      <c r="V76">
+        <v>0.0640987268437315</v>
+      </c>
+      <c r="W76">
+        <v>0.2234932240297169</v>
+      </c>
+      <c r="X76" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y76">
+        <v>0.3204936342186574</v>
+      </c>
+      <c r="Z76">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77">
+        <v>0.75</v>
+      </c>
+      <c r="B77">
+        <v>0.2365292516724593</v>
+      </c>
+      <c r="C77">
+        <v>-66.12502037075947</v>
+      </c>
+      <c r="D77">
+        <v>44.01897962924051</v>
+      </c>
+      <c r="E77">
+        <v>64.67499999999998</v>
+      </c>
+      <c r="F77">
+        <v>110.775</v>
+      </c>
+      <c r="G77">
+        <v>0.631</v>
+      </c>
+      <c r="H77">
+        <v>101.6</v>
+      </c>
+      <c r="I77">
+        <v>0</v>
+      </c>
+      <c r="J77">
+        <v>11.825</v>
+      </c>
+      <c r="K77">
+        <v>3.460000000000001</v>
+      </c>
+      <c r="L77">
+        <v>8.365</v>
+      </c>
+      <c r="M77">
+        <v>26.45307</v>
+      </c>
+      <c r="N77">
+        <v>-18.08807</v>
+      </c>
+      <c r="O77">
+        <v>-3.617614000000001</v>
+      </c>
+      <c r="P77">
+        <v>-14.470456</v>
+      </c>
+      <c r="Q77">
+        <v>-11.010456</v>
+      </c>
+      <c r="R77">
+        <v>3</v>
+      </c>
+      <c r="S77">
+        <v>0.2750250635618751</v>
+      </c>
+      <c r="T77">
+        <v>4.194818644614451</v>
+      </c>
+      <c r="U77">
+        <v>0.2388</v>
+      </c>
+      <c r="V77">
+        <v>0.06324407715248175</v>
+      </c>
+      <c r="W77">
+        <v>0.2236973143759874</v>
+      </c>
+      <c r="X77" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y77">
+        <v>0.3162203857624086</v>
+      </c>
+      <c r="Z77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78">
+        <v>0.76</v>
+      </c>
+      <c r="B78">
+        <v>0.2385292516724593</v>
+      </c>
+      <c r="C78">
+        <v>-68.04280687810019</v>
+      </c>
+      <c r="D78">
+        <v>43.5781931218998</v>
+      </c>
+      <c r="E78">
+        <v>66.15199999999999</v>
+      </c>
+      <c r="F78">
+        <v>112.252</v>
+      </c>
+      <c r="G78">
+        <v>0.631</v>
+      </c>
+      <c r="H78">
+        <v>101.6</v>
+      </c>
+      <c r="I78">
+        <v>0</v>
+      </c>
+      <c r="J78">
+        <v>11.825</v>
+      </c>
+      <c r="K78">
+        <v>3.460000000000001</v>
+      </c>
+      <c r="L78">
+        <v>8.365</v>
+      </c>
+      <c r="M78">
+        <v>26.8057776</v>
+      </c>
+      <c r="N78">
+        <v>-18.4407776</v>
+      </c>
+      <c r="O78">
+        <v>-3.68815552</v>
+      </c>
+      <c r="P78">
+        <v>-14.75262208</v>
+      </c>
+      <c r="Q78">
+        <v>-11.29262208</v>
+      </c>
+      <c r="R78">
+        <v>3.166666666666667</v>
+      </c>
+      <c r="S78">
+        <v>0.2848677745436199</v>
+      </c>
+      <c r="T78">
+        <v>4.369602754806721</v>
+      </c>
+      <c r="U78">
+        <v>0.2388</v>
+      </c>
+      <c r="V78">
+        <v>0.06241191824258067</v>
+      </c>
+      <c r="W78">
+        <v>0.2238960339236717</v>
+      </c>
+      <c r="X78" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y78">
+        <v>0.3120595912129034</v>
+      </c>
+      <c r="Z78">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79">
+        <v>0.77</v>
+      </c>
+      <c r="B79">
+        <v>0.2405292516724593</v>
+      </c>
+      <c r="C79">
+        <v>-69.9518532249796</v>
+      </c>
+      <c r="D79">
+        <v>43.1461467750204</v>
+      </c>
+      <c r="E79">
+        <v>67.62899999999999</v>
+      </c>
+      <c r="F79">
+        <v>113.729</v>
+      </c>
+      <c r="G79">
+        <v>0.631</v>
+      </c>
+      <c r="H79">
+        <v>101.6</v>
+      </c>
+      <c r="I79">
+        <v>0</v>
+      </c>
+      <c r="J79">
+        <v>11.825</v>
+      </c>
+      <c r="K79">
+        <v>3.460000000000001</v>
+      </c>
+      <c r="L79">
+        <v>8.365</v>
+      </c>
+      <c r="M79">
+        <v>27.1584852</v>
+      </c>
+      <c r="N79">
+        <v>-18.7934852</v>
+      </c>
+      <c r="O79">
+        <v>-3.75869704</v>
+      </c>
+      <c r="P79">
+        <v>-15.03478816</v>
+      </c>
+      <c r="Q79">
+        <v>-11.57478816</v>
+      </c>
+      <c r="R79">
+        <v>3.347826086956522</v>
+      </c>
+      <c r="S79">
+        <v>0.2955663734368207</v>
+      </c>
+      <c r="T79">
+        <v>4.559585483276577</v>
+      </c>
+      <c r="U79">
+        <v>0.2388</v>
+      </c>
+      <c r="V79">
+        <v>0.06160137384981988</v>
+      </c>
+      <c r="W79">
+        <v>0.224089591924663</v>
+      </c>
+      <c r="X79" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y79">
+        <v>0.3080068692490994</v>
+      </c>
+      <c r="Z79">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80">
+        <v>0.78</v>
+      </c>
+      <c r="B80">
+        <v>0.2425292516724593</v>
+      </c>
+      <c r="C80">
+        <v>-71.85241681656817</v>
+      </c>
+      <c r="D80">
+        <v>42.72258318343182</v>
+      </c>
+      <c r="E80">
+        <v>69.10599999999999</v>
+      </c>
+      <c r="F80">
+        <v>115.206</v>
+      </c>
+      <c r="G80">
+        <v>0.631</v>
+      </c>
+      <c r="H80">
+        <v>101.6</v>
+      </c>
+      <c r="I80">
+        <v>0</v>
+      </c>
+      <c r="J80">
+        <v>11.825</v>
+      </c>
+      <c r="K80">
+        <v>3.460000000000001</v>
+      </c>
+      <c r="L80">
+        <v>8.365</v>
+      </c>
+      <c r="M80">
+        <v>27.5111928</v>
+      </c>
+      <c r="N80">
+        <v>-19.1461928</v>
+      </c>
+      <c r="O80">
+        <v>-3.82923856</v>
+      </c>
+      <c r="P80">
+        <v>-15.31695424</v>
+      </c>
+      <c r="Q80">
+        <v>-11.85695424</v>
+      </c>
+      <c r="R80">
+        <v>3.545454545454546</v>
+      </c>
+      <c r="S80">
+        <v>0.3072375722294035</v>
+      </c>
+      <c r="T80">
+        <v>4.766839368880058</v>
+      </c>
+      <c r="U80">
+        <v>0.2388</v>
+      </c>
+      <c r="V80">
+        <v>0.06081161264661705</v>
+      </c>
+      <c r="W80">
+        <v>0.2242781868999879</v>
+      </c>
+      <c r="X80" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y80">
+        <v>0.3040580632330852</v>
+      </c>
+      <c r="Z80">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81">
+        <v>0.79</v>
+      </c>
+      <c r="B81">
+        <v>0.2445292516724593</v>
+      </c>
+      <c r="C81">
+        <v>-73.7447450485636</v>
+      </c>
+      <c r="D81">
+        <v>42.30725495143639</v>
+      </c>
+      <c r="E81">
+        <v>70.583</v>
+      </c>
+      <c r="F81">
+        <v>116.683</v>
+      </c>
+      <c r="G81">
+        <v>0.631</v>
+      </c>
+      <c r="H81">
+        <v>101.6</v>
+      </c>
+      <c r="I81">
+        <v>0</v>
+      </c>
+      <c r="J81">
+        <v>11.825</v>
+      </c>
+      <c r="K81">
+        <v>3.460000000000001</v>
+      </c>
+      <c r="L81">
+        <v>8.365</v>
+      </c>
+      <c r="M81">
+        <v>27.8639004</v>
+      </c>
+      <c r="N81">
+        <v>-19.4989004</v>
+      </c>
+      <c r="O81">
+        <v>-3.899780079999999</v>
+      </c>
+      <c r="P81">
+        <v>-15.59912032</v>
+      </c>
+      <c r="Q81">
+        <v>-12.13912032</v>
+      </c>
+      <c r="R81">
+        <v>3.761904761904763</v>
+      </c>
+      <c r="S81">
+        <v>0.320020313764137</v>
+      </c>
+      <c r="T81">
+        <v>4.993831719779109</v>
+      </c>
+      <c r="U81">
+        <v>0.2388</v>
+      </c>
+      <c r="V81">
+        <v>0.0600418453979257</v>
+      </c>
+      <c r="W81">
+        <v>0.2244620073189754</v>
+      </c>
+      <c r="X81" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y81">
+        <v>0.3002092269896286</v>
+      </c>
+      <c r="Z81">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82">
+        <v>0.8</v>
+      </c>
+      <c r="B82">
+        <v>0.2465292516724593</v>
+      </c>
+      <c r="C82">
+        <v>-75.62907578904252</v>
+      </c>
+      <c r="D82">
+        <v>41.89992421095748</v>
+      </c>
+      <c r="E82">
+        <v>72.06</v>
+      </c>
+      <c r="F82">
+        <v>118.16</v>
+      </c>
+      <c r="G82">
+        <v>0.631</v>
+      </c>
+      <c r="H82">
+        <v>101.6</v>
+      </c>
+      <c r="I82">
+        <v>0</v>
+      </c>
+      <c r="J82">
+        <v>11.825</v>
+      </c>
+      <c r="K82">
+        <v>3.460000000000001</v>
+      </c>
+      <c r="L82">
+        <v>8.365</v>
+      </c>
+      <c r="M82">
+        <v>28.216608</v>
+      </c>
+      <c r="N82">
+        <v>-19.851608</v>
+      </c>
+      <c r="O82">
+        <v>-3.9703216</v>
+      </c>
+      <c r="P82">
+        <v>-15.8812864</v>
+      </c>
+      <c r="Q82">
+        <v>-12.4212864</v>
+      </c>
+      <c r="R82">
+        <v>4.000000000000001</v>
+      </c>
+      <c r="S82">
+        <v>0.3340813294523439</v>
+      </c>
+      <c r="T82">
+        <v>5.243523305768065</v>
+      </c>
+      <c r="U82">
+        <v>0.2388</v>
+      </c>
+      <c r="V82">
+        <v>0.05929132233045162</v>
+      </c>
+      <c r="W82">
+        <v>0.2246412322274882</v>
+      </c>
+      <c r="X82" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y82">
+        <v>0.2964566116522582</v>
+      </c>
+      <c r="Z82">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="B83">
+        <v>0.2485292516724593</v>
+      </c>
+      <c r="C83">
+        <v>-77.50563783274251</v>
+      </c>
+      <c r="D83">
+        <v>41.5003621672575</v>
+      </c>
+      <c r="E83">
+        <v>73.53700000000001</v>
+      </c>
+      <c r="F83">
+        <v>119.637</v>
+      </c>
+      <c r="G83">
+        <v>0.631</v>
+      </c>
+      <c r="H83">
+        <v>101.6</v>
+      </c>
+      <c r="I83">
+        <v>0</v>
+      </c>
+      <c r="J83">
+        <v>11.825</v>
+      </c>
+      <c r="K83">
+        <v>3.460000000000001</v>
+      </c>
+      <c r="L83">
+        <v>8.365</v>
+      </c>
+      <c r="M83">
+        <v>28.5693156</v>
+      </c>
+      <c r="N83">
+        <v>-20.2043156</v>
+      </c>
+      <c r="O83">
+        <v>-4.04086312</v>
+      </c>
+      <c r="P83">
+        <v>-16.16345248</v>
+      </c>
+      <c r="Q83">
+        <v>-12.70345248</v>
+      </c>
+      <c r="R83">
+        <v>4.263157894736843</v>
+      </c>
+      <c r="S83">
+        <v>0.3496224520550988</v>
+      </c>
+      <c r="T83">
+        <v>5.519498216597964</v>
+      </c>
+      <c r="U83">
+        <v>0.2388</v>
+      </c>
+      <c r="V83">
+        <v>0.05855933069674234</v>
+      </c>
+      <c r="W83">
+        <v>0.2248160318296179</v>
+      </c>
+      <c r="X83" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y83">
+        <v>0.2927966534837118</v>
+      </c>
+      <c r="Z83">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84">
+        <v>0.8200000000000001</v>
+      </c>
+      <c r="B84">
+        <v>0.2505292516724593</v>
+      </c>
+      <c r="C84">
+        <v>-79.37465132959704</v>
+      </c>
+      <c r="D84">
+        <v>41.10834867040295</v>
+      </c>
+      <c r="E84">
+        <v>75.01400000000001</v>
+      </c>
+      <c r="F84">
+        <v>121.114</v>
+      </c>
+      <c r="G84">
+        <v>0.631</v>
+      </c>
+      <c r="H84">
+        <v>101.6</v>
+      </c>
+      <c r="I84">
+        <v>0</v>
+      </c>
+      <c r="J84">
+        <v>11.825</v>
+      </c>
+      <c r="K84">
+        <v>3.460000000000001</v>
+      </c>
+      <c r="L84">
+        <v>8.365</v>
+      </c>
+      <c r="M84">
+        <v>28.9220232</v>
+      </c>
+      <c r="N84">
+        <v>-20.5570232</v>
+      </c>
+      <c r="O84">
+        <v>-4.111404640000001</v>
+      </c>
+      <c r="P84">
+        <v>-16.44561856</v>
+      </c>
+      <c r="Q84">
+        <v>-12.98561856</v>
+      </c>
+      <c r="R84">
+        <v>4.555555555555557</v>
+      </c>
+      <c r="S84">
+        <v>0.3668903660581598</v>
+      </c>
+      <c r="T84">
+        <v>5.826137006408961</v>
+      </c>
+      <c r="U84">
+        <v>0.2388</v>
+      </c>
+      <c r="V84">
+        <v>0.05784519251751378</v>
+      </c>
+      <c r="W84">
+        <v>0.2249865680268177</v>
+      </c>
+      <c r="X84" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y84">
+        <v>0.2892259625875688</v>
+      </c>
+      <c r="Z84">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85">
+        <v>0.8300000000000001</v>
+      </c>
+      <c r="B85">
+        <v>0.2525292516724593</v>
+      </c>
+      <c r="C85">
+        <v>-81.23632818921007</v>
+      </c>
+      <c r="D85">
+        <v>40.72367181078992</v>
+      </c>
+      <c r="E85">
+        <v>76.49099999999999</v>
+      </c>
+      <c r="F85">
+        <v>122.591</v>
+      </c>
+      <c r="G85">
+        <v>0.631</v>
+      </c>
+      <c r="H85">
+        <v>101.6</v>
+      </c>
+      <c r="I85">
+        <v>0</v>
+      </c>
+      <c r="J85">
+        <v>11.825</v>
+      </c>
+      <c r="K85">
+        <v>3.460000000000001</v>
+      </c>
+      <c r="L85">
+        <v>8.365</v>
+      </c>
+      <c r="M85">
+        <v>29.2747308</v>
+      </c>
+      <c r="N85">
+        <v>-20.9097308</v>
+      </c>
+      <c r="O85">
+        <v>-4.18194616</v>
+      </c>
+      <c r="P85">
+        <v>-16.72778464</v>
+      </c>
+      <c r="Q85">
+        <v>-13.26778464</v>
+      </c>
+      <c r="R85">
+        <v>4.882352941176473</v>
+      </c>
+      <c r="S85">
+        <v>0.3861897993556987</v>
+      </c>
+      <c r="T85">
+        <v>6.16885094796243</v>
+      </c>
+      <c r="U85">
+        <v>0.2388</v>
+      </c>
+      <c r="V85">
+        <v>0.05714826248718229</v>
+      </c>
+      <c r="W85">
+        <v>0.2251529949180609</v>
+      </c>
+      <c r="X85" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y85">
+        <v>0.2857413124359115</v>
+      </c>
+      <c r="Z85">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86">
+        <v>0.84</v>
+      </c>
+      <c r="B86">
+        <v>0.2545292516724593</v>
+      </c>
+      <c r="C86">
+        <v>-83.09087246283151</v>
+      </c>
+      <c r="D86">
+        <v>40.34612753716847</v>
+      </c>
+      <c r="E86">
+        <v>77.96799999999999</v>
+      </c>
+      <c r="F86">
+        <v>124.068</v>
+      </c>
+      <c r="G86">
+        <v>0.631</v>
+      </c>
+      <c r="H86">
+        <v>101.6</v>
+      </c>
+      <c r="I86">
+        <v>0</v>
+      </c>
+      <c r="J86">
+        <v>11.825</v>
+      </c>
+      <c r="K86">
+        <v>3.460000000000001</v>
+      </c>
+      <c r="L86">
+        <v>8.365</v>
+      </c>
+      <c r="M86">
+        <v>29.6274384</v>
+      </c>
+      <c r="N86">
+        <v>-21.2624384</v>
+      </c>
+      <c r="O86">
+        <v>-4.252487680000001</v>
+      </c>
+      <c r="P86">
+        <v>-17.00995072</v>
+      </c>
+      <c r="Q86">
+        <v>-13.54995072</v>
+      </c>
+      <c r="R86">
+        <v>5.249999999999999</v>
+      </c>
+      <c r="S86">
+        <v>0.4079016618154297</v>
+      </c>
+      <c r="T86">
+        <v>6.554404132210079</v>
+      </c>
+      <c r="U86">
+        <v>0.2388</v>
+      </c>
+      <c r="V86">
+        <v>0.05646792602900155</v>
+      </c>
+      <c r="W86">
+        <v>0.2253154592642745</v>
+      </c>
+      <c r="X86" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y86">
+        <v>0.2823396301450077</v>
+      </c>
+      <c r="Z86">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87">
+        <v>0.85</v>
+      </c>
+      <c r="B87">
+        <v>0.2565292516724593</v>
+      </c>
+      <c r="C87">
+        <v>-84.93848070428052</v>
+      </c>
+      <c r="D87">
+        <v>39.97551929571947</v>
+      </c>
+      <c r="E87">
+        <v>79.44499999999999</v>
+      </c>
+      <c r="F87">
+        <v>125.545</v>
+      </c>
+      <c r="G87">
+        <v>0.631</v>
+      </c>
+      <c r="H87">
+        <v>101.6</v>
+      </c>
+      <c r="I87">
+        <v>0</v>
+      </c>
+      <c r="J87">
+        <v>11.825</v>
+      </c>
+      <c r="K87">
+        <v>3.460000000000001</v>
+      </c>
+      <c r="L87">
+        <v>8.365</v>
+      </c>
+      <c r="M87">
+        <v>29.980146</v>
+      </c>
+      <c r="N87">
+        <v>-21.615146</v>
+      </c>
+      <c r="O87">
+        <v>-4.3230292</v>
+      </c>
+      <c r="P87">
+        <v>-17.2921168</v>
+      </c>
+      <c r="Q87">
+        <v>-13.83211679999999</v>
+      </c>
+      <c r="R87">
+        <v>5.666666666666666</v>
+      </c>
+      <c r="S87">
+        <v>0.4325084392697918</v>
+      </c>
+      <c r="T87">
+        <v>6.991364407690752</v>
+      </c>
+      <c r="U87">
+        <v>0.2388</v>
+      </c>
+      <c r="V87">
+        <v>0.0558035974874839</v>
+      </c>
+      <c r="W87">
+        <v>0.2254741009199889</v>
+      </c>
+      <c r="X87" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y87">
+        <v>0.2790179874374195</v>
+      </c>
+      <c r="Z87">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88">
+        <v>0.86</v>
+      </c>
+      <c r="B88">
+        <v>0.2585292516724593</v>
+      </c>
+      <c r="C88">
+        <v>-86.77934231115759</v>
+      </c>
+      <c r="D88">
+        <v>39.6116576888424</v>
+      </c>
+      <c r="E88">
+        <v>80.922</v>
+      </c>
+      <c r="F88">
+        <v>127.022</v>
+      </c>
+      <c r="G88">
+        <v>0.631</v>
+      </c>
+      <c r="H88">
+        <v>101.6</v>
+      </c>
+      <c r="I88">
+        <v>0</v>
+      </c>
+      <c r="J88">
+        <v>11.825</v>
+      </c>
+      <c r="K88">
+        <v>3.460000000000001</v>
+      </c>
+      <c r="L88">
+        <v>8.365</v>
+      </c>
+      <c r="M88">
+        <v>30.3328536</v>
+      </c>
+      <c r="N88">
+        <v>-21.9678536</v>
+      </c>
+      <c r="O88">
+        <v>-4.39357072</v>
+      </c>
+      <c r="P88">
+        <v>-17.57428288</v>
+      </c>
+      <c r="Q88">
+        <v>-14.11428288</v>
+      </c>
+      <c r="R88">
+        <v>6.142857142857142</v>
+      </c>
+      <c r="S88">
+        <v>0.4606304706462054</v>
+      </c>
+      <c r="T88">
+        <v>7.490747579668662</v>
+      </c>
+      <c r="U88">
+        <v>0.2388</v>
+      </c>
+      <c r="V88">
+        <v>0.05515471844693175</v>
+      </c>
+      <c r="W88">
+        <v>0.2256290532348727</v>
+      </c>
+      <c r="X88" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y88">
+        <v>0.2757735922346588</v>
+      </c>
+      <c r="Z88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89">
+        <v>0.87</v>
+      </c>
+      <c r="B89">
+        <v>0.2605292516724593</v>
+      </c>
+      <c r="C89">
+        <v>-88.61363984759052</v>
+      </c>
+      <c r="D89">
+        <v>39.25436015240948</v>
+      </c>
+      <c r="E89">
+        <v>82.399</v>
+      </c>
+      <c r="F89">
+        <v>128.499</v>
+      </c>
+      <c r="G89">
+        <v>0.631</v>
+      </c>
+      <c r="H89">
+        <v>101.6</v>
+      </c>
+      <c r="I89">
+        <v>0</v>
+      </c>
+      <c r="J89">
+        <v>11.825</v>
+      </c>
+      <c r="K89">
+        <v>3.460000000000001</v>
+      </c>
+      <c r="L89">
+        <v>8.365</v>
+      </c>
+      <c r="M89">
+        <v>30.6855612</v>
+      </c>
+      <c r="N89">
+        <v>-22.3205612</v>
+      </c>
+      <c r="O89">
+        <v>-4.46411224</v>
+      </c>
+      <c r="P89">
+        <v>-17.85644896</v>
+      </c>
+      <c r="Q89">
+        <v>-14.39644896</v>
+      </c>
+      <c r="R89">
+        <v>6.692307692307692</v>
+      </c>
+      <c r="S89">
+        <v>0.4930789683882212</v>
+      </c>
+      <c r="T89">
+        <v>8.066958931950868</v>
+      </c>
+      <c r="U89">
+        <v>0.2388</v>
+      </c>
+      <c r="V89">
+        <v>0.05452075616593253</v>
+      </c>
+      <c r="W89">
+        <v>0.2257804434275753</v>
+      </c>
+      <c r="X89" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y89">
+        <v>0.2726037808296627</v>
+      </c>
+      <c r="Z89">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90">
+        <v>0.88</v>
+      </c>
+      <c r="B90">
+        <v>0.2625292516724593</v>
+      </c>
+      <c r="C90">
+        <v>-90.4415493496692</v>
+      </c>
+      <c r="D90">
+        <v>38.90345065033079</v>
+      </c>
+      <c r="E90">
+        <v>83.876</v>
+      </c>
+      <c r="F90">
+        <v>129.976</v>
+      </c>
+      <c r="G90">
+        <v>0.631</v>
+      </c>
+      <c r="H90">
+        <v>101.6</v>
+      </c>
+      <c r="I90">
+        <v>0</v>
+      </c>
+      <c r="J90">
+        <v>11.825</v>
+      </c>
+      <c r="K90">
+        <v>3.460000000000001</v>
+      </c>
+      <c r="L90">
+        <v>8.365</v>
+      </c>
+      <c r="M90">
+        <v>31.0382688</v>
+      </c>
+      <c r="N90">
+        <v>-22.6732688</v>
+      </c>
+      <c r="O90">
+        <v>-4.53465376</v>
+      </c>
+      <c r="P90">
+        <v>-18.13861504</v>
+      </c>
+      <c r="Q90">
+        <v>-14.67861504</v>
+      </c>
+      <c r="R90">
+        <v>7.333333333333334</v>
+      </c>
+      <c r="S90">
+        <v>0.5309355490872397</v>
+      </c>
+      <c r="T90">
+        <v>8.739205509613441</v>
+      </c>
+      <c r="U90">
+        <v>0.2388</v>
+      </c>
+      <c r="V90">
+        <v>0.05390120211859239</v>
+      </c>
+      <c r="W90">
+        <v>0.2259283929340802</v>
+      </c>
+      <c r="X90" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y90">
+        <v>0.2695060105929619</v>
+      </c>
+      <c r="Z90">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91">
+        <v>0.89</v>
+      </c>
+      <c r="B91">
+        <v>0.2645292516724593</v>
+      </c>
+      <c r="C91">
+        <v>-92.26324061464342</v>
+      </c>
+      <c r="D91">
+        <v>38.55875938535658</v>
+      </c>
+      <c r="E91">
+        <v>85.35300000000001</v>
+      </c>
+      <c r="F91">
+        <v>131.453</v>
+      </c>
+      <c r="G91">
+        <v>0.631</v>
+      </c>
+      <c r="H91">
+        <v>101.6</v>
+      </c>
+      <c r="I91">
+        <v>0</v>
+      </c>
+      <c r="J91">
+        <v>11.825</v>
+      </c>
+      <c r="K91">
+        <v>3.460000000000001</v>
+      </c>
+      <c r="L91">
+        <v>8.365</v>
+      </c>
+      <c r="M91">
+        <v>31.3909764</v>
+      </c>
+      <c r="N91">
+        <v>-23.0259764</v>
+      </c>
+      <c r="O91">
+        <v>-4.605195280000001</v>
+      </c>
+      <c r="P91">
+        <v>-18.42078112</v>
+      </c>
+      <c r="Q91">
+        <v>-14.96078112</v>
+      </c>
+      <c r="R91">
+        <v>8.090909090909092</v>
+      </c>
+      <c r="S91">
+        <v>0.5756751444588069</v>
+      </c>
+      <c r="T91">
+        <v>9.533678737760116</v>
+      </c>
+      <c r="U91">
+        <v>0.2388</v>
+      </c>
+      <c r="V91">
+        <v>0.05329557063411382</v>
+      </c>
+      <c r="W91">
+        <v>0.2260730177325736</v>
+      </c>
+      <c r="X91" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y91">
+        <v>0.266477853170569</v>
+      </c>
+      <c r="Z91">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92">
+        <v>0.9</v>
+      </c>
+      <c r="B92">
+        <v>0.2665292516724593</v>
+      </c>
+      <c r="C92">
+        <v>-94.07887747488142</v>
+      </c>
+      <c r="D92">
+        <v>38.22012252511858</v>
+      </c>
+      <c r="E92">
+        <v>86.83000000000001</v>
+      </c>
+      <c r="F92">
+        <v>132.93</v>
+      </c>
+      <c r="G92">
+        <v>0.631</v>
+      </c>
+      <c r="H92">
+        <v>101.6</v>
+      </c>
+      <c r="I92">
+        <v>0</v>
+      </c>
+      <c r="J92">
+        <v>11.825</v>
+      </c>
+      <c r="K92">
+        <v>3.460000000000001</v>
+      </c>
+      <c r="L92">
+        <v>8.365</v>
+      </c>
+      <c r="M92">
+        <v>31.743684</v>
+      </c>
+      <c r="N92">
+        <v>-23.378684</v>
+      </c>
+      <c r="O92">
+        <v>-4.6757368</v>
+      </c>
+      <c r="P92">
+        <v>-18.7029472</v>
+      </c>
+      <c r="Q92">
+        <v>-15.2429472</v>
+      </c>
+      <c r="R92">
+        <v>9.000000000000002</v>
+      </c>
+      <c r="S92">
+        <v>0.6293626589046877</v>
+      </c>
+      <c r="T92">
+        <v>10.48704661153613</v>
+      </c>
+      <c r="U92">
+        <v>0.2388</v>
+      </c>
+      <c r="V92">
+        <v>0.05270339762706812</v>
+      </c>
+      <c r="W92">
+        <v>0.2262144286466561</v>
+      </c>
+      <c r="X92" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y92">
+        <v>0.2635169881353406</v>
+      </c>
+      <c r="Z92">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93">
+        <v>0.91</v>
+      </c>
+      <c r="B93">
+        <v>0.2685292516724593</v>
+      </c>
+      <c r="C93">
+        <v>-95.88861805751833</v>
+      </c>
+      <c r="D93">
+        <v>37.88738194248165</v>
+      </c>
+      <c r="E93">
+        <v>88.30699999999999</v>
+      </c>
+      <c r="F93">
+        <v>134.407</v>
+      </c>
+      <c r="G93">
+        <v>0.631</v>
+      </c>
+      <c r="H93">
+        <v>101.6</v>
+      </c>
+      <c r="I93">
+        <v>0</v>
+      </c>
+      <c r="J93">
+        <v>11.825</v>
+      </c>
+      <c r="K93">
+        <v>3.460000000000001</v>
+      </c>
+      <c r="L93">
+        <v>8.365</v>
+      </c>
+      <c r="M93">
+        <v>32.0963916</v>
+      </c>
+      <c r="N93">
+        <v>-23.73139159999999</v>
+      </c>
+      <c r="O93">
+        <v>-4.746278319999999</v>
+      </c>
+      <c r="P93">
+        <v>-18.98511328</v>
+      </c>
+      <c r="Q93">
+        <v>-15.52511328</v>
+      </c>
+      <c r="R93">
+        <v>10.11111111111111</v>
+      </c>
+      <c r="S93">
+        <v>0.6949807321163197</v>
+      </c>
+      <c r="T93">
+        <v>11.65227401281792</v>
+      </c>
+      <c r="U93">
+        <v>0.2388</v>
+      </c>
+      <c r="V93">
+        <v>0.05212423941138605</v>
+      </c>
+      <c r="W93">
+        <v>0.226352731628561</v>
+      </c>
+      <c r="X93" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y93">
+        <v>0.2606211970569303</v>
+      </c>
+      <c r="Z93">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94">
+        <v>0.92</v>
+      </c>
+      <c r="B94">
+        <v>0.2705292516724593</v>
+      </c>
+      <c r="C94">
+        <v>-97.69261503065866</v>
+      </c>
+      <c r="D94">
+        <v>37.56038496934134</v>
+      </c>
+      <c r="E94">
+        <v>89.78399999999999</v>
+      </c>
+      <c r="F94">
+        <v>135.884</v>
+      </c>
+      <c r="G94">
+        <v>0.631</v>
+      </c>
+      <c r="H94">
+        <v>101.6</v>
+      </c>
+      <c r="I94">
+        <v>0</v>
+      </c>
+      <c r="J94">
+        <v>11.825</v>
+      </c>
+      <c r="K94">
+        <v>3.460000000000001</v>
+      </c>
+      <c r="L94">
+        <v>8.365</v>
+      </c>
+      <c r="M94">
+        <v>32.4490992</v>
+      </c>
+      <c r="N94">
+        <v>-24.0840992</v>
+      </c>
+      <c r="O94">
+        <v>-4.81681984</v>
+      </c>
+      <c r="P94">
+        <v>-19.26727936</v>
+      </c>
+      <c r="Q94">
+        <v>-15.80727936</v>
+      </c>
+      <c r="R94">
+        <v>11.50000000000001</v>
+      </c>
+      <c r="S94">
+        <v>0.77700332363086</v>
+      </c>
+      <c r="T94">
+        <v>13.10880826442017</v>
+      </c>
+      <c r="U94">
+        <v>0.2388</v>
+      </c>
+      <c r="V94">
+        <v>0.05155767159169708</v>
+      </c>
+      <c r="W94">
+        <v>0.2264880280239027</v>
+      </c>
+      <c r="X94" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y94">
+        <v>0.2577883579584854</v>
+      </c>
+      <c r="Z94">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95">
+        <v>0.93</v>
+      </c>
+      <c r="B95">
+        <v>0.2725292516724593</v>
+      </c>
+      <c r="C95">
+        <v>-99.49101583693837</v>
+      </c>
+      <c r="D95">
+        <v>37.23898416306162</v>
+      </c>
+      <c r="E95">
+        <v>91.261</v>
+      </c>
+      <c r="F95">
+        <v>137.361</v>
+      </c>
+      <c r="G95">
+        <v>0.631</v>
+      </c>
+      <c r="H95">
+        <v>101.6</v>
+      </c>
+      <c r="I95">
+        <v>0</v>
+      </c>
+      <c r="J95">
+        <v>11.825</v>
+      </c>
+      <c r="K95">
+        <v>3.460000000000001</v>
+      </c>
+      <c r="L95">
+        <v>8.365</v>
+      </c>
+      <c r="M95">
+        <v>32.8018068</v>
+      </c>
+      <c r="N95">
+        <v>-24.4368068</v>
+      </c>
+      <c r="O95">
+        <v>-4.88736136</v>
+      </c>
+      <c r="P95">
+        <v>-19.54944544</v>
+      </c>
+      <c r="Q95">
+        <v>-16.08944544</v>
+      </c>
+      <c r="R95">
+        <v>13.2857142857143</v>
+      </c>
+      <c r="S95">
+        <v>0.8824609412924114</v>
+      </c>
+      <c r="T95">
+        <v>14.98149515933734</v>
+      </c>
+      <c r="U95">
+        <v>0.2388</v>
+      </c>
+      <c r="V95">
+        <v>0.05100328802619495</v>
+      </c>
+      <c r="W95">
+        <v>0.2266204148193447</v>
+      </c>
+      <c r="X95" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y95">
+        <v>0.2550164401309748</v>
+      </c>
+      <c r="Z95">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96">
+        <v>0.9400000000000001</v>
+      </c>
+      <c r="B96">
+        <v>0.2745292516724593</v>
+      </c>
+      <c r="C96">
+        <v>-101.2839629151975</v>
+      </c>
+      <c r="D96">
+        <v>36.9230370848025</v>
+      </c>
+      <c r="E96">
+        <v>92.738</v>
+      </c>
+      <c r="F96">
+        <v>138.838</v>
+      </c>
+      <c r="G96">
+        <v>0.631</v>
+      </c>
+      <c r="H96">
+        <v>101.6</v>
+      </c>
+      <c r="I96">
+        <v>0</v>
+      </c>
+      <c r="J96">
+        <v>11.825</v>
+      </c>
+      <c r="K96">
+        <v>3.460000000000001</v>
+      </c>
+      <c r="L96">
+        <v>8.365</v>
+      </c>
+      <c r="M96">
+        <v>33.1545144</v>
+      </c>
+      <c r="N96">
+        <v>-24.7895144</v>
+      </c>
+      <c r="O96">
+        <v>-4.957902880000001</v>
+      </c>
+      <c r="P96">
+        <v>-19.83161152</v>
+      </c>
+      <c r="Q96">
+        <v>-16.37161152</v>
+      </c>
+      <c r="R96">
+        <v>15.66666666666668</v>
+      </c>
+      <c r="S96">
+        <v>1.02307109817448</v>
+      </c>
+      <c r="T96">
+        <v>17.4784110192269</v>
+      </c>
+      <c r="U96">
+        <v>0.2388</v>
+      </c>
+      <c r="V96">
+        <v>0.05046069985570351</v>
+      </c>
+      <c r="W96">
+        <v>0.226749984874458</v>
+      </c>
+      <c r="X96" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y96">
+        <v>0.2523034992785176</v>
+      </c>
+      <c r="Z96">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97">
+        <v>0.9500000000000001</v>
+      </c>
+      <c r="B97">
+        <v>0.2765292516724593</v>
+      </c>
+      <c r="C97">
+        <v>-103.071593910963</v>
+      </c>
+      <c r="D97">
+        <v>36.612406089037</v>
+      </c>
+      <c r="E97">
+        <v>94.215</v>
+      </c>
+      <c r="F97">
+        <v>140.315</v>
+      </c>
+      <c r="G97">
+        <v>0.631</v>
+      </c>
+      <c r="H97">
+        <v>101.6</v>
+      </c>
+      <c r="I97">
+        <v>0</v>
+      </c>
+      <c r="J97">
+        <v>11.825</v>
+      </c>
+      <c r="K97">
+        <v>3.460000000000001</v>
+      </c>
+      <c r="L97">
+        <v>8.365</v>
+      </c>
+      <c r="M97">
+        <v>33.507222</v>
+      </c>
+      <c r="N97">
+        <v>-25.142222</v>
+      </c>
+      <c r="O97">
+        <v>-5.0284444</v>
+      </c>
+      <c r="P97">
+        <v>-20.1137776</v>
+      </c>
+      <c r="Q97">
+        <v>-16.6537776</v>
+      </c>
+      <c r="R97">
+        <v>19.00000000000003</v>
+      </c>
+      <c r="S97">
+        <v>1.219925317809377</v>
+      </c>
+      <c r="T97">
+        <v>20.97409322307228</v>
+      </c>
+      <c r="U97">
+        <v>0.2388</v>
+      </c>
+      <c r="V97">
+        <v>0.04992953459406453</v>
+      </c>
+      <c r="W97">
+        <v>0.2268768271389374</v>
+      </c>
+      <c r="X97" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y97">
+        <v>0.2496476729703228</v>
+      </c>
+      <c r="Z97">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98">
+        <v>0.96</v>
+      </c>
+      <c r="B98">
+        <v>0.2785292516724593</v>
+      </c>
+      <c r="C98">
+        <v>-104.8540418763958</v>
+      </c>
+      <c r="D98">
+        <v>36.30695812360422</v>
+      </c>
+      <c r="E98">
+        <v>95.69199999999998</v>
+      </c>
+      <c r="F98">
+        <v>141.792</v>
+      </c>
+      <c r="G98">
+        <v>0.631</v>
+      </c>
+      <c r="H98">
+        <v>101.6</v>
+      </c>
+      <c r="I98">
+        <v>0</v>
+      </c>
+      <c r="J98">
+        <v>11.825</v>
+      </c>
+      <c r="K98">
+        <v>3.460000000000001</v>
+      </c>
+      <c r="L98">
+        <v>8.365</v>
+      </c>
+      <c r="M98">
+        <v>33.85992959999999</v>
+      </c>
+      <c r="N98">
+        <v>-25.49492959999999</v>
+      </c>
+      <c r="O98">
+        <v>-5.098985919999999</v>
+      </c>
+      <c r="P98">
+        <v>-20.39594367999999</v>
+      </c>
+      <c r="Q98">
+        <v>-16.93594367999999</v>
+      </c>
+      <c r="R98">
+        <v>23.99999999999998</v>
+      </c>
+      <c r="S98">
+        <v>1.515206647261718</v>
+      </c>
+      <c r="T98">
+        <v>26.2176165288403</v>
+      </c>
+      <c r="U98">
+        <v>0.2388</v>
+      </c>
+      <c r="V98">
+        <v>0.04940943527537637</v>
+      </c>
+      <c r="W98">
+        <v>0.2270010268562402</v>
+      </c>
+      <c r="X98" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y98">
+        <v>0.2470471763768819</v>
+      </c>
+      <c r="Z98">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99">
+        <v>0.97</v>
+      </c>
+      <c r="B99">
+        <v>0.2805292516724593</v>
+      </c>
+      <c r="C99">
+        <v>-106.6314354603117</v>
+      </c>
+      <c r="D99">
+        <v>36.00656453968828</v>
+      </c>
+      <c r="E99">
+        <v>97.16899999999998</v>
+      </c>
+      <c r="F99">
+        <v>143.269</v>
+      </c>
+      <c r="G99">
+        <v>0.631</v>
+      </c>
+      <c r="H99">
+        <v>101.6</v>
+      </c>
+      <c r="I99">
+        <v>0</v>
+      </c>
+      <c r="J99">
+        <v>11.825</v>
+      </c>
+      <c r="K99">
+        <v>3.460000000000001</v>
+      </c>
+      <c r="L99">
+        <v>8.365</v>
+      </c>
+      <c r="M99">
+        <v>34.2126372</v>
+      </c>
+      <c r="N99">
+        <v>-25.84763719999999</v>
+      </c>
+      <c r="O99">
+        <v>-5.16952744</v>
+      </c>
+      <c r="P99">
+        <v>-20.67810975999999</v>
+      </c>
+      <c r="Q99">
+        <v>-17.21810975999999</v>
+      </c>
+      <c r="R99">
+        <v>32.33333333333331</v>
+      </c>
+      <c r="S99">
+        <v>2.007342196348957</v>
+      </c>
+      <c r="T99">
+        <v>34.95682203845373</v>
+      </c>
+      <c r="U99">
+        <v>0.2388</v>
+      </c>
+      <c r="V99">
+        <v>0.04890005965398073</v>
+      </c>
+      <c r="W99">
+        <v>0.2271226657546294</v>
+      </c>
+      <c r="X99" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y99">
+        <v>0.2445002982699037</v>
+      </c>
+      <c r="Z99">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100">
+        <v>0.98</v>
+      </c>
+      <c r="B100">
+        <v>0.2825292516724593</v>
+      </c>
+      <c r="C100">
+        <v>-108.4038990888472</v>
+      </c>
+      <c r="D100">
+        <v>35.71110091115283</v>
+      </c>
+      <c r="E100">
+        <v>98.64599999999999</v>
+      </c>
+      <c r="F100">
+        <v>144.746</v>
+      </c>
+      <c r="G100">
+        <v>0.631</v>
+      </c>
+      <c r="H100">
+        <v>101.6</v>
+      </c>
+      <c r="I100">
+        <v>0</v>
+      </c>
+      <c r="J100">
+        <v>11.825</v>
+      </c>
+      <c r="K100">
+        <v>3.460000000000001</v>
+      </c>
+      <c r="L100">
+        <v>8.365</v>
+      </c>
+      <c r="M100">
+        <v>34.5653448</v>
+      </c>
+      <c r="N100">
+        <v>-26.2003448</v>
+      </c>
+      <c r="O100">
+        <v>-5.240068959999999</v>
+      </c>
+      <c r="P100">
+        <v>-20.96027584</v>
+      </c>
+      <c r="Q100">
+        <v>-17.50027584</v>
+      </c>
+      <c r="R100">
+        <v>48.99999999999996</v>
+      </c>
+      <c r="S100">
+        <v>2.991613294523436</v>
+      </c>
+      <c r="T100">
+        <v>52.4352330576806</v>
+      </c>
+      <c r="U100">
+        <v>0.2388</v>
+      </c>
+      <c r="V100">
+        <v>0.0484010794534299</v>
+      </c>
+      <c r="W100">
+        <v>0.227241822226521</v>
+      </c>
+      <c r="X100" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y100">
+        <v>0.2420053972671495</v>
+      </c>
+      <c r="Z100">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101">
+        <v>0.99</v>
+      </c>
+      <c r="B101">
+        <v>0.2845292516724593</v>
+      </c>
+      <c r="C101">
+        <v>-110.1715531373017</v>
+      </c>
+      <c r="D101">
+        <v>35.42044686269828</v>
+      </c>
+      <c r="E101">
+        <v>100.123</v>
+      </c>
+      <c r="F101">
+        <v>146.223</v>
+      </c>
+      <c r="G101">
+        <v>0.631</v>
+      </c>
+      <c r="H101">
+        <v>101.6</v>
+      </c>
+      <c r="I101">
+        <v>0</v>
+      </c>
+      <c r="J101">
+        <v>11.825</v>
+      </c>
+      <c r="K101">
+        <v>3.460000000000001</v>
+      </c>
+      <c r="L101">
+        <v>8.365</v>
+      </c>
+      <c r="M101">
+        <v>34.9180524</v>
+      </c>
+      <c r="N101">
+        <v>-26.5530524</v>
+      </c>
+      <c r="O101">
+        <v>-5.31061048</v>
+      </c>
+      <c r="P101">
+        <v>-21.24244192</v>
+      </c>
+      <c r="Q101">
+        <v>-17.78244192</v>
+      </c>
+      <c r="R101">
+        <v>98.99999999999991</v>
+      </c>
+      <c r="S101">
+        <v>5.944426589046872</v>
+      </c>
+      <c r="T101">
+        <v>104.8704661153612</v>
+      </c>
+      <c r="U101">
+        <v>0.2388</v>
+      </c>
+      <c r="V101">
+        <v>0.04791217966097101</v>
+      </c>
+      <c r="W101">
+        <v>0.2273585714969601</v>
+      </c>
+      <c r="X101" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y101">
+        <v>0.2395608983048552</v>
+      </c>
+      <c r="Z101">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/estonia/estonia_electrical_equipment.xlsx
+++ b/research/traditional_assets/database/data/estonia/estonia_electrical_equipment.xlsx
@@ -1278,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1415,22 +1415,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.103836180343591</v>
+        <v>0.1036645079829039</v>
       </c>
       <c r="C2">
-        <v>118.2072084267226</v>
+        <v>117.2893841858822</v>
       </c>
       <c r="D2">
-        <v>116.0172084267226</v>
+        <v>116.3423841858822</v>
       </c>
       <c r="E2">
-        <v>-36.7</v>
+        <v>-35.457</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>1.243</v>
       </c>
       <c r="G2">
         <v>2.19</v>
@@ -1451,28 +1451,28 @@
         <v>11.34222222222222</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.06252290000000001</v>
       </c>
       <c r="N2">
-        <v>11.34222222222222</v>
+        <v>11.27969932222222</v>
       </c>
       <c r="O2">
-        <v>2.268444444444444</v>
+        <v>2.255939864444445</v>
       </c>
       <c r="P2">
-        <v>9.073777777777778</v>
+        <v>9.023759457777778</v>
       </c>
       <c r="Q2">
-        <v>12.95377777777778</v>
+        <v>12.90375945777778</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.103836180343591</v>
+        <v>0.1043051595786908</v>
       </c>
       <c r="T2">
-        <v>1.100924895422504</v>
+        <v>1.109821258213797</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>181.4090872659813</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1497,22 +1497,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1036645079829039</v>
+        <v>0.1034928356222167</v>
       </c>
       <c r="C3">
-        <v>117.2893841858822</v>
+        <v>116.3733878889703</v>
       </c>
       <c r="D3">
-        <v>116.3423841858822</v>
+        <v>116.6693878889703</v>
       </c>
       <c r="E3">
-        <v>-35.457</v>
+        <v>-34.21400000000001</v>
       </c>
       <c r="F3">
-        <v>1.243</v>
+        <v>2.486</v>
       </c>
       <c r="G3">
         <v>2.19</v>
@@ -1533,28 +1533,28 @@
         <v>11.34222222222222</v>
       </c>
       <c r="M3">
-        <v>0.06252290000000001</v>
+        <v>0.1250458</v>
       </c>
       <c r="N3">
-        <v>11.27969932222222</v>
+        <v>11.21717642222222</v>
       </c>
       <c r="O3">
-        <v>2.255939864444445</v>
+        <v>2.243435284444444</v>
       </c>
       <c r="P3">
-        <v>9.023759457777778</v>
+        <v>8.973741137777777</v>
       </c>
       <c r="Q3">
-        <v>12.90375945777778</v>
+        <v>12.85374113777778</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1043051595786908</v>
+        <v>0.1047837098185884</v>
       </c>
       <c r="T3">
-        <v>1.109821258213797</v>
+        <v>1.118899179429402</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>181.4090872659813</v>
+        <v>90.70454363299064</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1579,22 +1579,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1034928356222167</v>
+        <v>0.1033211632615295</v>
       </c>
       <c r="C4">
-        <v>116.3733878889703</v>
+        <v>115.4592349928452</v>
       </c>
       <c r="D4">
-        <v>116.6693878889703</v>
+        <v>116.9982349928452</v>
       </c>
       <c r="E4">
-        <v>-34.21400000000001</v>
+        <v>-32.971</v>
       </c>
       <c r="F4">
-        <v>2.486</v>
+        <v>3.729</v>
       </c>
       <c r="G4">
         <v>2.19</v>
@@ -1615,28 +1615,28 @@
         <v>11.34222222222222</v>
       </c>
       <c r="M4">
-        <v>0.1250458</v>
+        <v>0.1875687</v>
       </c>
       <c r="N4">
-        <v>11.21717642222222</v>
+        <v>11.15465352222222</v>
       </c>
       <c r="O4">
-        <v>2.243435284444444</v>
+        <v>2.230930704444444</v>
       </c>
       <c r="P4">
-        <v>8.973741137777777</v>
+        <v>8.923722817777778</v>
       </c>
       <c r="Q4">
-        <v>12.85374113777778</v>
+        <v>12.80372281777778</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1047837098185884</v>
+        <v>0.1052721270737418</v>
       </c>
       <c r="T4">
-        <v>1.118899179429402</v>
+        <v>1.128164274278319</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>90.70454363299064</v>
+        <v>60.46969575532711</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1661,22 +1661,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1033211632615295</v>
+        <v>0.1031494909008423</v>
       </c>
       <c r="C5">
-        <v>115.4592349928452</v>
+        <v>114.5469411291262</v>
       </c>
       <c r="D5">
-        <v>116.9982349928452</v>
+        <v>117.3289411291262</v>
       </c>
       <c r="E5">
-        <v>-32.971</v>
+        <v>-31.728</v>
       </c>
       <c r="F5">
-        <v>3.729</v>
+        <v>4.972</v>
       </c>
       <c r="G5">
         <v>2.19</v>
@@ -1697,28 +1697,28 @@
         <v>11.34222222222222</v>
       </c>
       <c r="M5">
-        <v>0.1875687</v>
+        <v>0.2500916</v>
       </c>
       <c r="N5">
-        <v>11.15465352222222</v>
+        <v>11.09213062222222</v>
       </c>
       <c r="O5">
-        <v>2.230930704444444</v>
+        <v>2.218426124444445</v>
       </c>
       <c r="P5">
-        <v>8.923722817777778</v>
+        <v>8.873704497777778</v>
       </c>
       <c r="Q5">
-        <v>12.80372281777778</v>
+        <v>12.75370449777778</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1052721270737418</v>
+        <v>0.1057707196883774</v>
       </c>
       <c r="T5">
-        <v>1.128164274278319</v>
+        <v>1.137622391936588</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>60.46969575532711</v>
+        <v>45.35227181649532</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1031494909008423</v>
+        <v>0.1029778185401551</v>
       </c>
       <c r="C6">
-        <v>114.5469411291262</v>
+        <v>113.6365221066701</v>
       </c>
       <c r="D6">
-        <v>117.3289411291262</v>
+        <v>117.6615221066701</v>
       </c>
       <c r="E6">
-        <v>-31.728</v>
+        <v>-30.485</v>
       </c>
       <c r="F6">
-        <v>4.972</v>
+        <v>6.215</v>
       </c>
       <c r="G6">
         <v>2.19</v>
@@ -1779,28 +1779,28 @@
         <v>11.34222222222222</v>
       </c>
       <c r="M6">
-        <v>0.2500916</v>
+        <v>0.3126145</v>
       </c>
       <c r="N6">
-        <v>11.09213062222222</v>
+        <v>11.02960772222222</v>
       </c>
       <c r="O6">
-        <v>2.218426124444445</v>
+        <v>2.205921544444445</v>
       </c>
       <c r="P6">
-        <v>8.873704497777778</v>
+        <v>8.823686177777777</v>
       </c>
       <c r="Q6">
-        <v>12.75370449777778</v>
+        <v>12.70368617777778</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1057707196883774</v>
+        <v>0.106279808989637</v>
       </c>
       <c r="T6">
-        <v>1.137622391936588</v>
+        <v>1.147279627861347</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>45.35227181649532</v>
+        <v>36.28181745319626</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1825,22 +1825,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.1029778185401551</v>
+        <v>0.102806146179468</v>
       </c>
       <c r="C7">
-        <v>113.6365221066701</v>
+        <v>112.7279939140908</v>
       </c>
       <c r="D7">
-        <v>117.6615221066701</v>
+        <v>117.9959939140908</v>
       </c>
       <c r="E7">
-        <v>-30.485</v>
+        <v>-29.242</v>
       </c>
       <c r="F7">
-        <v>6.215</v>
+        <v>7.458</v>
       </c>
       <c r="G7">
         <v>2.19</v>
@@ -1861,28 +1861,28 @@
         <v>11.34222222222222</v>
       </c>
       <c r="M7">
-        <v>0.3126145</v>
+        <v>0.3751374</v>
       </c>
       <c r="N7">
-        <v>11.02960772222222</v>
+        <v>10.96708482222222</v>
       </c>
       <c r="O7">
-        <v>2.205921544444445</v>
+        <v>2.193416964444445</v>
       </c>
       <c r="P7">
-        <v>8.823686177777777</v>
+        <v>8.773667857777777</v>
       </c>
       <c r="Q7">
-        <v>12.70368617777778</v>
+        <v>12.65366785777778</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.106279808989637</v>
+        <v>0.1067997299781574</v>
       </c>
       <c r="T7">
-        <v>1.147279627861347</v>
+        <v>1.157142336890888</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>36.28181745319626</v>
+        <v>30.23484787766355</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1907,22 +1907,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.102806146179468</v>
+        <v>0.1026344738187808</v>
       </c>
       <c r="C8">
-        <v>112.7279939140908</v>
+        <v>111.8213727223212</v>
       </c>
       <c r="D8">
-        <v>117.9959939140908</v>
+        <v>118.3323727223212</v>
       </c>
       <c r="E8">
-        <v>-29.242</v>
+        <v>-27.999</v>
       </c>
       <c r="F8">
-        <v>7.457999999999999</v>
+        <v>8.700999999999999</v>
       </c>
       <c r="G8">
         <v>2.19</v>
@@ -1943,28 +1943,28 @@
         <v>11.34222222222222</v>
       </c>
       <c r="M8">
-        <v>0.3751374</v>
+        <v>0.4376602999999999</v>
       </c>
       <c r="N8">
-        <v>10.96708482222222</v>
+        <v>10.90456192222222</v>
       </c>
       <c r="O8">
-        <v>2.193416964444445</v>
+        <v>2.180912384444445</v>
       </c>
       <c r="P8">
-        <v>8.773667857777777</v>
+        <v>8.723649537777778</v>
       </c>
       <c r="Q8">
-        <v>12.65366785777778</v>
+        <v>12.60364953777778</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1067997299781574</v>
+        <v>0.1073308320632052</v>
       </c>
       <c r="T8">
-        <v>1.157142336890888</v>
+        <v>1.167217147189881</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>30.23484787766355</v>
+        <v>25.91558389514019</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1989,22 +1989,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1026344738187808</v>
+        <v>0.1024628014580936</v>
       </c>
       <c r="C9">
-        <v>111.8213727223211</v>
+        <v>110.9166748872194</v>
       </c>
       <c r="D9">
-        <v>118.3323727223212</v>
+        <v>118.6706748872194</v>
       </c>
       <c r="E9">
-        <v>-27.999</v>
+        <v>-26.756</v>
       </c>
       <c r="F9">
-        <v>8.701000000000001</v>
+        <v>9.944000000000001</v>
       </c>
       <c r="G9">
         <v>2.19</v>
@@ -2025,28 +2025,28 @@
         <v>11.34222222222222</v>
       </c>
       <c r="M9">
-        <v>0.4376603</v>
+        <v>0.5001832</v>
       </c>
       <c r="N9">
-        <v>10.90456192222222</v>
+        <v>10.84203902222222</v>
       </c>
       <c r="O9">
-        <v>2.180912384444445</v>
+        <v>2.168407804444445</v>
       </c>
       <c r="P9">
-        <v>8.723649537777778</v>
+        <v>8.673631217777778</v>
       </c>
       <c r="Q9">
-        <v>12.60364953777778</v>
+        <v>12.55363121777778</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1073308320632052</v>
+        <v>0.1078734798457539</v>
       </c>
       <c r="T9">
-        <v>1.167217147189881</v>
+        <v>1.17751097510407</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>25.91558389514019</v>
+        <v>22.67613590824766</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2071,22 +2071,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1024628014580936</v>
+        <v>0.1022911290974064</v>
       </c>
       <c r="C10">
-        <v>110.9166748872194</v>
+        <v>110.01391695222</v>
       </c>
       <c r="D10">
-        <v>118.6706748872194</v>
+        <v>119.01091695222</v>
       </c>
       <c r="E10">
-        <v>-26.756</v>
+        <v>-25.51300000000001</v>
       </c>
       <c r="F10">
-        <v>9.944000000000001</v>
+        <v>11.187</v>
       </c>
       <c r="G10">
         <v>2.19</v>
@@ -2107,28 +2107,28 @@
         <v>11.34222222222222</v>
       </c>
       <c r="M10">
-        <v>0.5001832</v>
+        <v>0.5627061</v>
       </c>
       <c r="N10">
-        <v>10.84203902222222</v>
+        <v>10.77951612222222</v>
       </c>
       <c r="O10">
-        <v>2.168407804444445</v>
+        <v>2.155903224444445</v>
       </c>
       <c r="P10">
-        <v>8.673631217777778</v>
+        <v>8.623612897777779</v>
       </c>
       <c r="Q10">
-        <v>12.55363121777778</v>
+        <v>12.50361289777778</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1078734798457539</v>
+        <v>0.1084280539531939</v>
       </c>
       <c r="T10">
-        <v>1.17751097510407</v>
+        <v>1.188031040994395</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>22.67613590824766</v>
+        <v>20.1565652517757</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2153,22 +2153,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1022911290974064</v>
+        <v>0.1021194567367192</v>
       </c>
       <c r="C11">
-        <v>110.01391695222</v>
+        <v>109.1131156510304</v>
       </c>
       <c r="D11">
-        <v>119.01091695222</v>
+        <v>119.3531156510304</v>
       </c>
       <c r="E11">
-        <v>-25.51300000000001</v>
+        <v>-24.27</v>
       </c>
       <c r="F11">
-        <v>11.187</v>
+        <v>12.43</v>
       </c>
       <c r="G11">
         <v>2.19</v>
@@ -2189,28 +2189,28 @@
         <v>11.34222222222222</v>
       </c>
       <c r="M11">
-        <v>0.5627061</v>
+        <v>0.6252289999999998</v>
       </c>
       <c r="N11">
-        <v>10.77951612222222</v>
+        <v>10.71699322222222</v>
       </c>
       <c r="O11">
-        <v>2.155903224444445</v>
+        <v>2.143398644444445</v>
       </c>
       <c r="P11">
-        <v>8.623612897777779</v>
+        <v>8.573594577777779</v>
       </c>
       <c r="Q11">
-        <v>12.50361289777778</v>
+        <v>12.45359457777778</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1084280539531939</v>
+        <v>0.108994951929688</v>
       </c>
       <c r="T11">
-        <v>1.188031040994395</v>
+        <v>1.198784886126727</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2227,7 +2227,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>20.1565652517757</v>
+        <v>18.14090872659814</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2235,22 +2235,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.1021194567367193</v>
+        <v>0.101947784376032</v>
       </c>
       <c r="C12">
-        <v>109.1131156510304</v>
+        <v>108.2142879103746</v>
       </c>
       <c r="D12">
-        <v>119.3531156510304</v>
+        <v>119.6972879103746</v>
       </c>
       <c r="E12">
-        <v>-24.27</v>
+        <v>-23.027</v>
       </c>
       <c r="F12">
-        <v>12.43</v>
+        <v>13.673</v>
       </c>
       <c r="G12">
         <v>2.19</v>
@@ -2271,28 +2271,28 @@
         <v>11.34222222222222</v>
       </c>
       <c r="M12">
-        <v>0.6252289999999999</v>
+        <v>0.6877519</v>
       </c>
       <c r="N12">
-        <v>10.71699322222222</v>
+        <v>10.65447032222222</v>
       </c>
       <c r="O12">
-        <v>2.143398644444445</v>
+        <v>2.130894064444445</v>
       </c>
       <c r="P12">
-        <v>8.573594577777779</v>
+        <v>8.523576257777778</v>
       </c>
       <c r="Q12">
-        <v>12.45359457777778</v>
+        <v>12.40357625777778</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1089949519296881</v>
+        <v>0.1095745891865529</v>
       </c>
       <c r="T12">
-        <v>1.198784886126727</v>
+        <v>1.209780390700235</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>18.14090872659813</v>
+        <v>16.4917352059983</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2317,22 +2317,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.101947784376032</v>
+        <v>0.1017761120153449</v>
       </c>
       <c r="C13">
-        <v>108.2142879103746</v>
+        <v>107.3174508527838</v>
       </c>
       <c r="D13">
-        <v>119.6972879103746</v>
+        <v>120.0434508527838</v>
       </c>
       <c r="E13">
-        <v>-23.027</v>
+        <v>-21.78400000000001</v>
       </c>
       <c r="F13">
-        <v>13.673</v>
+        <v>14.916</v>
       </c>
       <c r="G13">
         <v>2.19</v>
@@ -2353,28 +2353,28 @@
         <v>11.34222222222222</v>
       </c>
       <c r="M13">
-        <v>0.6877519</v>
+        <v>0.7502747999999999</v>
       </c>
       <c r="N13">
-        <v>10.65447032222222</v>
+        <v>10.59194742222222</v>
       </c>
       <c r="O13">
-        <v>2.130894064444445</v>
+        <v>2.118389484444445</v>
       </c>
       <c r="P13">
-        <v>8.523576257777778</v>
+        <v>8.473557937777779</v>
       </c>
       <c r="Q13">
-        <v>12.40357625777778</v>
+        <v>12.35355793777778</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1095745891865529</v>
+        <v>0.1101674000174374</v>
       </c>
       <c r="T13">
-        <v>1.209780390700235</v>
+        <v>1.22102579310496</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2391,7 +2391,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>16.4917352059983</v>
+        <v>15.11742393883178</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2399,22 +2399,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.1017761120153449</v>
+        <v>0.1016044396546577</v>
       </c>
       <c r="C14">
-        <v>107.3174508527838</v>
+        <v>106.4226217994365</v>
       </c>
       <c r="D14">
-        <v>120.0434508527838</v>
+        <v>120.3916217994365</v>
       </c>
       <c r="E14">
-        <v>-21.78400000000001</v>
+        <v>-20.541</v>
       </c>
       <c r="F14">
-        <v>14.916</v>
+        <v>16.159</v>
       </c>
       <c r="G14">
         <v>2.19</v>
@@ -2435,28 +2435,28 @@
         <v>11.34222222222222</v>
       </c>
       <c r="M14">
-        <v>0.7502747999999999</v>
+        <v>0.8127977</v>
       </c>
       <c r="N14">
-        <v>10.59194742222222</v>
+        <v>10.52942452222222</v>
       </c>
       <c r="O14">
-        <v>2.118389484444445</v>
+        <v>2.105884904444444</v>
       </c>
       <c r="P14">
-        <v>8.473557937777779</v>
+        <v>8.423539617777777</v>
       </c>
       <c r="Q14">
-        <v>12.35355793777778</v>
+        <v>12.30353961777778</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1101674000174374</v>
+        <v>0.1107738386835146</v>
       </c>
       <c r="T14">
-        <v>1.22102579310496</v>
+        <v>1.232529710507493</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2473,7 +2473,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>15.11742393883178</v>
+        <v>13.95454517430625</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2481,22 +2481,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1016044396546577</v>
+        <v>0.1014327672939705</v>
       </c>
       <c r="C15">
-        <v>106.4226217994365</v>
+        <v>105.5298182730471</v>
       </c>
       <c r="D15">
-        <v>120.3916217994365</v>
+        <v>120.7418182730471</v>
       </c>
       <c r="E15">
-        <v>-20.541</v>
+        <v>-19.298</v>
       </c>
       <c r="F15">
-        <v>16.159</v>
+        <v>17.402</v>
       </c>
       <c r="G15">
         <v>2.19</v>
@@ -2517,28 +2517,28 @@
         <v>11.34222222222222</v>
       </c>
       <c r="M15">
-        <v>0.8127977</v>
+        <v>0.8753206</v>
       </c>
       <c r="N15">
-        <v>10.52942452222222</v>
+        <v>10.46690162222222</v>
       </c>
       <c r="O15">
-        <v>2.105884904444444</v>
+        <v>2.093380324444444</v>
       </c>
       <c r="P15">
-        <v>8.423539617777777</v>
+        <v>8.373521297777778</v>
       </c>
       <c r="Q15">
-        <v>12.30353961777778</v>
+        <v>12.25352129777778</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1107738386835146</v>
+        <v>0.1113943805743843</v>
       </c>
       <c r="T15">
-        <v>1.232529710507493</v>
+        <v>1.244301160872877</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>13.95454517430625</v>
+        <v>12.95779194757009</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2563,22 +2563,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1014327672939705</v>
+        <v>0.1014410949332833</v>
       </c>
       <c r="C16">
-        <v>105.5298182730471</v>
+        <v>104.2697836131639</v>
       </c>
       <c r="D16">
-        <v>120.7418182730471</v>
+        <v>120.7247836131639</v>
       </c>
       <c r="E16">
-        <v>-19.298</v>
+        <v>-18.055</v>
       </c>
       <c r="F16">
-        <v>17.402</v>
+        <v>18.645</v>
       </c>
       <c r="G16">
         <v>2.19</v>
@@ -2599,45 +2599,45 @@
         <v>11.34222222222222</v>
       </c>
       <c r="M16">
-        <v>0.8753206</v>
+        <v>0.9658110000000001</v>
       </c>
       <c r="N16">
-        <v>10.46690162222222</v>
+        <v>10.37641122222222</v>
       </c>
       <c r="O16">
-        <v>2.093380324444444</v>
+        <v>2.075282244444444</v>
       </c>
       <c r="P16">
-        <v>8.373521297777778</v>
+        <v>8.301128977777777</v>
       </c>
       <c r="Q16">
-        <v>12.25352129777778</v>
+        <v>12.18112897777778</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1113943805743843</v>
+        <v>0.1120295234509215</v>
       </c>
       <c r="T16">
-        <v>1.244301160872877</v>
+        <v>1.256349586540976</v>
       </c>
       <c r="U16">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V16">
         <v>0.2</v>
       </c>
       <c r="W16">
-        <v>0.04024</v>
+        <v>0.04144</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y16">
-        <v>12.95779194757009</v>
+        <v>11.74372855788785</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2645,22 +2645,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1014410949332833</v>
+        <v>0.1012814225725961</v>
       </c>
       <c r="C17">
-        <v>104.2697836131639</v>
+        <v>103.3542422373614</v>
       </c>
       <c r="D17">
-        <v>120.7247836131639</v>
+        <v>121.0522422373614</v>
       </c>
       <c r="E17">
-        <v>-18.055</v>
+        <v>-16.812</v>
       </c>
       <c r="F17">
-        <v>18.645</v>
+        <v>19.888</v>
       </c>
       <c r="G17">
         <v>2.19</v>
@@ -2681,28 +2681,28 @@
         <v>11.34222222222222</v>
       </c>
       <c r="M17">
-        <v>0.965811</v>
+        <v>1.0301984</v>
       </c>
       <c r="N17">
-        <v>10.37641122222222</v>
+        <v>10.31202382222222</v>
       </c>
       <c r="O17">
-        <v>2.075282244444444</v>
+        <v>2.062404764444445</v>
       </c>
       <c r="P17">
-        <v>8.301128977777777</v>
+        <v>8.249619057777778</v>
       </c>
       <c r="Q17">
-        <v>12.18112897777778</v>
+        <v>12.12961905777778</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1120295234509215</v>
+        <v>0.1126797887769002</v>
       </c>
       <c r="T17">
-        <v>1.256349586540976</v>
+        <v>1.268684879486886</v>
       </c>
       <c r="U17">
         <v>0.0518</v>
@@ -2719,7 +2719,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>11.74372855788785</v>
+        <v>11.00974552301986</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2727,22 +2727,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.1012814225725961</v>
+        <v>0.101121750211909</v>
       </c>
       <c r="C18">
-        <v>103.3542422373614</v>
+        <v>102.4404821162598</v>
       </c>
       <c r="D18">
-        <v>121.0522422373614</v>
+        <v>121.3814821162598</v>
       </c>
       <c r="E18">
-        <v>-16.812</v>
+        <v>-15.569</v>
       </c>
       <c r="F18">
-        <v>19.888</v>
+        <v>21.131</v>
       </c>
       <c r="G18">
         <v>2.19</v>
@@ -2763,28 +2763,28 @@
         <v>11.34222222222222</v>
       </c>
       <c r="M18">
-        <v>1.0301984</v>
+        <v>1.0945858</v>
       </c>
       <c r="N18">
-        <v>10.31202382222222</v>
+        <v>10.24763642222222</v>
       </c>
       <c r="O18">
-        <v>2.062404764444445</v>
+        <v>2.049527284444444</v>
       </c>
       <c r="P18">
-        <v>8.249619057777778</v>
+        <v>8.198109137777777</v>
       </c>
       <c r="Q18">
-        <v>12.12961905777778</v>
+        <v>12.07810913777778</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1126797887769002</v>
+        <v>0.1133457231468783</v>
       </c>
       <c r="T18">
-        <v>1.268684879486886</v>
+        <v>1.281317408407397</v>
       </c>
       <c r="U18">
         <v>0.0518</v>
@@ -2801,7 +2801,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>11.00974552301986</v>
+        <v>10.36211343343045</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.101121750211909</v>
+        <v>0.1012068778512218</v>
       </c>
       <c r="C19">
-        <v>102.4404821162598</v>
+        <v>101.0217287766442</v>
       </c>
       <c r="D19">
-        <v>121.3814821162598</v>
+        <v>121.2057287766442</v>
       </c>
       <c r="E19">
-        <v>-15.569</v>
+        <v>-14.326</v>
       </c>
       <c r="F19">
-        <v>21.131</v>
+        <v>22.374</v>
       </c>
       <c r="G19">
         <v>2.19</v>
@@ -2845,45 +2845,45 @@
         <v>11.34222222222222</v>
       </c>
       <c r="M19">
-        <v>1.0945858</v>
+        <v>1.197009</v>
       </c>
       <c r="N19">
-        <v>10.24763642222222</v>
+        <v>10.14521322222222</v>
       </c>
       <c r="O19">
-        <v>2.049527284444444</v>
+        <v>2.029042644444444</v>
       </c>
       <c r="P19">
-        <v>8.198109137777777</v>
+        <v>8.116170577777778</v>
       </c>
       <c r="Q19">
-        <v>12.07810913777778</v>
+        <v>11.99617057777778</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1133457231468783</v>
+        <v>0.1140278998185631</v>
       </c>
       <c r="T19">
-        <v>1.281317408407397</v>
+        <v>1.294258047789383</v>
       </c>
       <c r="U19">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V19">
         <v>0.2</v>
       </c>
       <c r="W19">
-        <v>0.04144</v>
+        <v>0.0428</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y19">
-        <v>10.36211343343045</v>
+        <v>9.475469459479603</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2891,22 +2891,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1012068778512218</v>
+        <v>0.1010608054905346</v>
       </c>
       <c r="C20">
-        <v>101.0217287766442</v>
+        <v>100.0806211393286</v>
       </c>
       <c r="D20">
-        <v>121.2057287766442</v>
+        <v>121.5076211393286</v>
       </c>
       <c r="E20">
-        <v>-14.326</v>
+        <v>-13.083</v>
       </c>
       <c r="F20">
-        <v>22.374</v>
+        <v>23.617</v>
       </c>
       <c r="G20">
         <v>2.19</v>
@@ -2927,28 +2927,28 @@
         <v>11.34222222222222</v>
       </c>
       <c r="M20">
-        <v>1.197009</v>
+        <v>1.2635095</v>
       </c>
       <c r="N20">
-        <v>10.14521322222222</v>
+        <v>10.07871272222222</v>
       </c>
       <c r="O20">
-        <v>2.029042644444444</v>
+        <v>2.015742544444445</v>
       </c>
       <c r="P20">
-        <v>8.116170577777778</v>
+        <v>8.062970177777778</v>
       </c>
       <c r="Q20">
-        <v>11.99617057777778</v>
+        <v>11.94297017777778</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1140278998185631</v>
+        <v>0.1147269203586847</v>
       </c>
       <c r="T20">
-        <v>1.294258047789383</v>
+        <v>1.307518209131419</v>
       </c>
       <c r="U20">
         <v>0.0535</v>
@@ -2965,7 +2965,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>9.475469459479605</v>
+        <v>8.976760540559626</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2973,22 +2973,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1010608054905346</v>
+        <v>0.1009147331298474</v>
       </c>
       <c r="C21">
-        <v>100.0806211393286</v>
+        <v>99.14102112991553</v>
       </c>
       <c r="D21">
-        <v>121.5076211393286</v>
+        <v>121.8110211299155</v>
       </c>
       <c r="E21">
-        <v>-13.083</v>
+        <v>-11.84</v>
       </c>
       <c r="F21">
-        <v>23.617</v>
+        <v>24.86</v>
       </c>
       <c r="G21">
         <v>2.19</v>
@@ -3009,28 +3009,28 @@
         <v>11.34222222222222</v>
       </c>
       <c r="M21">
-        <v>1.2635095</v>
+        <v>1.33001</v>
       </c>
       <c r="N21">
-        <v>10.07871272222222</v>
+        <v>10.01221222222222</v>
       </c>
       <c r="O21">
-        <v>2.015742544444445</v>
+        <v>2.002442444444445</v>
       </c>
       <c r="P21">
-        <v>8.062970177777778</v>
+        <v>8.009769777777779</v>
       </c>
       <c r="Q21">
-        <v>11.94297017777778</v>
+        <v>11.88976977777778</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1147269203586847</v>
+        <v>0.1154434164123093</v>
       </c>
       <c r="T21">
-        <v>1.307518209131419</v>
+        <v>1.321109874507005</v>
       </c>
       <c r="U21">
         <v>0.0535</v>
@@ -3047,7 +3047,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>8.976760540559626</v>
+        <v>8.527922513531646</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3055,22 +3055,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1009147331298474</v>
+        <v>0.1007686607691602</v>
       </c>
       <c r="C22">
-        <v>99.14102112991553</v>
+        <v>98.20294007014655</v>
       </c>
       <c r="D22">
-        <v>121.8110211299155</v>
+        <v>122.1159400701466</v>
       </c>
       <c r="E22">
-        <v>-11.84</v>
+        <v>-10.597</v>
       </c>
       <c r="F22">
-        <v>24.86</v>
+        <v>26.103</v>
       </c>
       <c r="G22">
         <v>2.19</v>
@@ -3091,28 +3091,28 @@
         <v>11.34222222222222</v>
       </c>
       <c r="M22">
-        <v>1.33001</v>
+        <v>1.3965105</v>
       </c>
       <c r="N22">
-        <v>10.01221222222222</v>
+        <v>9.945711722222223</v>
       </c>
       <c r="O22">
-        <v>2.002442444444445</v>
+        <v>1.989142344444445</v>
       </c>
       <c r="P22">
-        <v>8.009769777777779</v>
+        <v>7.956569377777778</v>
       </c>
       <c r="Q22">
-        <v>11.88976977777778</v>
+        <v>11.83656937777778</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1154434164123093</v>
+        <v>0.1161780516065319</v>
       </c>
       <c r="T22">
-        <v>1.321109874507005</v>
+        <v>1.33504563267691</v>
       </c>
       <c r="U22">
         <v>0.0535</v>
@@ -3129,7 +3129,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>8.527922513531646</v>
+        <v>8.121830965268234</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3137,22 +3137,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1007686607691602</v>
+        <v>0.100622588408473</v>
       </c>
       <c r="C23">
-        <v>98.20294007014655</v>
+        <v>97.2663893954107</v>
       </c>
       <c r="D23">
-        <v>122.1159400701466</v>
+        <v>122.4223893954107</v>
       </c>
       <c r="E23">
-        <v>-10.597</v>
+        <v>-9.354000000000003</v>
       </c>
       <c r="F23">
-        <v>26.103</v>
+        <v>27.346</v>
       </c>
       <c r="G23">
         <v>2.19</v>
@@ -3173,28 +3173,28 @@
         <v>11.34222222222222</v>
       </c>
       <c r="M23">
-        <v>1.3965105</v>
+        <v>1.463011</v>
       </c>
       <c r="N23">
-        <v>9.945711722222223</v>
+        <v>9.879211222222223</v>
       </c>
       <c r="O23">
-        <v>1.989142344444445</v>
+        <v>1.975842244444445</v>
       </c>
       <c r="P23">
-        <v>7.956569377777778</v>
+        <v>7.903368977777778</v>
       </c>
       <c r="Q23">
-        <v>11.83656937777778</v>
+        <v>11.78336897777778</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1161780516065319</v>
+        <v>0.1169315236006065</v>
       </c>
       <c r="T23">
-        <v>1.33504563267691</v>
+        <v>1.349338717979377</v>
       </c>
       <c r="U23">
         <v>0.0535</v>
@@ -3211,7 +3211,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>8.121830965268234</v>
+        <v>7.752656830483313</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3219,22 +3219,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.100622588408473</v>
+        <v>0.1006237160477859</v>
       </c>
       <c r="C24">
-        <v>97.2663893954107</v>
+        <v>96.02101779830892</v>
       </c>
       <c r="D24">
-        <v>122.4223893954107</v>
+        <v>122.4200177983089</v>
       </c>
       <c r="E24">
-        <v>-9.354000000000003</v>
+        <v>-8.111000000000001</v>
       </c>
       <c r="F24">
-        <v>27.346</v>
+        <v>28.589</v>
       </c>
       <c r="G24">
         <v>2.19</v>
@@ -3255,45 +3255,45 @@
         <v>11.34222222222222</v>
       </c>
       <c r="M24">
-        <v>1.463011</v>
+        <v>1.5523827</v>
       </c>
       <c r="N24">
-        <v>9.879211222222223</v>
+        <v>9.789839522222222</v>
       </c>
       <c r="O24">
-        <v>1.975842244444445</v>
+        <v>1.957967904444444</v>
       </c>
       <c r="P24">
-        <v>7.903368977777778</v>
+        <v>7.831871617777777</v>
       </c>
       <c r="Q24">
-        <v>11.78336897777778</v>
+        <v>11.71187161777778</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1169315236006065</v>
+        <v>0.1177045662958258</v>
       </c>
       <c r="T24">
-        <v>1.349338717979377</v>
+        <v>1.364003052250739</v>
       </c>
       <c r="U24">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V24">
         <v>0.2</v>
       </c>
       <c r="W24">
-        <v>0.0428</v>
+        <v>0.04344000000000001</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y24">
-        <v>7.752656830483313</v>
+        <v>7.306331243076994</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3301,22 +3301,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1006237160477859</v>
+        <v>0.1004840436870987</v>
       </c>
       <c r="C25">
-        <v>96.02101779830892</v>
+        <v>95.07247087981949</v>
       </c>
       <c r="D25">
-        <v>122.4200177983089</v>
+        <v>122.7144708798195</v>
       </c>
       <c r="E25">
-        <v>-8.111000000000001</v>
+        <v>-6.868000000000002</v>
       </c>
       <c r="F25">
-        <v>28.589</v>
+        <v>29.832</v>
       </c>
       <c r="G25">
         <v>2.19</v>
@@ -3337,28 +3337,28 @@
         <v>11.34222222222222</v>
       </c>
       <c r="M25">
-        <v>1.5523827</v>
+        <v>1.6198776</v>
       </c>
       <c r="N25">
-        <v>9.789839522222222</v>
+        <v>9.722344622222222</v>
       </c>
       <c r="O25">
-        <v>1.957967904444444</v>
+        <v>1.944468924444444</v>
       </c>
       <c r="P25">
-        <v>7.831871617777777</v>
+        <v>7.777875697777778</v>
       </c>
       <c r="Q25">
-        <v>11.71187161777778</v>
+        <v>11.65787569777778</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1177045662958258</v>
+        <v>0.1184979522198667</v>
       </c>
       <c r="T25">
-        <v>1.364003052250739</v>
+        <v>1.379053290055558</v>
       </c>
       <c r="U25">
         <v>0.0543</v>
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>7.306331243076994</v>
+        <v>7.001900774615453</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3383,22 +3383,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1004840436870987</v>
+        <v>0.1003443713264115</v>
       </c>
       <c r="C26">
-        <v>95.07247087981951</v>
+        <v>94.12534385432977</v>
       </c>
       <c r="D26">
-        <v>122.7144708798195</v>
+        <v>123.0103438543298</v>
       </c>
       <c r="E26">
-        <v>-6.868000000000006</v>
+        <v>-5.625000000000004</v>
       </c>
       <c r="F26">
-        <v>29.832</v>
+        <v>31.075</v>
       </c>
       <c r="G26">
         <v>2.19</v>
@@ -3419,28 +3419,28 @@
         <v>11.34222222222222</v>
       </c>
       <c r="M26">
-        <v>1.6198776</v>
+        <v>1.6873725</v>
       </c>
       <c r="N26">
-        <v>9.722344622222222</v>
+        <v>9.654849722222222</v>
       </c>
       <c r="O26">
-        <v>1.944468924444444</v>
+        <v>1.930969944444445</v>
       </c>
       <c r="P26">
-        <v>7.777875697777778</v>
+        <v>7.723879777777777</v>
       </c>
       <c r="Q26">
-        <v>11.65787569777778</v>
+        <v>11.60387977777778</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1184979522198667</v>
+        <v>0.119312495101882</v>
       </c>
       <c r="T26">
-        <v>1.379053290055558</v>
+        <v>1.394504867535172</v>
       </c>
       <c r="U26">
         <v>0.0543</v>
@@ -3457,7 +3457,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>7.001900774615454</v>
+        <v>6.721824743630836</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3465,22 +3465,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1003443713264115</v>
+        <v>0.1002046989657243</v>
       </c>
       <c r="C27">
-        <v>94.12534385432977</v>
+        <v>93.17964701703923</v>
       </c>
       <c r="D27">
-        <v>123.0103438543298</v>
+        <v>123.3076470170392</v>
       </c>
       <c r="E27">
-        <v>-5.625000000000004</v>
+        <v>-4.382000000000005</v>
       </c>
       <c r="F27">
-        <v>31.075</v>
+        <v>32.318</v>
       </c>
       <c r="G27">
         <v>2.19</v>
@@ -3501,28 +3501,28 @@
         <v>11.34222222222222</v>
       </c>
       <c r="M27">
-        <v>1.6873725</v>
+        <v>1.7548674</v>
       </c>
       <c r="N27">
-        <v>9.654849722222222</v>
+        <v>9.587354822222222</v>
       </c>
       <c r="O27">
-        <v>1.930969944444445</v>
+        <v>1.917470964444445</v>
       </c>
       <c r="P27">
-        <v>7.723879777777777</v>
+        <v>7.669883857777778</v>
       </c>
       <c r="Q27">
-        <v>11.60387977777778</v>
+        <v>11.54988385777778</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.119312495101882</v>
+        <v>0.1201490526563842</v>
       </c>
       <c r="T27">
-        <v>1.394504867535172</v>
+        <v>1.410374055216938</v>
       </c>
       <c r="U27">
         <v>0.0543</v>
@@ -3539,7 +3539,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>6.721824743630836</v>
+        <v>6.463293022721958</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3547,22 +3547,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1002046989657243</v>
+        <v>0.1000650266050371</v>
       </c>
       <c r="C28">
-        <v>93.17964701703923</v>
+        <v>92.2353907629184</v>
       </c>
       <c r="D28">
-        <v>123.3076470170392</v>
+        <v>123.6063907629184</v>
       </c>
       <c r="E28">
-        <v>-4.382000000000005</v>
+        <v>-3.139000000000003</v>
       </c>
       <c r="F28">
-        <v>32.318</v>
+        <v>33.561</v>
       </c>
       <c r="G28">
         <v>2.19</v>
@@ -3583,28 +3583,28 @@
         <v>11.34222222222222</v>
       </c>
       <c r="M28">
-        <v>1.7548674</v>
+        <v>1.8223623</v>
       </c>
       <c r="N28">
-        <v>9.587354822222222</v>
+        <v>9.519859922222222</v>
       </c>
       <c r="O28">
-        <v>1.917470964444445</v>
+        <v>1.903971984444444</v>
       </c>
       <c r="P28">
-        <v>7.669883857777778</v>
+        <v>7.615887937777778</v>
       </c>
       <c r="Q28">
-        <v>11.54988385777778</v>
+        <v>11.49588793777778</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1201490526563842</v>
+        <v>0.1210085295959413</v>
       </c>
       <c r="T28">
-        <v>1.410374055216938</v>
+        <v>1.426678015163958</v>
       </c>
       <c r="U28">
         <v>0.0543</v>
@@ -3621,7 +3621,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>6.463293022721958</v>
+        <v>6.223911799658182</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3629,22 +3629,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1000650266050371</v>
+        <v>0.10014935424435</v>
       </c>
       <c r="C29">
-        <v>92.2353907629184</v>
+        <v>90.81185035932069</v>
       </c>
       <c r="D29">
-        <v>123.6063907629184</v>
+        <v>123.4258503593207</v>
       </c>
       <c r="E29">
-        <v>-3.139000000000003</v>
+        <v>-1.896000000000001</v>
       </c>
       <c r="F29">
-        <v>33.561</v>
+        <v>34.804</v>
       </c>
       <c r="G29">
         <v>2.19</v>
@@ -3665,45 +3665,45 @@
         <v>11.34222222222222</v>
       </c>
       <c r="M29">
-        <v>1.8223623</v>
+        <v>1.9246612</v>
       </c>
       <c r="N29">
-        <v>9.519859922222222</v>
+        <v>9.417561022222223</v>
       </c>
       <c r="O29">
-        <v>1.903971984444444</v>
+        <v>1.883512204444445</v>
       </c>
       <c r="P29">
-        <v>7.615887937777778</v>
+        <v>7.534048817777778</v>
       </c>
       <c r="Q29">
-        <v>11.49588793777778</v>
+        <v>11.41404881777778</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1210085295959413</v>
+        <v>0.1218918808949305</v>
       </c>
       <c r="T29">
-        <v>1.426678015163958</v>
+        <v>1.443434862887284</v>
       </c>
       <c r="U29">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V29">
         <v>0.2</v>
       </c>
       <c r="W29">
-        <v>0.04344000000000001</v>
+        <v>0.04424</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y29">
-        <v>6.223911799658182</v>
+        <v>5.893100677782782</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3711,22 +3711,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.10014935424435</v>
+        <v>0.1000176818836628</v>
       </c>
       <c r="C30">
-        <v>90.81185035932069</v>
+        <v>89.85098466354654</v>
       </c>
       <c r="D30">
-        <v>123.4258503593207</v>
+        <v>123.7079846635465</v>
       </c>
       <c r="E30">
-        <v>-1.896000000000001</v>
+        <v>-0.6529999999999987</v>
       </c>
       <c r="F30">
-        <v>34.804</v>
+        <v>36.047</v>
       </c>
       <c r="G30">
         <v>2.19</v>
@@ -3747,28 +3747,28 @@
         <v>11.34222222222222</v>
       </c>
       <c r="M30">
-        <v>1.9246612</v>
+        <v>1.9933991</v>
       </c>
       <c r="N30">
-        <v>9.417561022222223</v>
+        <v>9.348823122222223</v>
       </c>
       <c r="O30">
-        <v>1.883512204444445</v>
+        <v>1.869764624444445</v>
       </c>
       <c r="P30">
-        <v>7.534048817777778</v>
+        <v>7.479058497777778</v>
       </c>
       <c r="Q30">
-        <v>11.41404881777778</v>
+        <v>11.35905849777778</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1218918808949305</v>
+        <v>0.1228001153291025</v>
       </c>
       <c r="T30">
-        <v>1.443434862887284</v>
+        <v>1.46066373449014</v>
       </c>
       <c r="U30">
         <v>0.0553</v>
@@ -3785,7 +3785,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>5.893100677782782</v>
+        <v>5.689890309583375</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3793,22 +3793,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1000176818836628</v>
+        <v>0.09988600952297561</v>
       </c>
       <c r="C31">
-        <v>89.85098466354654</v>
+        <v>88.8914117623732</v>
       </c>
       <c r="D31">
-        <v>123.7079846635465</v>
+        <v>123.9914117623732</v>
       </c>
       <c r="E31">
-        <v>-0.6530000000000058</v>
+        <v>0.5899999999999963</v>
       </c>
       <c r="F31">
-        <v>36.047</v>
+        <v>37.29</v>
       </c>
       <c r="G31">
         <v>2.19</v>
@@ -3829,28 +3829,28 @@
         <v>11.34222222222222</v>
       </c>
       <c r="M31">
-        <v>1.9933991</v>
+        <v>2.062137</v>
       </c>
       <c r="N31">
-        <v>9.348823122222223</v>
+        <v>9.280085222222223</v>
       </c>
       <c r="O31">
-        <v>1.869764624444445</v>
+        <v>1.856017044444445</v>
       </c>
       <c r="P31">
-        <v>7.479058497777778</v>
+        <v>7.424068177777778</v>
       </c>
       <c r="Q31">
-        <v>11.35905849777778</v>
+        <v>11.30406817777778</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1228001153291025</v>
+        <v>0.1237342993185366</v>
       </c>
       <c r="T31">
-        <v>1.46066373449014</v>
+        <v>1.478384859567363</v>
       </c>
       <c r="U31">
         <v>0.0553</v>
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>5.689890309583376</v>
+        <v>5.50022729926393</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.09988600952297561</v>
+        <v>0.0997543371622884</v>
       </c>
       <c r="C32">
-        <v>88.8914117623732</v>
+        <v>87.93314056196245</v>
       </c>
       <c r="D32">
-        <v>123.9914117623732</v>
+        <v>124.2761405619624</v>
       </c>
       <c r="E32">
-        <v>0.5899999999999963</v>
+        <v>1.832999999999998</v>
       </c>
       <c r="F32">
-        <v>37.29</v>
+        <v>38.533</v>
       </c>
       <c r="G32">
         <v>2.19</v>
@@ -3911,28 +3911,28 @@
         <v>11.34222222222222</v>
       </c>
       <c r="M32">
-        <v>2.062137</v>
+        <v>2.1308749</v>
       </c>
       <c r="N32">
-        <v>9.280085222222223</v>
+        <v>9.211347322222222</v>
       </c>
       <c r="O32">
-        <v>1.856017044444445</v>
+        <v>1.842269464444445</v>
       </c>
       <c r="P32">
-        <v>7.424068177777778</v>
+        <v>7.369077857777778</v>
       </c>
       <c r="Q32">
-        <v>11.30406817777778</v>
+        <v>11.24907785777778</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1237342993185366</v>
+        <v>0.1246955611047658</v>
       </c>
       <c r="T32">
-        <v>1.478384859567363</v>
+        <v>1.496619640443926</v>
       </c>
       <c r="U32">
         <v>0.0553</v>
@@ -3949,7 +3949,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>5.50022729926393</v>
+        <v>5.322800612190899</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3957,22 +3957,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.0997543371622884</v>
+        <v>0.09962266480160122</v>
       </c>
       <c r="C33">
-        <v>87.93314056196245</v>
+        <v>86.97618005047119</v>
       </c>
       <c r="D33">
-        <v>124.2761405619624</v>
+        <v>124.5621800504712</v>
       </c>
       <c r="E33">
-        <v>1.832999999999998</v>
+        <v>3.076000000000001</v>
       </c>
       <c r="F33">
-        <v>38.533</v>
+        <v>39.776</v>
       </c>
       <c r="G33">
         <v>2.19</v>
@@ -3993,28 +3993,28 @@
         <v>11.34222222222222</v>
       </c>
       <c r="M33">
-        <v>2.1308749</v>
+        <v>2.1996128</v>
       </c>
       <c r="N33">
-        <v>9.211347322222222</v>
+        <v>9.142609422222222</v>
       </c>
       <c r="O33">
-        <v>1.842269464444445</v>
+        <v>1.828521884444444</v>
       </c>
       <c r="P33">
-        <v>7.369077857777778</v>
+        <v>7.314087537777778</v>
       </c>
       <c r="Q33">
-        <v>11.24907785777778</v>
+        <v>11.19408753777778</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1246955611047658</v>
+        <v>0.1256850952964724</v>
       </c>
       <c r="T33">
-        <v>1.496619640443926</v>
+        <v>1.515390738405094</v>
       </c>
       <c r="U33">
         <v>0.0553</v>
@@ -4031,7 +4031,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>5.322800612190899</v>
+        <v>5.156463093059934</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4039,22 +4039,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.09962266480160122</v>
+        <v>0.09949099244091404</v>
       </c>
       <c r="C34">
-        <v>86.97618005047119</v>
+        <v>86.02053929899751</v>
       </c>
       <c r="D34">
-        <v>124.5621800504712</v>
+        <v>124.8495392989975</v>
       </c>
       <c r="E34">
-        <v>3.076000000000001</v>
+        <v>4.318999999999996</v>
       </c>
       <c r="F34">
-        <v>39.776</v>
+        <v>41.019</v>
       </c>
       <c r="G34">
         <v>2.19</v>
@@ -4075,28 +4075,28 @@
         <v>11.34222222222222</v>
       </c>
       <c r="M34">
-        <v>2.1996128</v>
+        <v>2.2683507</v>
       </c>
       <c r="N34">
-        <v>9.142609422222222</v>
+        <v>9.073871522222223</v>
       </c>
       <c r="O34">
-        <v>1.828521884444444</v>
+        <v>1.814774304444445</v>
       </c>
       <c r="P34">
-        <v>7.314087537777778</v>
+        <v>7.259097217777779</v>
       </c>
       <c r="Q34">
-        <v>11.19408753777778</v>
+        <v>11.13909721777778</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1256850952964724</v>
+        <v>0.1267041678222598</v>
       </c>
       <c r="T34">
-        <v>1.515390738405094</v>
+        <v>1.534722167648685</v>
       </c>
       <c r="U34">
         <v>0.0553</v>
@@ -4113,7 +4113,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>5.156463093059934</v>
+        <v>5.000206635694482</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4121,22 +4121,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.09949099244091404</v>
+        <v>0.09935932008022685</v>
       </c>
       <c r="C35">
-        <v>86.02053929899751</v>
+        <v>85.06622746253947</v>
       </c>
       <c r="D35">
-        <v>124.8495392989975</v>
+        <v>125.1382274625395</v>
       </c>
       <c r="E35">
-        <v>4.318999999999996</v>
+        <v>5.561999999999998</v>
       </c>
       <c r="F35">
-        <v>41.019</v>
+        <v>42.262</v>
       </c>
       <c r="G35">
         <v>2.19</v>
@@ -4157,28 +4157,28 @@
         <v>11.34222222222222</v>
       </c>
       <c r="M35">
-        <v>2.2683507</v>
+        <v>2.3370886</v>
       </c>
       <c r="N35">
-        <v>9.073871522222223</v>
+        <v>9.005133622222223</v>
       </c>
       <c r="O35">
-        <v>1.814774304444445</v>
+        <v>1.801026724444445</v>
       </c>
       <c r="P35">
-        <v>7.259097217777779</v>
+        <v>7.204106897777779</v>
       </c>
       <c r="Q35">
-        <v>11.13909721777778</v>
+        <v>11.08410689777778</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1267041678222598</v>
+        <v>0.1277541213336771</v>
       </c>
       <c r="T35">
-        <v>1.534722167648685</v>
+        <v>1.554639397778446</v>
       </c>
       <c r="U35">
         <v>0.0553</v>
@@ -4195,7 +4195,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>5.000206635694482</v>
+        <v>4.853141734644645</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4203,22 +4203,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.09935932008022685</v>
+        <v>0.09922764771953967</v>
       </c>
       <c r="C36">
-        <v>85.06622746253947</v>
+        <v>84.11325378096734</v>
       </c>
       <c r="D36">
-        <v>125.1382274625395</v>
+        <v>125.4282537809674</v>
       </c>
       <c r="E36">
-        <v>5.561999999999998</v>
+        <v>6.805</v>
       </c>
       <c r="F36">
-        <v>42.262</v>
+        <v>43.505</v>
       </c>
       <c r="G36">
         <v>2.19</v>
@@ -4239,28 +4239,28 @@
         <v>11.34222222222222</v>
       </c>
       <c r="M36">
-        <v>2.3370886</v>
+        <v>2.4058265</v>
       </c>
       <c r="N36">
-        <v>9.005133622222223</v>
+        <v>8.936395722222223</v>
       </c>
       <c r="O36">
-        <v>1.801026724444445</v>
+        <v>1.787279144444445</v>
       </c>
       <c r="P36">
-        <v>7.204106897777779</v>
+        <v>7.149116577777778</v>
       </c>
       <c r="Q36">
-        <v>11.08410689777778</v>
+        <v>11.02911657777778</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1277541213336771</v>
+        <v>0.1288363811069841</v>
       </c>
       <c r="T36">
-        <v>1.554639397778446</v>
+        <v>1.575169465758352</v>
       </c>
       <c r="U36">
         <v>0.0553</v>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>4.853141734644645</v>
+        <v>4.714480542226225</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4285,22 +4285,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.09922764771953967</v>
+        <v>0.09909597535885251</v>
       </c>
       <c r="C37">
-        <v>84.11325378096734</v>
+        <v>83.16162758000934</v>
       </c>
       <c r="D37">
-        <v>125.4282537809674</v>
+        <v>125.7196275800093</v>
       </c>
       <c r="E37">
-        <v>6.805</v>
+        <v>8.048000000000002</v>
       </c>
       <c r="F37">
-        <v>43.505</v>
+        <v>44.748</v>
       </c>
       <c r="G37">
         <v>2.19</v>
@@ -4321,28 +4321,28 @@
         <v>11.34222222222222</v>
       </c>
       <c r="M37">
-        <v>2.4058265</v>
+        <v>2.4745644</v>
       </c>
       <c r="N37">
-        <v>8.936395722222223</v>
+        <v>8.867657822222222</v>
       </c>
       <c r="O37">
-        <v>1.787279144444445</v>
+        <v>1.773531564444444</v>
       </c>
       <c r="P37">
-        <v>7.149116577777778</v>
+        <v>7.094126257777778</v>
       </c>
       <c r="Q37">
-        <v>11.02911657777778</v>
+        <v>10.97412625777778</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1288363811069841</v>
+        <v>0.1299524614982071</v>
       </c>
       <c r="T37">
-        <v>1.575169465758352</v>
+        <v>1.596341098362632</v>
       </c>
       <c r="U37">
         <v>0.0553</v>
@@ -4359,7 +4359,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>4.714480542226225</v>
+        <v>4.583522749386608</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4367,22 +4367,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.09909597535885251</v>
+        <v>0.09970430299816532</v>
       </c>
       <c r="C38">
-        <v>83.16162758000934</v>
+        <v>80.58367778470904</v>
       </c>
       <c r="D38">
-        <v>125.7196275800093</v>
+        <v>124.384677784709</v>
       </c>
       <c r="E38">
-        <v>8.047999999999995</v>
+        <v>9.290999999999997</v>
       </c>
       <c r="F38">
-        <v>44.748</v>
+        <v>45.991</v>
       </c>
       <c r="G38">
         <v>2.19</v>
@@ -4403,45 +4403,45 @@
         <v>11.34222222222222</v>
       </c>
       <c r="M38">
-        <v>2.4745644</v>
+        <v>2.6582798</v>
       </c>
       <c r="N38">
-        <v>8.867657822222222</v>
+        <v>8.683942422222222</v>
       </c>
       <c r="O38">
-        <v>1.773531564444444</v>
+        <v>1.736788484444444</v>
       </c>
       <c r="P38">
-        <v>7.094126257777778</v>
+        <v>6.947153937777777</v>
       </c>
       <c r="Q38">
-        <v>10.97412625777778</v>
+        <v>10.82715393777778</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.129952461498207</v>
+        <v>0.1311039730129608</v>
       </c>
       <c r="T38">
-        <v>1.596341098362631</v>
+        <v>1.618184846287681</v>
       </c>
       <c r="U38">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V38">
         <v>0.2</v>
       </c>
       <c r="W38">
-        <v>0.04424</v>
+        <v>0.04624</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y38">
-        <v>4.583522749386608</v>
+        <v>4.26675259023607</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4449,22 +4449,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.09970430299816532</v>
+        <v>0.09959263063747811</v>
       </c>
       <c r="C39">
-        <v>80.58367778470904</v>
+        <v>79.58360952430633</v>
       </c>
       <c r="D39">
-        <v>124.384677784709</v>
+        <v>124.6276095243063</v>
       </c>
       <c r="E39">
-        <v>9.290999999999997</v>
+        <v>10.534</v>
       </c>
       <c r="F39">
-        <v>45.991</v>
+        <v>47.234</v>
       </c>
       <c r="G39">
         <v>2.19</v>
@@ -4485,28 +4485,28 @@
         <v>11.34222222222222</v>
       </c>
       <c r="M39">
-        <v>2.6582798</v>
+        <v>2.7301252</v>
       </c>
       <c r="N39">
-        <v>8.683942422222222</v>
+        <v>8.612097022222223</v>
       </c>
       <c r="O39">
-        <v>1.736788484444444</v>
+        <v>1.722419404444445</v>
       </c>
       <c r="P39">
-        <v>6.947153937777777</v>
+        <v>6.889677617777778</v>
       </c>
       <c r="Q39">
-        <v>10.82715393777778</v>
+        <v>10.76967761777778</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1311039730129608</v>
+        <v>0.1322926300604486</v>
       </c>
       <c r="T39">
-        <v>1.618184846287681</v>
+        <v>1.640733231242571</v>
       </c>
       <c r="U39">
         <v>0.0578</v>
@@ -4523,7 +4523,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>4.26675259023607</v>
+        <v>4.15446962733512</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4531,22 +4531,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.09959263063747811</v>
+        <v>0.09948095827679095</v>
       </c>
       <c r="C40">
-        <v>79.58360952430633</v>
+        <v>78.58449204528019</v>
       </c>
       <c r="D40">
-        <v>124.6276095243063</v>
+        <v>124.8714920452802</v>
       </c>
       <c r="E40">
-        <v>10.534</v>
+        <v>11.777</v>
       </c>
       <c r="F40">
-        <v>47.234</v>
+        <v>48.477</v>
       </c>
       <c r="G40">
         <v>2.19</v>
@@ -4567,28 +4567,28 @@
         <v>11.34222222222222</v>
       </c>
       <c r="M40">
-        <v>2.7301252</v>
+        <v>2.801970600000001</v>
       </c>
       <c r="N40">
-        <v>8.612097022222223</v>
+        <v>8.540251622222222</v>
       </c>
       <c r="O40">
-        <v>1.722419404444445</v>
+        <v>1.708050324444444</v>
       </c>
       <c r="P40">
-        <v>6.889677617777778</v>
+        <v>6.832201297777777</v>
       </c>
       <c r="Q40">
-        <v>10.76967761777778</v>
+        <v>10.71220129777778</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1322926300604486</v>
+        <v>0.1335202594701491</v>
       </c>
       <c r="T40">
-        <v>1.640733231242571</v>
+        <v>1.664020907507457</v>
       </c>
       <c r="U40">
         <v>0.0578</v>
@@ -4605,7 +4605,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>4.15446962733512</v>
+        <v>4.047944765095759</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4613,22 +4613,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.09948095827679095</v>
+        <v>0.1004892859161038</v>
       </c>
       <c r="C41">
-        <v>78.58449204528019</v>
+        <v>75.17339378799819</v>
       </c>
       <c r="D41">
-        <v>124.8714920452802</v>
+        <v>122.7033937879982</v>
       </c>
       <c r="E41">
-        <v>11.777</v>
+        <v>13.02</v>
       </c>
       <c r="F41">
-        <v>48.477</v>
+        <v>49.72</v>
       </c>
       <c r="G41">
         <v>2.19</v>
@@ -4649,45 +4649,45 @@
         <v>11.34222222222222</v>
       </c>
       <c r="M41">
-        <v>2.801970600000001</v>
+        <v>3.047836</v>
       </c>
       <c r="N41">
-        <v>8.540251622222222</v>
+        <v>8.294386222222222</v>
       </c>
       <c r="O41">
-        <v>1.708050324444444</v>
+        <v>1.658877244444445</v>
       </c>
       <c r="P41">
-        <v>6.832201297777777</v>
+        <v>6.635508977777778</v>
       </c>
       <c r="Q41">
-        <v>10.71220129777778</v>
+        <v>10.51550897777778</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1335202594701491</v>
+        <v>0.1347888098601729</v>
       </c>
       <c r="T41">
-        <v>1.664020907507457</v>
+        <v>1.68808483964784</v>
       </c>
       <c r="U41">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V41">
         <v>0.2</v>
       </c>
       <c r="W41">
-        <v>0.04624</v>
+        <v>0.04904</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y41">
-        <v>4.047944765095759</v>
+        <v>3.721401749379633</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4695,22 +4695,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1004892859161038</v>
+        <v>0.1004056135554166</v>
       </c>
       <c r="C42">
-        <v>75.17339378799819</v>
+        <v>74.10743678635367</v>
       </c>
       <c r="D42">
-        <v>122.7033937879982</v>
+        <v>122.8804367863537</v>
       </c>
       <c r="E42">
-        <v>13.02</v>
+        <v>14.263</v>
       </c>
       <c r="F42">
-        <v>49.72</v>
+        <v>50.963</v>
       </c>
       <c r="G42">
         <v>2.19</v>
@@ -4731,28 +4731,28 @@
         <v>11.34222222222222</v>
       </c>
       <c r="M42">
-        <v>3.047836</v>
+        <v>3.1240319</v>
       </c>
       <c r="N42">
-        <v>8.294386222222222</v>
+        <v>8.218190322222222</v>
       </c>
       <c r="O42">
-        <v>1.658877244444445</v>
+        <v>1.643638064444445</v>
       </c>
       <c r="P42">
-        <v>6.635508977777778</v>
+        <v>6.574552257777778</v>
       </c>
       <c r="Q42">
-        <v>10.51550897777778</v>
+        <v>10.45455225777778</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1347888098601729</v>
+        <v>0.1361003619583332</v>
       </c>
       <c r="T42">
-        <v>1.68808483964784</v>
+        <v>1.712964498301456</v>
       </c>
       <c r="U42">
         <v>0.0613</v>
@@ -4769,7 +4769,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>3.721401749379633</v>
+        <v>3.6306358530533</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4777,22 +4777,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1004056135554166</v>
+        <v>0.1003219411947294</v>
       </c>
       <c r="C43">
-        <v>74.10743678635367</v>
+        <v>73.04199141707338</v>
       </c>
       <c r="D43">
-        <v>122.8804367863537</v>
+        <v>123.0579914170734</v>
       </c>
       <c r="E43">
-        <v>14.263</v>
+        <v>15.506</v>
       </c>
       <c r="F43">
-        <v>50.963</v>
+        <v>52.206</v>
       </c>
       <c r="G43">
         <v>2.19</v>
@@ -4813,28 +4813,28 @@
         <v>11.34222222222222</v>
       </c>
       <c r="M43">
-        <v>3.1240319</v>
+        <v>3.2002278</v>
       </c>
       <c r="N43">
-        <v>8.218190322222222</v>
+        <v>8.141994422222222</v>
       </c>
       <c r="O43">
-        <v>1.643638064444445</v>
+        <v>1.628398884444445</v>
       </c>
       <c r="P43">
-        <v>6.574552257777778</v>
+        <v>6.513595537777777</v>
       </c>
       <c r="Q43">
-        <v>10.45455225777778</v>
+        <v>10.39359553777778</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1361003619583332</v>
+        <v>0.1374571399909128</v>
       </c>
       <c r="T43">
-        <v>1.712964498301456</v>
+        <v>1.73870207621899</v>
       </c>
       <c r="U43">
         <v>0.0613</v>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>3.6306358530533</v>
+        <v>3.544192142266316</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4859,22 +4859,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1003219411947294</v>
+        <v>0.1012014688340422</v>
       </c>
       <c r="C44">
-        <v>73.04199141707338</v>
+        <v>69.95788101456104</v>
       </c>
       <c r="D44">
-        <v>123.0579914170734</v>
+        <v>121.216881014561</v>
       </c>
       <c r="E44">
-        <v>15.50599999999999</v>
+        <v>16.749</v>
       </c>
       <c r="F44">
-        <v>52.206</v>
+        <v>53.449</v>
       </c>
       <c r="G44">
         <v>2.19</v>
@@ -4895,45 +4895,45 @@
         <v>11.34222222222222</v>
       </c>
       <c r="M44">
-        <v>3.2002278</v>
+        <v>3.4260809</v>
       </c>
       <c r="N44">
-        <v>8.141994422222222</v>
+        <v>7.916141322222222</v>
       </c>
       <c r="O44">
-        <v>1.628398884444445</v>
+        <v>1.583228264444444</v>
       </c>
       <c r="P44">
-        <v>6.513595537777777</v>
+        <v>6.332913057777778</v>
       </c>
       <c r="Q44">
-        <v>10.39359553777778</v>
+        <v>10.21291305777778</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1374571399909127</v>
+        <v>0.1388615242702495</v>
       </c>
       <c r="T44">
-        <v>1.73870207621899</v>
+        <v>1.765342727045911</v>
       </c>
       <c r="U44">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V44">
         <v>0.2</v>
       </c>
       <c r="W44">
-        <v>0.04904</v>
+        <v>0.05128000000000001</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y44">
-        <v>3.544192142266317</v>
+        <v>3.310552947603258</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1012014688340422</v>
+        <v>0.1011401964733551</v>
       </c>
       <c r="C45">
-        <v>69.95788101456104</v>
+        <v>68.84135497819881</v>
       </c>
       <c r="D45">
-        <v>121.216881014561</v>
+        <v>121.3433549781988</v>
       </c>
       <c r="E45">
-        <v>16.749</v>
+        <v>17.992</v>
       </c>
       <c r="F45">
-        <v>53.449</v>
+        <v>54.692</v>
       </c>
       <c r="G45">
         <v>2.19</v>
@@ -4977,28 +4977,28 @@
         <v>11.34222222222222</v>
       </c>
       <c r="M45">
-        <v>3.4260809</v>
+        <v>3.5057572</v>
       </c>
       <c r="N45">
-        <v>7.916141322222222</v>
+        <v>7.836465022222223</v>
       </c>
       <c r="O45">
-        <v>1.583228264444444</v>
+        <v>1.567293004444445</v>
       </c>
       <c r="P45">
-        <v>6.332913057777778</v>
+        <v>6.269172017777779</v>
       </c>
       <c r="Q45">
-        <v>10.21291305777778</v>
+        <v>10.14917201777778</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1388615242702495</v>
+        <v>0.1403160651309912</v>
       </c>
       <c r="T45">
-        <v>1.765342727045911</v>
+        <v>1.792934829688078</v>
       </c>
       <c r="U45">
         <v>0.0641</v>
@@ -5015,7 +5015,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>3.310552947603258</v>
+        <v>3.235313107885002</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5023,22 +5023,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1011401964733551</v>
+        <v>0.1010789241126679</v>
       </c>
       <c r="C46">
-        <v>68.84135497819881</v>
+        <v>67.72509313557197</v>
       </c>
       <c r="D46">
-        <v>121.3433549781988</v>
+        <v>121.470093135572</v>
       </c>
       <c r="E46">
-        <v>17.992</v>
+        <v>19.235</v>
       </c>
       <c r="F46">
-        <v>54.692</v>
+        <v>55.935</v>
       </c>
       <c r="G46">
         <v>2.19</v>
@@ -5059,28 +5059,28 @@
         <v>11.34222222222222</v>
       </c>
       <c r="M46">
-        <v>3.5057572</v>
+        <v>3.5854335</v>
       </c>
       <c r="N46">
-        <v>7.836465022222223</v>
+        <v>7.756788722222222</v>
       </c>
       <c r="O46">
-        <v>1.567293004444445</v>
+        <v>1.551357744444444</v>
       </c>
       <c r="P46">
-        <v>6.269172017777779</v>
+        <v>6.205430977777778</v>
       </c>
       <c r="Q46">
-        <v>10.14917201777778</v>
+        <v>10.08543097777778</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1403160651309912</v>
+        <v>0.1418234983866688</v>
       </c>
       <c r="T46">
-        <v>1.792934829688078</v>
+        <v>1.821530281517235</v>
       </c>
       <c r="U46">
         <v>0.0641</v>
@@ -5097,7 +5097,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>3.235313107885002</v>
+        <v>3.163417261043113</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5105,22 +5105,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1010789241126679</v>
+        <v>0.1010176517519807</v>
       </c>
       <c r="C47">
-        <v>67.72509313557197</v>
+        <v>66.60909631536458</v>
       </c>
       <c r="D47">
-        <v>121.470093135572</v>
+        <v>121.5970963153646</v>
       </c>
       <c r="E47">
-        <v>19.235</v>
+        <v>20.478</v>
       </c>
       <c r="F47">
-        <v>55.935</v>
+        <v>57.178</v>
       </c>
       <c r="G47">
         <v>2.19</v>
@@ -5141,28 +5141,28 @@
         <v>11.34222222222222</v>
       </c>
       <c r="M47">
-        <v>3.5854335</v>
+        <v>3.665109800000001</v>
       </c>
       <c r="N47">
-        <v>7.756788722222222</v>
+        <v>7.677112422222222</v>
       </c>
       <c r="O47">
-        <v>1.551357744444444</v>
+        <v>1.535422484444444</v>
       </c>
       <c r="P47">
-        <v>6.205430977777778</v>
+        <v>6.141689937777778</v>
       </c>
       <c r="Q47">
-        <v>10.08543097777778</v>
+        <v>10.02168993777778</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1418234983866688</v>
+        <v>0.1433867625036679</v>
       </c>
       <c r="T47">
-        <v>1.821530281517235</v>
+        <v>1.851184824154878</v>
       </c>
       <c r="U47">
         <v>0.0641</v>
@@ -5179,7 +5179,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>3.163417261043113</v>
+        <v>3.094647320585654</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5187,22 +5187,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1010176517519807</v>
+        <v>0.1009563793912935</v>
       </c>
       <c r="C48">
-        <v>66.60909631536458</v>
+        <v>65.49336534973011</v>
       </c>
       <c r="D48">
-        <v>121.5970963153646</v>
+        <v>121.7243653497301</v>
       </c>
       <c r="E48">
-        <v>20.478</v>
+        <v>21.721</v>
       </c>
       <c r="F48">
-        <v>57.178</v>
+        <v>58.421</v>
       </c>
       <c r="G48">
         <v>2.19</v>
@@ -5223,28 +5223,28 @@
         <v>11.34222222222222</v>
       </c>
       <c r="M48">
-        <v>3.665109800000001</v>
+        <v>3.7447861</v>
       </c>
       <c r="N48">
-        <v>7.677112422222222</v>
+        <v>7.597436122222222</v>
       </c>
       <c r="O48">
-        <v>1.535422484444444</v>
+        <v>1.519487224444444</v>
       </c>
       <c r="P48">
-        <v>6.141689937777778</v>
+        <v>6.077948897777778</v>
       </c>
       <c r="Q48">
-        <v>10.02168993777778</v>
+        <v>9.957948897777776</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1433867625036679</v>
+        <v>0.1450090177194217</v>
       </c>
       <c r="T48">
-        <v>1.851184824154878</v>
+        <v>1.881958406137338</v>
       </c>
       <c r="U48">
         <v>0.0641</v>
@@ -5261,7 +5261,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>3.094647320585654</v>
+        <v>3.028803760573193</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5269,22 +5269,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1009563793912935</v>
+        <v>0.1038903070306063</v>
       </c>
       <c r="C49">
-        <v>65.49336534973011</v>
+        <v>58.44106012877251</v>
       </c>
       <c r="D49">
-        <v>121.7243653497301</v>
+        <v>115.9150601287725</v>
       </c>
       <c r="E49">
-        <v>21.721</v>
+        <v>22.964</v>
       </c>
       <c r="F49">
-        <v>58.421</v>
+        <v>59.664</v>
       </c>
       <c r="G49">
         <v>2.19</v>
@@ -5305,45 +5305,45 @@
         <v>11.34222222222222</v>
       </c>
       <c r="M49">
-        <v>3.7447861</v>
+        <v>4.289841600000001</v>
       </c>
       <c r="N49">
-        <v>7.597436122222222</v>
+        <v>7.052380622222222</v>
       </c>
       <c r="O49">
-        <v>1.519487224444444</v>
+        <v>1.410476124444444</v>
       </c>
       <c r="P49">
-        <v>6.077948897777778</v>
+        <v>5.641904497777777</v>
       </c>
       <c r="Q49">
-        <v>9.957948897777776</v>
+        <v>9.521904497777776</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1450090177194217</v>
+        <v>0.1466936673665506</v>
       </c>
       <c r="T49">
-        <v>1.881958406137338</v>
+        <v>1.913915587426815</v>
       </c>
       <c r="U49">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V49">
         <v>0.2</v>
       </c>
       <c r="W49">
-        <v>0.05128000000000001</v>
+        <v>0.05752000000000001</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y49">
-        <v>3.028803760573193</v>
+        <v>2.643972267466058</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5351,22 +5351,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1038903070306063</v>
+        <v>0.1038914346699191</v>
       </c>
       <c r="C50">
-        <v>58.44106012877251</v>
+        <v>57.19593395192591</v>
       </c>
       <c r="D50">
-        <v>115.9150601287725</v>
+        <v>115.9129339519259</v>
       </c>
       <c r="E50">
-        <v>22.96399999999999</v>
+        <v>24.20699999999999</v>
       </c>
       <c r="F50">
-        <v>59.66399999999999</v>
+        <v>60.907</v>
       </c>
       <c r="G50">
         <v>2.19</v>
@@ -5387,28 +5387,28 @@
         <v>11.34222222222222</v>
       </c>
       <c r="M50">
-        <v>4.2898416</v>
+        <v>4.3792133</v>
       </c>
       <c r="N50">
-        <v>7.052380622222223</v>
+        <v>6.963008922222222</v>
       </c>
       <c r="O50">
-        <v>1.410476124444445</v>
+        <v>1.392601784444444</v>
       </c>
       <c r="P50">
-        <v>5.641904497777778</v>
+        <v>5.570407137777778</v>
       </c>
       <c r="Q50">
-        <v>9.521904497777777</v>
+        <v>9.450407137777777</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1466936673665506</v>
+        <v>0.1484443817057238</v>
       </c>
       <c r="T50">
-        <v>1.913915587426815</v>
+        <v>1.947125991511959</v>
       </c>
       <c r="U50">
         <v>0.07190000000000001</v>
@@ -5425,7 +5425,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>2.643972267466058</v>
+        <v>2.590013649762669</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5433,22 +5433,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1038914346699191</v>
+        <v>0.103892562309232</v>
       </c>
       <c r="C51">
-        <v>57.19593395192591</v>
+        <v>55.95080785307682</v>
       </c>
       <c r="D51">
-        <v>115.9129339519259</v>
+        <v>115.9108078530768</v>
       </c>
       <c r="E51">
-        <v>24.20699999999999</v>
+        <v>25.45</v>
       </c>
       <c r="F51">
-        <v>60.907</v>
+        <v>62.15</v>
       </c>
       <c r="G51">
         <v>2.19</v>
@@ -5469,28 +5469,28 @@
         <v>11.34222222222222</v>
       </c>
       <c r="M51">
-        <v>4.3792133</v>
+        <v>4.468585</v>
       </c>
       <c r="N51">
-        <v>6.963008922222222</v>
+        <v>6.873637222222222</v>
       </c>
       <c r="O51">
-        <v>1.392601784444444</v>
+        <v>1.374727444444445</v>
       </c>
       <c r="P51">
-        <v>5.570407137777778</v>
+        <v>5.498909777777778</v>
       </c>
       <c r="Q51">
-        <v>9.450407137777777</v>
+        <v>9.378909777777777</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1484443817057238</v>
+        <v>0.1502651246184639</v>
       </c>
       <c r="T51">
-        <v>1.947125991511959</v>
+        <v>1.981664811760508</v>
       </c>
       <c r="U51">
         <v>0.07190000000000001</v>
@@ -5507,7 +5507,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>2.590013649762669</v>
+        <v>2.538213376767416</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5515,22 +5515,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.103892562309232</v>
+        <v>0.1054848899485448</v>
       </c>
       <c r="C52">
-        <v>55.95080785307682</v>
+        <v>51.78141701753736</v>
       </c>
       <c r="D52">
-        <v>115.9108078530768</v>
+        <v>112.9844170175374</v>
       </c>
       <c r="E52">
-        <v>25.45</v>
+        <v>26.693</v>
       </c>
       <c r="F52">
-        <v>62.15</v>
+        <v>63.393</v>
       </c>
       <c r="G52">
         <v>2.19</v>
@@ -5551,45 +5551,45 @@
         <v>11.34222222222222</v>
       </c>
       <c r="M52">
-        <v>4.468585</v>
+        <v>4.805189400000001</v>
       </c>
       <c r="N52">
-        <v>6.873637222222222</v>
+        <v>6.537032822222222</v>
       </c>
       <c r="O52">
-        <v>1.374727444444445</v>
+        <v>1.307406564444444</v>
       </c>
       <c r="P52">
-        <v>5.498909777777778</v>
+        <v>5.229626257777777</v>
       </c>
       <c r="Q52">
-        <v>9.378909777777777</v>
+        <v>9.109626257777776</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1502651246184639</v>
+        <v>0.1521601835684587</v>
       </c>
       <c r="T52">
-        <v>1.981664811760508</v>
+        <v>2.017613379774304</v>
       </c>
       <c r="U52">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V52">
         <v>0.2</v>
       </c>
       <c r="W52">
-        <v>0.05752000000000001</v>
+        <v>0.06064000000000001</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y52">
-        <v>2.538213376767416</v>
+        <v>2.36041106355188</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5597,22 +5597,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1054848899485448</v>
+        <v>0.1055172175878576</v>
       </c>
       <c r="C53">
-        <v>51.78141701753736</v>
+        <v>50.48053469417027</v>
       </c>
       <c r="D53">
-        <v>112.9844170175374</v>
+        <v>112.9265346941703</v>
       </c>
       <c r="E53">
-        <v>26.693</v>
+        <v>27.93599999999999</v>
       </c>
       <c r="F53">
-        <v>63.393</v>
+        <v>64.636</v>
       </c>
       <c r="G53">
         <v>2.19</v>
@@ -5633,28 +5633,28 @@
         <v>11.34222222222222</v>
       </c>
       <c r="M53">
-        <v>4.805189400000001</v>
+        <v>4.8994088</v>
       </c>
       <c r="N53">
-        <v>6.537032822222222</v>
+        <v>6.442813422222223</v>
       </c>
       <c r="O53">
-        <v>1.307406564444444</v>
+        <v>1.288562684444445</v>
       </c>
       <c r="P53">
-        <v>5.229626257777777</v>
+        <v>5.154250737777778</v>
       </c>
       <c r="Q53">
-        <v>9.109626257777776</v>
+        <v>9.034250737777777</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1521601835684587</v>
+        <v>0.1541342033080366</v>
       </c>
       <c r="T53">
-        <v>2.017613379774304</v>
+        <v>2.055059804788675</v>
       </c>
       <c r="U53">
         <v>0.07580000000000001</v>
@@ -5671,7 +5671,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>2.36041106355188</v>
+        <v>2.31501854309896</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5679,22 +5679,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1055172175878576</v>
+        <v>0.1055495452271704</v>
       </c>
       <c r="C54">
-        <v>50.48053469417027</v>
+        <v>49.17971164708078</v>
       </c>
       <c r="D54">
-        <v>112.9265346941703</v>
+        <v>112.8687116470808</v>
       </c>
       <c r="E54">
-        <v>27.93599999999999</v>
+        <v>29.179</v>
       </c>
       <c r="F54">
-        <v>64.636</v>
+        <v>65.879</v>
       </c>
       <c r="G54">
         <v>2.19</v>
@@ -5715,28 +5715,28 @@
         <v>11.34222222222222</v>
       </c>
       <c r="M54">
-        <v>4.8994088</v>
+        <v>4.993628200000001</v>
       </c>
       <c r="N54">
-        <v>6.442813422222223</v>
+        <v>6.348594022222222</v>
       </c>
       <c r="O54">
-        <v>1.288562684444445</v>
+        <v>1.269718804444445</v>
       </c>
       <c r="P54">
-        <v>5.154250737777778</v>
+        <v>5.078875217777777</v>
       </c>
       <c r="Q54">
-        <v>9.034250737777777</v>
+        <v>8.958875217777777</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1541342033080366</v>
+        <v>0.1561922238875966</v>
       </c>
       <c r="T54">
-        <v>2.055059804788675</v>
+        <v>2.094099694697274</v>
       </c>
       <c r="U54">
         <v>0.07580000000000001</v>
@@ -5753,7 +5753,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>2.31501854309896</v>
+        <v>2.271338947946149</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5761,22 +5761,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1055495452271704</v>
+        <v>0.1055818728664832</v>
       </c>
       <c r="C55">
-        <v>49.17971164708078</v>
+        <v>47.87894778525978</v>
       </c>
       <c r="D55">
-        <v>112.8687116470808</v>
+        <v>112.8109477852598</v>
       </c>
       <c r="E55">
-        <v>29.179</v>
+        <v>30.422</v>
       </c>
       <c r="F55">
-        <v>65.879</v>
+        <v>67.122</v>
       </c>
       <c r="G55">
         <v>2.19</v>
@@ -5797,28 +5797,28 @@
         <v>11.34222222222222</v>
       </c>
       <c r="M55">
-        <v>4.993628200000001</v>
+        <v>5.087847600000001</v>
       </c>
       <c r="N55">
-        <v>6.348594022222222</v>
+        <v>6.254374622222222</v>
       </c>
       <c r="O55">
-        <v>1.269718804444445</v>
+        <v>1.250874924444444</v>
       </c>
       <c r="P55">
-        <v>5.078875217777777</v>
+        <v>5.003499697777777</v>
       </c>
       <c r="Q55">
-        <v>8.958875217777777</v>
+        <v>8.883499697777776</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1561922238875966</v>
+        <v>0.1583397236227896</v>
       </c>
       <c r="T55">
-        <v>2.094099694697274</v>
+        <v>2.134836971123639</v>
       </c>
       <c r="U55">
         <v>0.07580000000000001</v>
@@ -5835,7 +5835,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>2.271338947946149</v>
+        <v>2.229277115576775</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5843,22 +5843,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1055818728664832</v>
+        <v>0.105614200505796</v>
       </c>
       <c r="C56">
-        <v>47.87894778525978</v>
+        <v>46.57824301788436</v>
       </c>
       <c r="D56">
-        <v>112.8109477852598</v>
+        <v>112.7532430178844</v>
       </c>
       <c r="E56">
-        <v>30.422</v>
+        <v>31.66500000000001</v>
       </c>
       <c r="F56">
-        <v>67.122</v>
+        <v>68.36500000000001</v>
       </c>
       <c r="G56">
         <v>2.19</v>
@@ -5879,28 +5879,28 @@
         <v>11.34222222222222</v>
       </c>
       <c r="M56">
-        <v>5.087847600000001</v>
+        <v>5.182067000000001</v>
       </c>
       <c r="N56">
-        <v>6.254374622222222</v>
+        <v>6.160155222222222</v>
       </c>
       <c r="O56">
-        <v>1.250874924444444</v>
+        <v>1.232031044444444</v>
       </c>
       <c r="P56">
-        <v>5.003499697777777</v>
+        <v>4.928124177777777</v>
       </c>
       <c r="Q56">
-        <v>8.883499697777776</v>
+        <v>8.808124177777776</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1583397236227896</v>
+        <v>0.1605826677906579</v>
       </c>
       <c r="T56">
-        <v>2.134836971123639</v>
+        <v>2.177384793168954</v>
       </c>
       <c r="U56">
         <v>0.07580000000000001</v>
@@ -5917,7 +5917,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>2.229277115576775</v>
+        <v>2.188744804384471</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5925,22 +5925,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.105614200505796</v>
+        <v>0.1056465281451089</v>
       </c>
       <c r="C57">
-        <v>46.57824301788436</v>
+        <v>45.27759725431744</v>
       </c>
       <c r="D57">
-        <v>112.7532430178844</v>
+        <v>112.6955972543174</v>
       </c>
       <c r="E57">
-        <v>31.66500000000001</v>
+        <v>32.908</v>
       </c>
       <c r="F57">
-        <v>68.36500000000001</v>
+        <v>69.608</v>
       </c>
       <c r="G57">
         <v>2.19</v>
@@ -5961,28 +5961,28 @@
         <v>11.34222222222222</v>
       </c>
       <c r="M57">
-        <v>5.182067000000001</v>
+        <v>5.276286400000001</v>
       </c>
       <c r="N57">
-        <v>6.160155222222222</v>
+        <v>6.065935822222221</v>
       </c>
       <c r="O57">
-        <v>1.232031044444444</v>
+        <v>1.213187164444444</v>
       </c>
       <c r="P57">
-        <v>4.928124177777777</v>
+        <v>4.852748657777777</v>
       </c>
       <c r="Q57">
-        <v>8.808124177777776</v>
+        <v>8.732748657777776</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1605826677906579</v>
+        <v>0.1629275639661565</v>
       </c>
       <c r="T57">
-        <v>2.177384793168954</v>
+        <v>2.221866607125418</v>
       </c>
       <c r="U57">
         <v>0.07580000000000001</v>
@@ -5999,7 +5999,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>2.188744804384471</v>
+        <v>2.149660075734748</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1056465281451089</v>
+        <v>0.1056788557844217</v>
       </c>
       <c r="C58">
-        <v>45.27759725431744</v>
+        <v>43.97701040410708</v>
       </c>
       <c r="D58">
-        <v>112.6955972543174</v>
+        <v>112.6380104041071</v>
       </c>
       <c r="E58">
-        <v>32.908</v>
+        <v>34.151</v>
       </c>
       <c r="F58">
-        <v>69.608</v>
+        <v>70.851</v>
       </c>
       <c r="G58">
         <v>2.19</v>
@@ -6043,28 +6043,28 @@
         <v>11.34222222222222</v>
       </c>
       <c r="M58">
-        <v>5.276286400000001</v>
+        <v>5.3705058</v>
       </c>
       <c r="N58">
-        <v>6.065935822222221</v>
+        <v>5.971716422222222</v>
       </c>
       <c r="O58">
-        <v>1.213187164444444</v>
+        <v>1.194343284444445</v>
       </c>
       <c r="P58">
-        <v>4.852748657777777</v>
+        <v>4.777373137777778</v>
       </c>
       <c r="Q58">
-        <v>8.732748657777776</v>
+        <v>8.657373137777777</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1629275639661565</v>
+        <v>0.1653815250800504</v>
       </c>
       <c r="T58">
-        <v>2.221866607125418</v>
+        <v>2.268417342661253</v>
       </c>
       <c r="U58">
         <v>0.07580000000000001</v>
@@ -6081,7 +6081,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>2.149660075734748</v>
+        <v>2.111946741072735</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6089,22 +6089,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1056788557844217</v>
+        <v>0.1057111834237345</v>
       </c>
       <c r="C59">
-        <v>43.97701040410708</v>
+        <v>42.67648237698612</v>
       </c>
       <c r="D59">
-        <v>112.6380104041071</v>
+        <v>112.5804823769861</v>
       </c>
       <c r="E59">
-        <v>34.151</v>
+        <v>35.39400000000001</v>
       </c>
       <c r="F59">
-        <v>70.851</v>
+        <v>72.09400000000001</v>
       </c>
       <c r="G59">
         <v>2.19</v>
@@ -6125,28 +6125,28 @@
         <v>11.34222222222222</v>
       </c>
       <c r="M59">
-        <v>5.3705058</v>
+        <v>5.464725200000001</v>
       </c>
       <c r="N59">
-        <v>5.971716422222222</v>
+        <v>5.877497022222221</v>
       </c>
       <c r="O59">
-        <v>1.194343284444445</v>
+        <v>1.175499404444444</v>
       </c>
       <c r="P59">
-        <v>4.777373137777778</v>
+        <v>4.701997617777777</v>
       </c>
       <c r="Q59">
-        <v>8.657373137777777</v>
+        <v>8.581997617777777</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1653815250800504</v>
+        <v>0.1679523414850821</v>
       </c>
       <c r="T59">
-        <v>2.268417342661253</v>
+        <v>2.317184779889272</v>
       </c>
       <c r="U59">
         <v>0.07580000000000001</v>
@@ -6163,7 +6163,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>2.111946741072735</v>
+        <v>2.075533866226653</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6171,22 +6171,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1057111834237345</v>
+        <v>0.1057435110630473</v>
       </c>
       <c r="C60">
-        <v>42.67648237698617</v>
+        <v>41.37601308287189</v>
       </c>
       <c r="D60">
-        <v>112.5804823769862</v>
+        <v>112.5230130828719</v>
       </c>
       <c r="E60">
-        <v>35.39399999999999</v>
+        <v>36.63699999999999</v>
       </c>
       <c r="F60">
-        <v>72.09399999999999</v>
+        <v>73.33699999999999</v>
       </c>
       <c r="G60">
         <v>2.19</v>
@@ -6207,28 +6207,28 @@
         <v>11.34222222222222</v>
       </c>
       <c r="M60">
-        <v>5.4647252</v>
+        <v>5.558944599999999</v>
       </c>
       <c r="N60">
-        <v>5.877497022222222</v>
+        <v>5.783277622222223</v>
       </c>
       <c r="O60">
-        <v>1.175499404444444</v>
+        <v>1.156655524444445</v>
       </c>
       <c r="P60">
-        <v>4.701997617777778</v>
+        <v>4.626622097777778</v>
       </c>
       <c r="Q60">
-        <v>8.581997617777777</v>
+        <v>8.506622097777777</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1679523414850821</v>
+        <v>0.1706485635684081</v>
       </c>
       <c r="T60">
-        <v>2.317184779889271</v>
+        <v>2.368331116494266</v>
       </c>
       <c r="U60">
         <v>0.07580000000000001</v>
@@ -6245,7 +6245,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>2.075533866226653</v>
+        <v>2.040355326121118</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6253,22 +6253,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1057435110630473</v>
+        <v>0.1057758387023601</v>
       </c>
       <c r="C61">
-        <v>41.37601308287189</v>
+        <v>40.07560243186529</v>
       </c>
       <c r="D61">
-        <v>112.5230130828719</v>
+        <v>112.4656024318653</v>
       </c>
       <c r="E61">
-        <v>36.63699999999999</v>
+        <v>37.88</v>
       </c>
       <c r="F61">
-        <v>73.33699999999999</v>
+        <v>74.58</v>
       </c>
       <c r="G61">
         <v>2.19</v>
@@ -6289,28 +6289,28 @@
         <v>11.34222222222222</v>
       </c>
       <c r="M61">
-        <v>5.558944599999999</v>
+        <v>5.653164</v>
       </c>
       <c r="N61">
-        <v>5.783277622222223</v>
+        <v>5.689058222222222</v>
       </c>
       <c r="O61">
-        <v>1.156655524444445</v>
+        <v>1.137811644444444</v>
       </c>
       <c r="P61">
-        <v>4.626622097777778</v>
+        <v>4.551246577777778</v>
       </c>
       <c r="Q61">
-        <v>8.506622097777777</v>
+        <v>8.431246577777777</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1706485635684081</v>
+        <v>0.1734795967559003</v>
       </c>
       <c r="T61">
-        <v>2.368331116494266</v>
+        <v>2.42203476992951</v>
       </c>
       <c r="U61">
         <v>0.07580000000000001</v>
@@ -6327,7 +6327,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>2.040355326121118</v>
+        <v>2.006349404019098</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6335,22 +6335,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1057758387023601</v>
+        <v>0.1127377663416729</v>
       </c>
       <c r="C62">
-        <v>40.07560243186529</v>
+        <v>27.69859491915054</v>
       </c>
       <c r="D62">
-        <v>112.4656024318653</v>
+        <v>101.3315949191505</v>
       </c>
       <c r="E62">
-        <v>37.88</v>
+        <v>39.12299999999999</v>
       </c>
       <c r="F62">
-        <v>74.58</v>
+        <v>75.82299999999999</v>
       </c>
       <c r="G62">
         <v>2.19</v>
@@ -6371,45 +6371,45 @@
         <v>11.34222222222222</v>
       </c>
       <c r="M62">
-        <v>5.653164</v>
+        <v>6.824069999999999</v>
       </c>
       <c r="N62">
-        <v>5.689058222222222</v>
+        <v>4.518152222222223</v>
       </c>
       <c r="O62">
-        <v>1.137811644444444</v>
+        <v>0.9036304444444447</v>
       </c>
       <c r="P62">
-        <v>4.551246577777778</v>
+        <v>3.614521777777779</v>
       </c>
       <c r="Q62">
-        <v>8.431246577777777</v>
+        <v>7.494521777777778</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1734795967559003</v>
+        <v>0.1764558111324947</v>
       </c>
       <c r="T62">
-        <v>2.42203476992951</v>
+        <v>2.478492456874253</v>
       </c>
       <c r="U62">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V62">
         <v>0.2</v>
       </c>
       <c r="W62">
-        <v>0.06064000000000001</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y62">
-        <v>2.006349404019098</v>
+        <v>1.662090544531669</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6417,22 +6417,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1127377663416729</v>
+        <v>0.1128836939809858</v>
       </c>
       <c r="C63">
-        <v>27.69859491915054</v>
+        <v>26.24575676665911</v>
       </c>
       <c r="D63">
-        <v>101.3315949191505</v>
+        <v>101.1217567666591</v>
       </c>
       <c r="E63">
-        <v>39.12299999999999</v>
+        <v>40.366</v>
       </c>
       <c r="F63">
-        <v>75.82299999999999</v>
+        <v>77.066</v>
       </c>
       <c r="G63">
         <v>2.19</v>
@@ -6453,28 +6453,28 @@
         <v>11.34222222222222</v>
       </c>
       <c r="M63">
-        <v>6.824069999999999</v>
+        <v>6.93594</v>
       </c>
       <c r="N63">
-        <v>4.518152222222223</v>
+        <v>4.406282222222223</v>
       </c>
       <c r="O63">
-        <v>0.9036304444444447</v>
+        <v>0.8812564444444446</v>
       </c>
       <c r="P63">
-        <v>3.614521777777779</v>
+        <v>3.525025777777778</v>
       </c>
       <c r="Q63">
-        <v>7.494521777777778</v>
+        <v>7.405025777777777</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1764558111324947</v>
+        <v>0.1795886683710152</v>
       </c>
       <c r="T63">
-        <v>2.478492456874253</v>
+        <v>2.537921601026615</v>
       </c>
       <c r="U63">
         <v>0.09</v>
@@ -6491,7 +6491,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>1.662090544531669</v>
+        <v>1.635282632523093</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6499,22 +6499,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1128836939809858</v>
+        <v>0.1130296216202986</v>
       </c>
       <c r="C64">
-        <v>26.24575676665911</v>
+        <v>24.79378588674619</v>
       </c>
       <c r="D64">
-        <v>101.1217567666591</v>
+        <v>100.9127858867462</v>
       </c>
       <c r="E64">
-        <v>40.366</v>
+        <v>41.60899999999999</v>
       </c>
       <c r="F64">
-        <v>77.066</v>
+        <v>78.309</v>
       </c>
       <c r="G64">
         <v>2.19</v>
@@ -6535,28 +6535,28 @@
         <v>11.34222222222222</v>
       </c>
       <c r="M64">
-        <v>6.93594</v>
+        <v>7.047809999999999</v>
       </c>
       <c r="N64">
-        <v>4.406282222222223</v>
+        <v>4.294412222222223</v>
       </c>
       <c r="O64">
-        <v>0.8812564444444446</v>
+        <v>0.8588824444444447</v>
       </c>
       <c r="P64">
-        <v>3.525025777777778</v>
+        <v>3.435529777777778</v>
       </c>
       <c r="Q64">
-        <v>7.405025777777777</v>
+        <v>7.315529777777778</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1795886683710152</v>
+        <v>0.1828908692440502</v>
       </c>
       <c r="T64">
-        <v>2.537921601026615</v>
+        <v>2.600563131349376</v>
       </c>
       <c r="U64">
         <v>0.09</v>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>1.635282632523093</v>
+        <v>1.609325765340187</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6581,22 +6581,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1130296216202986</v>
+        <v>0.1131755492596114</v>
       </c>
       <c r="C65">
-        <v>24.79378588674619</v>
+        <v>23.34267691377237</v>
       </c>
       <c r="D65">
-        <v>100.9127858867462</v>
+        <v>100.7046769137724</v>
       </c>
       <c r="E65">
-        <v>41.60899999999999</v>
+        <v>42.852</v>
       </c>
       <c r="F65">
-        <v>78.309</v>
+        <v>79.55200000000001</v>
       </c>
       <c r="G65">
         <v>2.19</v>
@@ -6617,28 +6617,28 @@
         <v>11.34222222222222</v>
       </c>
       <c r="M65">
-        <v>7.047809999999999</v>
+        <v>7.159680000000001</v>
       </c>
       <c r="N65">
-        <v>4.294412222222223</v>
+        <v>4.182542222222222</v>
       </c>
       <c r="O65">
-        <v>0.8588824444444447</v>
+        <v>0.8365084444444444</v>
       </c>
       <c r="P65">
-        <v>3.435529777777778</v>
+        <v>3.346033777777778</v>
       </c>
       <c r="Q65">
-        <v>7.315529777777778</v>
+        <v>7.226033777777777</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1828908692440502</v>
+        <v>0.1863765257211428</v>
       </c>
       <c r="T65">
-        <v>2.600563131349376</v>
+        <v>2.666684746690066</v>
       </c>
       <c r="U65">
         <v>0.09</v>
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>1.609325765340187</v>
+        <v>1.584180050256746</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6663,22 +6663,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1131755492596114</v>
+        <v>0.1133214768989242</v>
       </c>
       <c r="C66">
-        <v>23.34267691377237</v>
+        <v>21.89242452626868</v>
       </c>
       <c r="D66">
-        <v>100.7046769137724</v>
+        <v>100.4974245262687</v>
       </c>
       <c r="E66">
-        <v>42.852</v>
+        <v>44.095</v>
       </c>
       <c r="F66">
-        <v>79.55200000000001</v>
+        <v>80.795</v>
       </c>
       <c r="G66">
         <v>2.19</v>
@@ -6699,28 +6699,28 @@
         <v>11.34222222222222</v>
       </c>
       <c r="M66">
-        <v>7.159680000000001</v>
+        <v>7.27155</v>
       </c>
       <c r="N66">
-        <v>4.182542222222222</v>
+        <v>4.070672222222223</v>
       </c>
       <c r="O66">
-        <v>0.8365084444444444</v>
+        <v>0.8141344444444446</v>
       </c>
       <c r="P66">
-        <v>3.346033777777778</v>
+        <v>3.256537777777778</v>
       </c>
       <c r="Q66">
-        <v>7.226033777777777</v>
+        <v>7.136537777777777</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1863765257211428</v>
+        <v>0.1900613625683549</v>
       </c>
       <c r="T66">
-        <v>2.666684746690066</v>
+        <v>2.736584740050225</v>
       </c>
       <c r="U66">
         <v>0.09</v>
@@ -6737,7 +6737,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>1.584180050256746</v>
+        <v>1.559808049483566</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6745,22 +6745,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1133214768989242</v>
+        <v>0.113467404538237</v>
       </c>
       <c r="C67">
-        <v>21.89242452626868</v>
+        <v>20.44302344648301</v>
       </c>
       <c r="D67">
-        <v>100.4974245262687</v>
+        <v>100.291023446483</v>
       </c>
       <c r="E67">
-        <v>44.095</v>
+        <v>45.33799999999999</v>
       </c>
       <c r="F67">
-        <v>80.795</v>
+        <v>82.038</v>
       </c>
       <c r="G67">
         <v>2.19</v>
@@ -6781,28 +6781,28 @@
         <v>11.34222222222222</v>
       </c>
       <c r="M67">
-        <v>7.27155</v>
+        <v>7.383419999999999</v>
       </c>
       <c r="N67">
-        <v>4.070672222222223</v>
+        <v>3.958802222222223</v>
       </c>
       <c r="O67">
-        <v>0.8141344444444446</v>
+        <v>0.7917604444444447</v>
       </c>
       <c r="P67">
-        <v>3.256537777777778</v>
+        <v>3.167041777777778</v>
       </c>
       <c r="Q67">
-        <v>7.136537777777777</v>
+        <v>7.047041777777777</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1900613625683549</v>
+        <v>0.1939629545242266</v>
       </c>
       <c r="T67">
-        <v>2.736584740050225</v>
+        <v>2.810596497725688</v>
       </c>
       <c r="U67">
         <v>0.09</v>
@@ -6819,7 +6819,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>1.559808049483566</v>
+        <v>1.53617459418836</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6827,22 +6827,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.113467404538237</v>
+        <v>0.1136133321775498</v>
       </c>
       <c r="C68">
-        <v>20.44302344648301</v>
+        <v>18.99446843993198</v>
       </c>
       <c r="D68">
-        <v>100.291023446483</v>
+        <v>100.085468439932</v>
       </c>
       <c r="E68">
-        <v>45.33799999999999</v>
+        <v>46.581</v>
       </c>
       <c r="F68">
-        <v>82.038</v>
+        <v>83.28100000000001</v>
       </c>
       <c r="G68">
         <v>2.19</v>
@@ -6863,28 +6863,28 @@
         <v>11.34222222222222</v>
       </c>
       <c r="M68">
-        <v>7.383419999999999</v>
+        <v>7.495290000000001</v>
       </c>
       <c r="N68">
-        <v>3.958802222222223</v>
+        <v>3.846932222222222</v>
       </c>
       <c r="O68">
-        <v>0.7917604444444447</v>
+        <v>0.7693864444444444</v>
       </c>
       <c r="P68">
-        <v>3.167041777777778</v>
+        <v>3.077545777777777</v>
       </c>
       <c r="Q68">
-        <v>7.047041777777777</v>
+        <v>6.957545777777776</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1939629545242266</v>
+        <v>0.1981010065986359</v>
       </c>
       <c r="T68">
-        <v>2.810596497725688</v>
+        <v>2.889093816472391</v>
       </c>
       <c r="U68">
         <v>0.09</v>
@@ -6901,7 +6901,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>1.53617459418836</v>
+        <v>1.513246615170623</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6909,22 +6909,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1136133321775498</v>
+        <v>0.14705153498782</v>
       </c>
       <c r="C69">
-        <v>18.99446843993198</v>
+        <v>-14.23228432227988</v>
       </c>
       <c r="D69">
-        <v>100.085468439932</v>
+        <v>68.10171567772012</v>
       </c>
       <c r="E69">
-        <v>46.581</v>
+        <v>47.824</v>
       </c>
       <c r="F69">
-        <v>83.28100000000001</v>
+        <v>84.524</v>
       </c>
       <c r="G69">
         <v>2.19</v>
@@ -6945,45 +6945,45 @@
         <v>11.34222222222222</v>
       </c>
       <c r="M69">
-        <v>7.495290000000001</v>
+        <v>12.4081232</v>
       </c>
       <c r="N69">
-        <v>3.846932222222222</v>
+        <v>-1.06590097777778</v>
       </c>
       <c r="O69">
-        <v>0.7693864444444444</v>
+        <v>-0.213180195555556</v>
       </c>
       <c r="P69">
-        <v>3.077545777777777</v>
+        <v>-0.8527207822222238</v>
       </c>
       <c r="Q69">
-        <v>6.957545777777776</v>
+        <v>3.027279217777775</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1981010065986359</v>
+        <v>0.2046165286461805</v>
       </c>
       <c r="T69">
-        <v>2.889093816472391</v>
+        <v>3.01269086207996</v>
       </c>
       <c r="U69">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V69">
-        <v>0.2</v>
+        <v>0.1828193037642022</v>
       </c>
       <c r="W69">
-        <v>0.07199999999999999</v>
+        <v>0.1199621262074151</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y69">
-        <v>1.513246615170623</v>
+        <v>0.9140965188210108</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6991,22 +6991,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.14705153498782</v>
+        <v>0.14806153498782</v>
       </c>
       <c r="C70">
-        <v>-14.23228432227988</v>
+        <v>-16.12634729420304</v>
       </c>
       <c r="D70">
-        <v>68.10171567772012</v>
+        <v>67.45065270579697</v>
       </c>
       <c r="E70">
-        <v>47.824</v>
+        <v>49.06700000000001</v>
       </c>
       <c r="F70">
-        <v>84.524</v>
+        <v>85.76700000000001</v>
       </c>
       <c r="G70">
         <v>2.19</v>
@@ -7027,37 +7027,37 @@
         <v>11.34222222222222</v>
       </c>
       <c r="M70">
-        <v>12.4081232</v>
+        <v>12.5905956</v>
       </c>
       <c r="N70">
-        <v>-1.06590097777778</v>
+        <v>-1.24837337777778</v>
       </c>
       <c r="O70">
-        <v>-0.213180195555556</v>
+        <v>-0.2496746755555559</v>
       </c>
       <c r="P70">
-        <v>-0.8527207822222238</v>
+        <v>-0.9986987022222238</v>
       </c>
       <c r="Q70">
-        <v>3.027279217777775</v>
+        <v>2.881301297777775</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.2046165286461805</v>
+        <v>0.2097396424734766</v>
       </c>
       <c r="T70">
-        <v>3.01269086207996</v>
+        <v>3.109874438276089</v>
       </c>
       <c r="U70">
         <v>0.1468</v>
       </c>
       <c r="V70">
-        <v>0.1828193037642022</v>
+        <v>0.1801697486371847</v>
       </c>
       <c r="W70">
-        <v>0.1199621262074151</v>
+        <v>0.1203510809000613</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.9140965188210108</v>
+        <v>0.9008487431859237</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7073,22 +7073,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.14806153498782</v>
+        <v>0.1490715349878201</v>
       </c>
       <c r="C71">
-        <v>-16.12634729420304</v>
+        <v>-18.00807962286392</v>
       </c>
       <c r="D71">
-        <v>67.45065270579697</v>
+        <v>66.81192037713609</v>
       </c>
       <c r="E71">
-        <v>49.06700000000001</v>
+        <v>50.31</v>
       </c>
       <c r="F71">
-        <v>85.76700000000001</v>
+        <v>87.01000000000001</v>
       </c>
       <c r="G71">
         <v>2.19</v>
@@ -7109,37 +7109,37 @@
         <v>11.34222222222222</v>
       </c>
       <c r="M71">
-        <v>12.5905956</v>
+        <v>12.773068</v>
       </c>
       <c r="N71">
-        <v>-1.24837337777778</v>
+        <v>-1.43084577777778</v>
       </c>
       <c r="O71">
-        <v>-0.2496746755555559</v>
+        <v>-0.2861691555555559</v>
       </c>
       <c r="P71">
-        <v>-0.9986987022222238</v>
+        <v>-1.144676622222224</v>
       </c>
       <c r="Q71">
-        <v>2.881301297777775</v>
+        <v>2.735323377777775</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.2097396424734766</v>
+        <v>0.2152042972225925</v>
       </c>
       <c r="T71">
-        <v>3.109874438276089</v>
+        <v>3.213536919551958</v>
       </c>
       <c r="U71">
         <v>0.1468</v>
       </c>
       <c r="V71">
-        <v>0.1801697486371847</v>
+        <v>0.177595895085225</v>
       </c>
       <c r="W71">
-        <v>0.1203510809000613</v>
+        <v>0.120728922601489</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7147,7 +7147,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.9008487431859237</v>
+        <v>0.8879794754261248</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7155,22 +7155,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1490715349878201</v>
+        <v>0.1500815349878201</v>
       </c>
       <c r="C72">
-        <v>-18.00807962286392</v>
+        <v>-19.87782832184539</v>
       </c>
       <c r="D72">
-        <v>66.81192037713609</v>
+        <v>66.18517167815463</v>
       </c>
       <c r="E72">
-        <v>50.31</v>
+        <v>51.55300000000001</v>
       </c>
       <c r="F72">
-        <v>87.01000000000001</v>
+        <v>88.25300000000001</v>
       </c>
       <c r="G72">
         <v>2.19</v>
@@ -7191,37 +7191,37 @@
         <v>11.34222222222222</v>
       </c>
       <c r="M72">
-        <v>12.773068</v>
+        <v>12.9555404</v>
       </c>
       <c r="N72">
-        <v>-1.43084577777778</v>
+        <v>-1.613318177777781</v>
       </c>
       <c r="O72">
-        <v>-0.2861691555555559</v>
+        <v>-0.3226636355555563</v>
       </c>
       <c r="P72">
-        <v>-1.144676622222224</v>
+        <v>-1.290654542222225</v>
       </c>
       <c r="Q72">
-        <v>2.735323377777775</v>
+        <v>2.589345457777774</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.2152042972225925</v>
+        <v>0.2210458247130268</v>
       </c>
       <c r="T72">
-        <v>3.213536919551958</v>
+        <v>3.324348537467543</v>
       </c>
       <c r="U72">
         <v>0.1468</v>
       </c>
       <c r="V72">
-        <v>0.177595895085225</v>
+        <v>0.1750945444502218</v>
       </c>
       <c r="W72">
-        <v>0.120728922601489</v>
+        <v>0.1210961208747075</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.8879794754261248</v>
+        <v>0.8754727222511088</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7237,22 +7237,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1500815349878201</v>
+        <v>0.15109153498782</v>
       </c>
       <c r="C73">
-        <v>-19.87782832184537</v>
+        <v>-21.73592750469439</v>
       </c>
       <c r="D73">
-        <v>66.18517167815463</v>
+        <v>65.57007249530561</v>
       </c>
       <c r="E73">
-        <v>51.553</v>
+        <v>52.79599999999999</v>
       </c>
       <c r="F73">
-        <v>88.253</v>
+        <v>89.496</v>
       </c>
       <c r="G73">
         <v>2.19</v>
@@ -7273,37 +7273,37 @@
         <v>11.34222222222222</v>
       </c>
       <c r="M73">
-        <v>12.9555404</v>
+        <v>13.1380128</v>
       </c>
       <c r="N73">
-        <v>-1.61331817777778</v>
+        <v>-1.795790577777778</v>
       </c>
       <c r="O73">
-        <v>-0.3226636355555559</v>
+        <v>-0.3591581155555556</v>
       </c>
       <c r="P73">
-        <v>-1.290654542222224</v>
+        <v>-1.436632462222222</v>
       </c>
       <c r="Q73">
-        <v>2.589345457777775</v>
+        <v>2.443367537777777</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.2210458247130267</v>
+        <v>0.2273046041670634</v>
       </c>
       <c r="T73">
-        <v>3.324348537467542</v>
+        <v>3.443075270948526</v>
       </c>
       <c r="U73">
         <v>0.1468</v>
       </c>
       <c r="V73">
-        <v>0.1750945444502218</v>
+        <v>0.1726626757773021</v>
       </c>
       <c r="W73">
-        <v>0.1210961208747075</v>
+        <v>0.1214531191958921</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7311,7 +7311,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.8754727222511089</v>
+        <v>0.8633133788865103</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7319,22 +7319,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.15109153498782</v>
+        <v>0.15210153498782</v>
       </c>
       <c r="C74">
-        <v>-21.73592750469439</v>
+        <v>-23.5826989788421</v>
       </c>
       <c r="D74">
-        <v>65.57007249530561</v>
+        <v>64.96630102115789</v>
       </c>
       <c r="E74">
-        <v>52.79599999999999</v>
+        <v>54.03899999999999</v>
       </c>
       <c r="F74">
-        <v>89.496</v>
+        <v>90.73899999999999</v>
       </c>
       <c r="G74">
         <v>2.19</v>
@@ -7355,37 +7355,37 @@
         <v>11.34222222222222</v>
       </c>
       <c r="M74">
-        <v>13.1380128</v>
+        <v>13.3204852</v>
       </c>
       <c r="N74">
-        <v>-1.795790577777778</v>
+        <v>-1.978262977777778</v>
       </c>
       <c r="O74">
-        <v>-0.3591581155555556</v>
+        <v>-0.3956525955555556</v>
       </c>
       <c r="P74">
-        <v>-1.436632462222222</v>
+        <v>-1.582610382222222</v>
       </c>
       <c r="Q74">
-        <v>2.443367537777777</v>
+        <v>2.297389617777777</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.2273046041670634</v>
+        <v>0.2340269969139916</v>
       </c>
       <c r="T74">
-        <v>3.443075270948526</v>
+        <v>3.570596577279952</v>
       </c>
       <c r="U74">
         <v>0.1468</v>
       </c>
       <c r="V74">
-        <v>0.1726626757773021</v>
+        <v>0.1702974336433664</v>
       </c>
       <c r="W74">
-        <v>0.1214531191958921</v>
+        <v>0.1218003367411538</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7393,7 +7393,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.8633133788865103</v>
+        <v>0.8514871682168321</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7401,22 +7401,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.15210153498782</v>
+        <v>0.15311153498782</v>
       </c>
       <c r="C75">
-        <v>-23.5826989788421</v>
+        <v>-25.41845280700988</v>
       </c>
       <c r="D75">
-        <v>64.96630102115789</v>
+        <v>64.37354719299012</v>
       </c>
       <c r="E75">
-        <v>54.03899999999999</v>
+        <v>55.282</v>
       </c>
       <c r="F75">
-        <v>90.73899999999999</v>
+        <v>91.982</v>
       </c>
       <c r="G75">
         <v>2.19</v>
@@ -7437,37 +7437,37 @@
         <v>11.34222222222222</v>
       </c>
       <c r="M75">
-        <v>13.3204852</v>
+        <v>13.5029576</v>
       </c>
       <c r="N75">
-        <v>-1.978262977777778</v>
+        <v>-2.16073537777778</v>
       </c>
       <c r="O75">
-        <v>-0.3956525955555556</v>
+        <v>-0.4321470755555559</v>
       </c>
       <c r="P75">
-        <v>-1.582610382222222</v>
+        <v>-1.728588302222224</v>
       </c>
       <c r="Q75">
-        <v>2.297389617777777</v>
+        <v>2.151411697777776</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.2340269969139916</v>
+        <v>0.241266496795299</v>
       </c>
       <c r="T75">
-        <v>3.570596577279952</v>
+        <v>3.707927214867643</v>
       </c>
       <c r="U75">
         <v>0.1468</v>
       </c>
       <c r="V75">
-        <v>0.1702974336433664</v>
+        <v>0.1679961169725101</v>
       </c>
       <c r="W75">
-        <v>0.1218003367411538</v>
+        <v>0.1221381700284355</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7475,7 +7475,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.8514871682168321</v>
+        <v>0.8399805848625505</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7483,22 +7483,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.15311153498782</v>
+        <v>0.15412153498782</v>
       </c>
       <c r="C76">
-        <v>-25.41845280700988</v>
+        <v>-27.24348783815972</v>
       </c>
       <c r="D76">
-        <v>64.37354719299012</v>
+        <v>63.79151216184027</v>
       </c>
       <c r="E76">
-        <v>55.282</v>
+        <v>56.52499999999999</v>
       </c>
       <c r="F76">
-        <v>91.982</v>
+        <v>93.22499999999999</v>
       </c>
       <c r="G76">
         <v>2.19</v>
@@ -7519,37 +7519,37 @@
         <v>11.34222222222222</v>
       </c>
       <c r="M76">
-        <v>13.5029576</v>
+        <v>13.68543</v>
       </c>
       <c r="N76">
-        <v>-2.16073537777778</v>
+        <v>-2.343207777777778</v>
       </c>
       <c r="O76">
-        <v>-0.4321470755555559</v>
+        <v>-0.4686415555555556</v>
       </c>
       <c r="P76">
-        <v>-1.728588302222224</v>
+        <v>-1.874566222222222</v>
       </c>
       <c r="Q76">
-        <v>2.151411697777776</v>
+        <v>2.005433777777777</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.241266496795299</v>
+        <v>0.249085156667111</v>
       </c>
       <c r="T76">
-        <v>3.707927214867643</v>
+        <v>3.856244303462349</v>
       </c>
       <c r="U76">
         <v>0.1468</v>
       </c>
       <c r="V76">
-        <v>0.1679961169725101</v>
+        <v>0.16575616874621</v>
       </c>
       <c r="W76">
-        <v>0.1221381700284355</v>
+        <v>0.1224669944280564</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.8399805848625505</v>
+        <v>0.8287808437310499</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7565,22 +7565,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.15412153498782</v>
+        <v>0.15513153498782</v>
       </c>
       <c r="C77">
-        <v>-27.24348783815972</v>
+        <v>-29.05809220989937</v>
       </c>
       <c r="D77">
-        <v>63.79151216184027</v>
+        <v>63.21990779010063</v>
       </c>
       <c r="E77">
-        <v>56.52499999999999</v>
+        <v>57.768</v>
       </c>
       <c r="F77">
-        <v>93.22499999999999</v>
+        <v>94.468</v>
       </c>
       <c r="G77">
         <v>2.19</v>
@@ -7601,37 +7601,37 @@
         <v>11.34222222222222</v>
       </c>
       <c r="M77">
-        <v>13.68543</v>
+        <v>13.8679024</v>
       </c>
       <c r="N77">
-        <v>-2.343207777777778</v>
+        <v>-2.52568017777778</v>
       </c>
       <c r="O77">
-        <v>-0.4686415555555556</v>
+        <v>-0.505136035555556</v>
       </c>
       <c r="P77">
-        <v>-1.874566222222222</v>
+        <v>-2.020544142222223</v>
       </c>
       <c r="Q77">
-        <v>2.005433777777777</v>
+        <v>1.859455857777776</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.249085156667111</v>
+        <v>0.2575553715282405</v>
       </c>
       <c r="T77">
-        <v>3.856244303462349</v>
+        <v>4.016921149439947</v>
       </c>
       <c r="U77">
         <v>0.1468</v>
       </c>
       <c r="V77">
-        <v>0.16575616874621</v>
+        <v>0.1635751665258651</v>
       </c>
       <c r="W77">
-        <v>0.1224669944280564</v>
+        <v>0.122787165554003</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7639,7 +7639,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.8287808437310499</v>
+        <v>0.8178758326293254</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7647,22 +7647,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.15513153498782</v>
+        <v>0.15614153498782</v>
       </c>
       <c r="C78">
-        <v>-29.05809220989937</v>
+        <v>-30.86254382411612</v>
       </c>
       <c r="D78">
-        <v>63.21990779010063</v>
+        <v>62.65845617588388</v>
       </c>
       <c r="E78">
-        <v>57.768</v>
+        <v>59.011</v>
       </c>
       <c r="F78">
-        <v>94.468</v>
+        <v>95.711</v>
       </c>
       <c r="G78">
         <v>2.19</v>
@@ -7683,37 +7683,37 @@
         <v>11.34222222222222</v>
       </c>
       <c r="M78">
-        <v>13.8679024</v>
+        <v>14.0503748</v>
       </c>
       <c r="N78">
-        <v>-2.52568017777778</v>
+        <v>-2.70815257777778</v>
       </c>
       <c r="O78">
-        <v>-0.505136035555556</v>
+        <v>-0.541630515555556</v>
       </c>
       <c r="P78">
-        <v>-2.020544142222223</v>
+        <v>-2.166522062222223</v>
       </c>
       <c r="Q78">
-        <v>1.859455857777776</v>
+        <v>1.713477937777776</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2575553715282405</v>
+        <v>0.2667621268120771</v>
       </c>
       <c r="T78">
-        <v>4.016921149439947</v>
+        <v>4.19156989506777</v>
       </c>
       <c r="U78">
         <v>0.1468</v>
       </c>
       <c r="V78">
-        <v>0.1635751665258651</v>
+        <v>0.1614508137138409</v>
       </c>
       <c r="W78">
-        <v>0.122787165554003</v>
+        <v>0.1230990205468082</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7721,7 +7721,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.8178758326293254</v>
+        <v>0.8072540685692043</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7729,22 +7729,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.15614153498782</v>
+        <v>0.2012117945672419</v>
       </c>
       <c r="C79">
-        <v>-30.86254382411612</v>
+        <v>-49.88945323769477</v>
       </c>
       <c r="D79">
-        <v>62.65845617588388</v>
+        <v>44.87454676230524</v>
       </c>
       <c r="E79">
-        <v>59.011</v>
+        <v>60.254</v>
       </c>
       <c r="F79">
-        <v>95.711</v>
+        <v>96.95400000000001</v>
       </c>
       <c r="G79">
         <v>2.19</v>
@@ -7765,45 +7765,45 @@
         <v>11.34222222222222</v>
       </c>
       <c r="M79">
-        <v>14.0503748</v>
+        <v>19.4683632</v>
       </c>
       <c r="N79">
-        <v>-2.70815257777778</v>
+        <v>-8.12614097777778</v>
       </c>
       <c r="O79">
-        <v>-0.541630515555556</v>
+        <v>-1.625228195555556</v>
       </c>
       <c r="P79">
-        <v>-2.166522062222223</v>
+        <v>-6.500912782222224</v>
       </c>
       <c r="Q79">
-        <v>1.713477937777776</v>
+        <v>-2.620912782222225</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2667621268120771</v>
+        <v>0.2856252215736348</v>
       </c>
       <c r="T79">
-        <v>4.19156989506777</v>
+        <v>4.549395832349771</v>
       </c>
       <c r="U79">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V79">
-        <v>0.1614508137138409</v>
+        <v>0.1165195256088321</v>
       </c>
       <c r="W79">
-        <v>0.1230990205468082</v>
+        <v>0.1774028792577465</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y79">
-        <v>0.8072540685692043</v>
+        <v>0.5825976280441605</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7811,22 +7811,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2012117945672419</v>
+        <v>0.2027617945672419</v>
       </c>
       <c r="C80">
-        <v>-49.88945323769477</v>
+        <v>-51.56623442978169</v>
       </c>
       <c r="D80">
-        <v>44.87454676230524</v>
+        <v>44.44076557021832</v>
       </c>
       <c r="E80">
-        <v>60.254</v>
+        <v>61.497</v>
       </c>
       <c r="F80">
-        <v>96.95400000000001</v>
+        <v>98.197</v>
       </c>
       <c r="G80">
         <v>2.19</v>
@@ -7847,37 +7847,37 @@
         <v>11.34222222222222</v>
       </c>
       <c r="M80">
-        <v>19.4683632</v>
+        <v>19.7179576</v>
       </c>
       <c r="N80">
-        <v>-8.12614097777778</v>
+        <v>-8.375735377777779</v>
       </c>
       <c r="O80">
-        <v>-1.625228195555556</v>
+        <v>-1.675147075555556</v>
       </c>
       <c r="P80">
-        <v>-6.500912782222224</v>
+        <v>-6.700588302222224</v>
       </c>
       <c r="Q80">
-        <v>-2.620912782222225</v>
+        <v>-2.820588302222225</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2856252215736348</v>
+        <v>0.2970454702199983</v>
       </c>
       <c r="T80">
-        <v>4.549395832349771</v>
+        <v>4.766033729128331</v>
       </c>
       <c r="U80">
         <v>0.2008</v>
       </c>
       <c r="V80">
-        <v>0.1165195256088321</v>
+        <v>0.1150445949049228</v>
       </c>
       <c r="W80">
-        <v>0.1774028792577465</v>
+        <v>0.1776990453430915</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7885,7 +7885,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.5825976280441605</v>
+        <v>0.5752229745246141</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7893,22 +7893,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2027617945672419</v>
+        <v>0.2043117945672419</v>
       </c>
       <c r="C81">
-        <v>-51.56623442978169</v>
+        <v>-53.23470959376722</v>
       </c>
       <c r="D81">
-        <v>44.44076557021832</v>
+        <v>44.01529040623278</v>
       </c>
       <c r="E81">
-        <v>61.497</v>
+        <v>62.73999999999999</v>
       </c>
       <c r="F81">
-        <v>98.197</v>
+        <v>99.44</v>
       </c>
       <c r="G81">
         <v>2.19</v>
@@ -7929,37 +7929,37 @@
         <v>11.34222222222222</v>
       </c>
       <c r="M81">
-        <v>19.7179576</v>
+        <v>19.967552</v>
       </c>
       <c r="N81">
-        <v>-8.375735377777779</v>
+        <v>-8.625329777777779</v>
       </c>
       <c r="O81">
-        <v>-1.675147075555556</v>
+        <v>-1.725065955555556</v>
       </c>
       <c r="P81">
-        <v>-6.700588302222224</v>
+        <v>-6.900263822222223</v>
       </c>
       <c r="Q81">
-        <v>-2.820588302222225</v>
+        <v>-3.020263822222224</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2970454702199983</v>
+        <v>0.3096077437309983</v>
       </c>
       <c r="T81">
-        <v>4.766033729128331</v>
+        <v>5.004335415584748</v>
       </c>
       <c r="U81">
         <v>0.2008</v>
       </c>
       <c r="V81">
-        <v>0.1150445949049228</v>
+        <v>0.1136065374686113</v>
       </c>
       <c r="W81">
-        <v>0.1776990453430915</v>
+        <v>0.1779878072763029</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.5752229745246141</v>
+        <v>0.5680326873430565</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7975,22 +7975,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2043117945672419</v>
+        <v>0.2058617945672419</v>
       </c>
       <c r="C82">
-        <v>-53.23470959376722</v>
+        <v>-54.89511503262287</v>
       </c>
       <c r="D82">
-        <v>44.01529040623278</v>
+        <v>43.59788496737714</v>
       </c>
       <c r="E82">
-        <v>62.73999999999999</v>
+        <v>63.983</v>
       </c>
       <c r="F82">
-        <v>99.44</v>
+        <v>100.683</v>
       </c>
       <c r="G82">
         <v>2.19</v>
@@ -8011,37 +8011,37 @@
         <v>11.34222222222222</v>
       </c>
       <c r="M82">
-        <v>19.967552</v>
+        <v>20.2171464</v>
       </c>
       <c r="N82">
-        <v>-8.625329777777779</v>
+        <v>-8.874924177777778</v>
       </c>
       <c r="O82">
-        <v>-1.725065955555556</v>
+        <v>-1.774984835555556</v>
       </c>
       <c r="P82">
-        <v>-6.900263822222223</v>
+        <v>-7.099939342222223</v>
       </c>
       <c r="Q82">
-        <v>-3.020263822222224</v>
+        <v>-3.219939342222224</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.3096077437309983</v>
+        <v>0.3234923618221034</v>
       </c>
       <c r="T82">
-        <v>5.004335415584748</v>
+        <v>5.267721490089208</v>
       </c>
       <c r="U82">
         <v>0.2008</v>
       </c>
       <c r="V82">
-        <v>0.1136065374686113</v>
+        <v>0.1122039876233198</v>
       </c>
       <c r="W82">
-        <v>0.1779878072763029</v>
+        <v>0.1782694392852374</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8049,7 +8049,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.5680326873430565</v>
+        <v>0.561019938116599</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8057,22 +8057,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2058617945672419</v>
+        <v>0.2074117945672419</v>
       </c>
       <c r="C83">
-        <v>-54.89511503262287</v>
+        <v>-56.54767816989978</v>
       </c>
       <c r="D83">
-        <v>43.59788496737714</v>
+        <v>43.18832183010023</v>
       </c>
       <c r="E83">
-        <v>63.983</v>
+        <v>65.226</v>
       </c>
       <c r="F83">
-        <v>100.683</v>
+        <v>101.926</v>
       </c>
       <c r="G83">
         <v>2.19</v>
@@ -8093,37 +8093,37 @@
         <v>11.34222222222222</v>
       </c>
       <c r="M83">
-        <v>20.2171464</v>
+        <v>20.4667408</v>
       </c>
       <c r="N83">
-        <v>-8.874924177777778</v>
+        <v>-9.124518577777778</v>
       </c>
       <c r="O83">
-        <v>-1.774984835555556</v>
+        <v>-1.824903715555556</v>
       </c>
       <c r="P83">
-        <v>-7.099939342222223</v>
+        <v>-7.299614862222223</v>
       </c>
       <c r="Q83">
-        <v>-3.219939342222224</v>
+        <v>-3.419614862222224</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.3234923618221034</v>
+        <v>0.3389197152566648</v>
       </c>
       <c r="T83">
-        <v>5.267721490089208</v>
+        <v>5.560372683983054</v>
       </c>
       <c r="U83">
         <v>0.2008</v>
       </c>
       <c r="V83">
-        <v>0.1122039876233198</v>
+        <v>0.1108356463108403</v>
       </c>
       <c r="W83">
-        <v>0.1782694392852374</v>
+        <v>0.1785442022207833</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8131,7 +8131,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.561019938116599</v>
+        <v>0.5541782315542014</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8139,22 +8139,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2074117945672419</v>
+        <v>0.2089617945672419</v>
       </c>
       <c r="C84">
-        <v>-56.54767816989978</v>
+        <v>-58.19261796291838</v>
       </c>
       <c r="D84">
-        <v>43.18832183010023</v>
+        <v>42.78638203708164</v>
       </c>
       <c r="E84">
-        <v>65.226</v>
+        <v>66.46900000000001</v>
       </c>
       <c r="F84">
-        <v>101.926</v>
+        <v>103.169</v>
       </c>
       <c r="G84">
         <v>2.19</v>
@@ -8175,37 +8175,37 @@
         <v>11.34222222222222</v>
       </c>
       <c r="M84">
-        <v>20.4667408</v>
+        <v>20.7163352</v>
       </c>
       <c r="N84">
-        <v>-9.124518577777778</v>
+        <v>-9.374112977777781</v>
       </c>
       <c r="O84">
-        <v>-1.824903715555556</v>
+        <v>-1.874822595555556</v>
       </c>
       <c r="P84">
-        <v>-7.299614862222223</v>
+        <v>-7.499290382222225</v>
       </c>
       <c r="Q84">
-        <v>-3.419614862222224</v>
+        <v>-3.619290382222226</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.3389197152566648</v>
+        <v>0.3561620514482333</v>
       </c>
       <c r="T84">
-        <v>5.560372683983054</v>
+        <v>5.887453430099704</v>
       </c>
       <c r="U84">
         <v>0.2008</v>
       </c>
       <c r="V84">
-        <v>0.1108356463108403</v>
+        <v>0.1095002770781796</v>
       </c>
       <c r="W84">
-        <v>0.1785442022207833</v>
+        <v>0.1788123443627015</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8213,7 +8213,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.5541782315542014</v>
+        <v>0.5475013853908978</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8221,22 +8221,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2089617945672419</v>
+        <v>0.2105117945672419</v>
       </c>
       <c r="C85">
-        <v>-58.19261796291838</v>
+        <v>-59.83014529309798</v>
       </c>
       <c r="D85">
-        <v>42.78638203708164</v>
+        <v>42.39185470690203</v>
       </c>
       <c r="E85">
-        <v>66.46900000000001</v>
+        <v>67.712</v>
       </c>
       <c r="F85">
-        <v>103.169</v>
+        <v>104.412</v>
       </c>
       <c r="G85">
         <v>2.19</v>
@@ -8257,37 +8257,37 @@
         <v>11.34222222222222</v>
       </c>
       <c r="M85">
-        <v>20.7163352</v>
+        <v>20.9659296</v>
       </c>
       <c r="N85">
-        <v>-9.374112977777781</v>
+        <v>-9.62370737777778</v>
       </c>
       <c r="O85">
-        <v>-1.874822595555556</v>
+        <v>-1.924741475555556</v>
       </c>
       <c r="P85">
-        <v>-7.499290382222225</v>
+        <v>-7.698965902222224</v>
       </c>
       <c r="Q85">
-        <v>-3.619290382222226</v>
+        <v>-3.818965902222225</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.3561620514482333</v>
+        <v>0.375559679663748</v>
       </c>
       <c r="T85">
-        <v>5.887453430099704</v>
+        <v>6.255419269480937</v>
       </c>
       <c r="U85">
         <v>0.2008</v>
       </c>
       <c r="V85">
-        <v>0.1095002770781796</v>
+        <v>0.1081967023510584</v>
       </c>
       <c r="W85">
-        <v>0.1788123443627015</v>
+        <v>0.1790741021679075</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.5475013853908978</v>
+        <v>0.5409835117552919</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8303,22 +8303,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2105117945672419</v>
+        <v>0.2120617945672419</v>
       </c>
       <c r="C86">
-        <v>-59.83014529309795</v>
+        <v>-61.46046333488881</v>
       </c>
       <c r="D86">
-        <v>42.39185470690204</v>
+        <v>42.0045366651112</v>
       </c>
       <c r="E86">
-        <v>67.71199999999999</v>
+        <v>68.955</v>
       </c>
       <c r="F86">
-        <v>104.412</v>
+        <v>105.655</v>
       </c>
       <c r="G86">
         <v>2.19</v>
@@ -8339,37 +8339,37 @@
         <v>11.34222222222222</v>
       </c>
       <c r="M86">
-        <v>20.9659296</v>
+        <v>21.215524</v>
       </c>
       <c r="N86">
-        <v>-9.623707377777777</v>
+        <v>-9.87330177777778</v>
       </c>
       <c r="O86">
-        <v>-1.924741475555555</v>
+        <v>-1.974660355555556</v>
       </c>
       <c r="P86">
-        <v>-7.698965902222222</v>
+        <v>-7.898641422222224</v>
       </c>
       <c r="Q86">
-        <v>-3.818965902222223</v>
+        <v>-4.018641422222225</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.3755596796637477</v>
+        <v>0.3975436583079975</v>
       </c>
       <c r="T86">
-        <v>6.255419269480933</v>
+        <v>6.672447220779661</v>
       </c>
       <c r="U86">
         <v>0.2008</v>
       </c>
       <c r="V86">
-        <v>0.1081967023510584</v>
+        <v>0.1069237999704577</v>
       </c>
       <c r="W86">
-        <v>0.1790741021679075</v>
+        <v>0.1793297009659321</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.5409835117552919</v>
+        <v>0.5346189998522883</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8385,22 +8385,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2120617945672419</v>
+        <v>0.2136117945672419</v>
       </c>
       <c r="C87">
-        <v>-61.46046333488881</v>
+        <v>-63.0837679046624</v>
       </c>
       <c r="D87">
-        <v>42.0045366651112</v>
+        <v>41.6242320953376</v>
       </c>
       <c r="E87">
-        <v>68.955</v>
+        <v>70.19799999999999</v>
       </c>
       <c r="F87">
-        <v>105.655</v>
+        <v>106.898</v>
       </c>
       <c r="G87">
         <v>2.19</v>
@@ -8421,37 +8421,37 @@
         <v>11.34222222222222</v>
       </c>
       <c r="M87">
-        <v>21.215524</v>
+        <v>21.4651184</v>
       </c>
       <c r="N87">
-        <v>-9.87330177777778</v>
+        <v>-10.12289617777778</v>
       </c>
       <c r="O87">
-        <v>-1.974660355555556</v>
+        <v>-2.024579235555556</v>
       </c>
       <c r="P87">
-        <v>-7.898641422222224</v>
+        <v>-8.098316942222223</v>
       </c>
       <c r="Q87">
-        <v>-4.018641422222225</v>
+        <v>-4.218316942222224</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.3975436583079975</v>
+        <v>0.4226682053299975</v>
       </c>
       <c r="T87">
-        <v>6.672447220779661</v>
+        <v>7.149050593692496</v>
       </c>
       <c r="U87">
         <v>0.2008</v>
       </c>
       <c r="V87">
-        <v>0.1069237999704577</v>
+        <v>0.1056804999708012</v>
       </c>
       <c r="W87">
-        <v>0.1793297009659321</v>
+        <v>0.1795793556058631</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.5346189998522883</v>
+        <v>0.528402499854006</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8467,22 +8467,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2136117945672419</v>
+        <v>0.2151617945672419</v>
       </c>
       <c r="C88">
-        <v>-63.0837679046624</v>
+        <v>-64.70024779081908</v>
       </c>
       <c r="D88">
-        <v>41.6242320953376</v>
+        <v>41.25075220918092</v>
       </c>
       <c r="E88">
-        <v>70.19799999999999</v>
+        <v>71.44099999999999</v>
       </c>
       <c r="F88">
-        <v>106.898</v>
+        <v>108.141</v>
       </c>
       <c r="G88">
         <v>2.19</v>
@@ -8503,37 +8503,37 @@
         <v>11.34222222222222</v>
       </c>
       <c r="M88">
-        <v>21.4651184</v>
+        <v>21.7147128</v>
       </c>
       <c r="N88">
-        <v>-10.12289617777778</v>
+        <v>-10.37249057777777</v>
       </c>
       <c r="O88">
-        <v>-2.024579235555556</v>
+        <v>-2.074498115555555</v>
       </c>
       <c r="P88">
-        <v>-8.098316942222223</v>
+        <v>-8.29799246222222</v>
       </c>
       <c r="Q88">
-        <v>-4.218316942222224</v>
+        <v>-4.417992462222221</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.4226682053299975</v>
+        <v>0.4516580672784588</v>
       </c>
       <c r="T88">
-        <v>7.149050593692496</v>
+        <v>7.698977562438071</v>
       </c>
       <c r="U88">
         <v>0.2008</v>
       </c>
       <c r="V88">
-        <v>0.1056804999708012</v>
+        <v>0.1044657815803322</v>
       </c>
       <c r="W88">
-        <v>0.1795793556058631</v>
+        <v>0.1798232710586693</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8541,7 +8541,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.528402499854006</v>
+        <v>0.5223289079016612</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8549,22 +8549,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2151617945672419</v>
+        <v>0.2167117945672419</v>
       </c>
       <c r="C89">
-        <v>-64.70024779081908</v>
+        <v>-66.31008506628189</v>
       </c>
       <c r="D89">
-        <v>41.25075220918092</v>
+        <v>40.88391493371812</v>
       </c>
       <c r="E89">
-        <v>71.44099999999999</v>
+        <v>72.684</v>
       </c>
       <c r="F89">
-        <v>108.141</v>
+        <v>109.384</v>
       </c>
       <c r="G89">
         <v>2.19</v>
@@ -8585,37 +8585,37 @@
         <v>11.34222222222222</v>
       </c>
       <c r="M89">
-        <v>21.7147128</v>
+        <v>21.9643072</v>
       </c>
       <c r="N89">
-        <v>-10.37249057777777</v>
+        <v>-10.62208497777778</v>
       </c>
       <c r="O89">
-        <v>-2.074498115555555</v>
+        <v>-2.124416995555556</v>
       </c>
       <c r="P89">
-        <v>-8.29799246222222</v>
+        <v>-8.497667982222222</v>
       </c>
       <c r="Q89">
-        <v>-4.417992462222221</v>
+        <v>-4.617667982222223</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.4516580672784588</v>
+        <v>0.4854795728849971</v>
       </c>
       <c r="T89">
-        <v>7.698977562438071</v>
+        <v>8.34055902597458</v>
       </c>
       <c r="U89">
         <v>0.2008</v>
       </c>
       <c r="V89">
-        <v>0.1044657815803322</v>
+        <v>0.1032786704260103</v>
       </c>
       <c r="W89">
-        <v>0.1798232710586693</v>
+        <v>0.1800616429784571</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8623,7 +8623,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.5223289079016612</v>
+        <v>0.5163933521300513</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8631,22 +8631,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2167117945672419</v>
+        <v>0.2182617945672419</v>
       </c>
       <c r="C90">
-        <v>-66.31008506628189</v>
+        <v>-67.9134553844636</v>
       </c>
       <c r="D90">
-        <v>40.88391493371812</v>
+        <v>40.52354461553639</v>
       </c>
       <c r="E90">
-        <v>72.684</v>
+        <v>73.92699999999999</v>
       </c>
       <c r="F90">
-        <v>109.384</v>
+        <v>110.627</v>
       </c>
       <c r="G90">
         <v>2.19</v>
@@ -8667,37 +8667,37 @@
         <v>11.34222222222222</v>
       </c>
       <c r="M90">
-        <v>21.9643072</v>
+        <v>22.2139016</v>
       </c>
       <c r="N90">
-        <v>-10.62208497777778</v>
+        <v>-10.87167937777778</v>
       </c>
       <c r="O90">
-        <v>-2.124416995555556</v>
+        <v>-2.174335875555556</v>
       </c>
       <c r="P90">
-        <v>-8.497667982222222</v>
+        <v>-8.697343502222221</v>
       </c>
       <c r="Q90">
-        <v>-4.617667982222223</v>
+        <v>-4.817343502222222</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.4854795728849971</v>
+        <v>0.5254504431472694</v>
       </c>
       <c r="T90">
-        <v>8.34055902597458</v>
+        <v>9.098791664699538</v>
       </c>
       <c r="U90">
         <v>0.2008</v>
       </c>
       <c r="V90">
-        <v>0.1032786704260103</v>
+        <v>0.1021182359268416</v>
       </c>
       <c r="W90">
-        <v>0.1800616429784571</v>
+        <v>0.1802946582258902</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.5163933521300513</v>
+        <v>0.5105911796342081</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8713,22 +8713,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2182617945672419</v>
+        <v>0.219811794567242</v>
       </c>
       <c r="C91">
-        <v>-67.9134553844636</v>
+        <v>-69.51052825971803</v>
       </c>
       <c r="D91">
-        <v>40.52354461553639</v>
+        <v>40.16947174028198</v>
       </c>
       <c r="E91">
-        <v>73.92699999999999</v>
+        <v>75.17</v>
       </c>
       <c r="F91">
-        <v>110.627</v>
+        <v>111.87</v>
       </c>
       <c r="G91">
         <v>2.19</v>
@@ -8749,37 +8749,37 @@
         <v>11.34222222222222</v>
       </c>
       <c r="M91">
-        <v>22.2139016</v>
+        <v>22.463496</v>
       </c>
       <c r="N91">
-        <v>-10.87167937777778</v>
+        <v>-11.12127377777778</v>
       </c>
       <c r="O91">
-        <v>-2.174335875555556</v>
+        <v>-2.224254755555556</v>
       </c>
       <c r="P91">
-        <v>-8.697343502222221</v>
+        <v>-8.897019022222224</v>
       </c>
       <c r="Q91">
-        <v>-4.817343502222222</v>
+        <v>-5.017019022222225</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.5254504431472694</v>
+        <v>0.5734154874619966</v>
       </c>
       <c r="T91">
-        <v>9.098791664699538</v>
+        <v>10.0086708311695</v>
       </c>
       <c r="U91">
         <v>0.2008</v>
       </c>
       <c r="V91">
-        <v>0.1021182359268416</v>
+        <v>0.1009835888609878</v>
       </c>
       <c r="W91">
-        <v>0.1802946582258902</v>
+        <v>0.1805224953567137</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8787,7 +8787,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.5105911796342081</v>
+        <v>0.504917944304939</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8795,22 +8795,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.219811794567242</v>
+        <v>0.2539947127432755</v>
       </c>
       <c r="C92">
-        <v>-69.51052825971803</v>
+        <v>-77.24331830573323</v>
       </c>
       <c r="D92">
-        <v>40.16947174028198</v>
+        <v>33.67968169426677</v>
       </c>
       <c r="E92">
-        <v>75.17</v>
+        <v>76.413</v>
       </c>
       <c r="F92">
-        <v>111.87</v>
+        <v>113.113</v>
       </c>
       <c r="G92">
         <v>2.19</v>
@@ -8831,45 +8831,45 @@
         <v>11.34222222222222</v>
       </c>
       <c r="M92">
-        <v>22.463496</v>
+        <v>26.6720454</v>
       </c>
       <c r="N92">
-        <v>-11.12127377777778</v>
+        <v>-15.32982317777778</v>
       </c>
       <c r="O92">
-        <v>-2.224254755555556</v>
+        <v>-3.065964635555556</v>
       </c>
       <c r="P92">
-        <v>-8.897019022222224</v>
+        <v>-12.26385854222222</v>
       </c>
       <c r="Q92">
-        <v>-5.017019022222225</v>
+        <v>-8.383858542222224</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.5734154874619966</v>
+        <v>0.6407385213581462</v>
       </c>
       <c r="T92">
-        <v>10.0086708311695</v>
+        <v>11.28576390677934</v>
       </c>
       <c r="U92">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.1009835888609878</v>
+        <v>0.08504951196747905</v>
       </c>
       <c r="W92">
-        <v>0.1805224953567137</v>
+        <v>0.2157453250780685</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y92">
-        <v>0.504917944304939</v>
+        <v>0.4252475598373953</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8877,22 +8877,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2539947127432755</v>
+        <v>0.2558947127432755</v>
       </c>
       <c r="C93">
-        <v>-77.24331830573323</v>
+        <v>-78.78607189288675</v>
       </c>
       <c r="D93">
-        <v>33.67968169426677</v>
+        <v>33.37992810711326</v>
       </c>
       <c r="E93">
-        <v>76.413</v>
+        <v>77.65600000000001</v>
       </c>
       <c r="F93">
-        <v>113.113</v>
+        <v>114.356</v>
       </c>
       <c r="G93">
         <v>2.19</v>
@@ -8913,37 +8913,37 @@
         <v>11.34222222222222</v>
       </c>
       <c r="M93">
-        <v>26.6720454</v>
+        <v>26.9651448</v>
       </c>
       <c r="N93">
-        <v>-15.32982317777778</v>
+        <v>-15.62292257777778</v>
       </c>
       <c r="O93">
-        <v>-3.065964635555556</v>
+        <v>-3.124584515555556</v>
       </c>
       <c r="P93">
-        <v>-12.26385854222222</v>
+        <v>-12.49833806222223</v>
       </c>
       <c r="Q93">
-        <v>-8.383858542222224</v>
+        <v>-8.618338062222227</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.6407385213581462</v>
+        <v>0.7151058365279146</v>
       </c>
       <c r="T93">
-        <v>11.28576390677934</v>
+        <v>12.69648439512676</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.08504951196747905</v>
+        <v>0.08412506075044122</v>
       </c>
       <c r="W93">
-        <v>0.2157453250780685</v>
+        <v>0.215963310675046</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.4252475598373953</v>
+        <v>0.4206253037522061</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8959,22 +8959,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2558947127432755</v>
+        <v>0.2577947127432754</v>
       </c>
       <c r="C94">
-        <v>-78.78607189288675</v>
+        <v>-80.32353685695001</v>
       </c>
       <c r="D94">
-        <v>33.37992810711326</v>
+        <v>33.08546314304999</v>
       </c>
       <c r="E94">
-        <v>77.65600000000001</v>
+        <v>78.899</v>
       </c>
       <c r="F94">
-        <v>114.356</v>
+        <v>115.599</v>
       </c>
       <c r="G94">
         <v>2.19</v>
@@ -8995,37 +8995,37 @@
         <v>11.34222222222222</v>
       </c>
       <c r="M94">
-        <v>26.9651448</v>
+        <v>27.2582442</v>
       </c>
       <c r="N94">
-        <v>-15.62292257777778</v>
+        <v>-15.91602197777778</v>
       </c>
       <c r="O94">
-        <v>-3.124584515555556</v>
+        <v>-3.183204395555556</v>
       </c>
       <c r="P94">
-        <v>-12.49833806222223</v>
+        <v>-12.73281758222222</v>
       </c>
       <c r="Q94">
-        <v>-8.618338062222227</v>
+        <v>-8.852817582222226</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.7151058365279146</v>
+        <v>0.8107209560319025</v>
       </c>
       <c r="T94">
-        <v>12.69648439512676</v>
+        <v>14.51026788014487</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.08412506075044122</v>
+        <v>0.08322049020473755</v>
       </c>
       <c r="W94">
-        <v>0.215963310675046</v>
+        <v>0.2161766084097229</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.4206253037522061</v>
+        <v>0.4161024510236878</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9041,22 +9041,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2577947127432754</v>
+        <v>0.2596947127432754</v>
       </c>
       <c r="C95">
-        <v>-80.32353685695001</v>
+        <v>-81.85585193665588</v>
       </c>
       <c r="D95">
-        <v>33.08546314304999</v>
+        <v>32.79614806334412</v>
       </c>
       <c r="E95">
-        <v>78.899</v>
+        <v>80.142</v>
       </c>
       <c r="F95">
-        <v>115.599</v>
+        <v>116.842</v>
       </c>
       <c r="G95">
         <v>2.19</v>
@@ -9077,37 +9077,37 @@
         <v>11.34222222222222</v>
       </c>
       <c r="M95">
-        <v>27.2582442</v>
+        <v>27.5513436</v>
       </c>
       <c r="N95">
-        <v>-15.91602197777778</v>
+        <v>-16.20912137777778</v>
       </c>
       <c r="O95">
-        <v>-3.183204395555556</v>
+        <v>-3.241824275555556</v>
       </c>
       <c r="P95">
-        <v>-12.73281758222222</v>
+        <v>-12.96729710222222</v>
       </c>
       <c r="Q95">
-        <v>-8.852817582222226</v>
+        <v>-9.087297102222223</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.8107209560319025</v>
+        <v>0.9382077820372198</v>
       </c>
       <c r="T95">
-        <v>14.51026788014487</v>
+        <v>16.92864586016902</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.08322049020473755</v>
+        <v>0.08233516584085739</v>
       </c>
       <c r="W95">
-        <v>0.2161766084097229</v>
+        <v>0.2163853678947258</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9115,7 +9115,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.4161024510236878</v>
+        <v>0.4116758292042869</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9123,22 +9123,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2596947127432754</v>
+        <v>0.2615947127432755</v>
       </c>
       <c r="C96">
-        <v>-81.85585193665588</v>
+        <v>-83.38315106001377</v>
       </c>
       <c r="D96">
-        <v>32.79614806334412</v>
+        <v>32.51184893998624</v>
       </c>
       <c r="E96">
-        <v>80.142</v>
+        <v>81.38500000000001</v>
       </c>
       <c r="F96">
-        <v>116.842</v>
+        <v>118.085</v>
       </c>
       <c r="G96">
         <v>2.19</v>
@@ -9159,37 +9159,37 @@
         <v>11.34222222222222</v>
       </c>
       <c r="M96">
-        <v>27.5513436</v>
+        <v>27.844443</v>
       </c>
       <c r="N96">
-        <v>-16.20912137777778</v>
+        <v>-16.50222077777778</v>
       </c>
       <c r="O96">
-        <v>-3.241824275555556</v>
+        <v>-3.300444155555556</v>
       </c>
       <c r="P96">
-        <v>-12.96729710222222</v>
+        <v>-13.20177662222222</v>
       </c>
       <c r="Q96">
-        <v>-9.087297102222223</v>
+        <v>-9.321776622222224</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.9382077820372198</v>
+        <v>1.116689338444665</v>
       </c>
       <c r="T96">
-        <v>16.92864586016902</v>
+        <v>20.31437503220284</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.08233516584085739</v>
+        <v>0.08146847988463783</v>
       </c>
       <c r="W96">
-        <v>0.2163853678947258</v>
+        <v>0.2165897324432024</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9197,7 +9197,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.4116758292042869</v>
+        <v>0.4073423994231891</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9205,22 +9205,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2615947127432755</v>
+        <v>0.2634947127432755</v>
       </c>
       <c r="C97">
-        <v>-83.38315106001377</v>
+        <v>-84.90556355103041</v>
       </c>
       <c r="D97">
-        <v>32.51184893998624</v>
+        <v>32.23243644896959</v>
       </c>
       <c r="E97">
-        <v>81.38500000000001</v>
+        <v>82.628</v>
       </c>
       <c r="F97">
-        <v>118.085</v>
+        <v>119.328</v>
       </c>
       <c r="G97">
         <v>2.19</v>
@@ -9241,37 +9241,37 @@
         <v>11.34222222222222</v>
       </c>
       <c r="M97">
-        <v>27.844443</v>
+        <v>28.1375424</v>
       </c>
       <c r="N97">
-        <v>-16.50222077777778</v>
+        <v>-16.79532017777778</v>
       </c>
       <c r="O97">
-        <v>-3.300444155555556</v>
+        <v>-3.359064035555556</v>
       </c>
       <c r="P97">
-        <v>-13.20177662222222</v>
+        <v>-13.43625614222222</v>
       </c>
       <c r="Q97">
-        <v>-9.321776622222224</v>
+        <v>-9.556256142222225</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.116689338444665</v>
+        <v>1.384411673055831</v>
       </c>
       <c r="T97">
-        <v>20.31437503220284</v>
+        <v>25.39296879025355</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.08146847988463783</v>
+        <v>0.08061984988583952</v>
       </c>
       <c r="W97">
-        <v>0.2165897324432024</v>
+        <v>0.2167898393969191</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9279,7 +9279,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.4073423994231891</v>
+        <v>0.4030992494291975</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9287,22 +9287,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2634947127432755</v>
+        <v>0.2653947127432755</v>
       </c>
       <c r="C98">
-        <v>-84.90556355103041</v>
+        <v>-86.42321432586238</v>
       </c>
       <c r="D98">
-        <v>32.23243644896959</v>
+        <v>31.95778567413761</v>
       </c>
       <c r="E98">
-        <v>82.62799999999999</v>
+        <v>83.871</v>
       </c>
       <c r="F98">
-        <v>119.328</v>
+        <v>120.571</v>
       </c>
       <c r="G98">
         <v>2.19</v>
@@ -9323,37 +9323,37 @@
         <v>11.34222222222222</v>
       </c>
       <c r="M98">
-        <v>28.1375424</v>
+        <v>28.4306418</v>
       </c>
       <c r="N98">
-        <v>-16.79532017777777</v>
+        <v>-17.08841957777778</v>
       </c>
       <c r="O98">
-        <v>-3.359064035555555</v>
+        <v>-3.417683915555556</v>
       </c>
       <c r="P98">
-        <v>-13.43625614222222</v>
+        <v>-13.67073566222222</v>
       </c>
       <c r="Q98">
-        <v>-9.556256142222221</v>
+        <v>-9.790735662222223</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.384411673055828</v>
+        <v>1.830615564074437</v>
       </c>
       <c r="T98">
-        <v>25.39296879025349</v>
+        <v>33.85729172033799</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.08061984988583953</v>
+        <v>0.07978871741278963</v>
       </c>
       <c r="W98">
-        <v>0.2167898393969191</v>
+        <v>0.2169858204340642</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.4030992494291976</v>
+        <v>0.3989435870639481</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9369,22 +9369,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2653947127432755</v>
+        <v>0.2672947127432754</v>
       </c>
       <c r="C99">
-        <v>-86.42321432586238</v>
+        <v>-87.93622407902443</v>
       </c>
       <c r="D99">
-        <v>31.95778567413761</v>
+        <v>31.68777592097556</v>
       </c>
       <c r="E99">
-        <v>83.871</v>
+        <v>85.11399999999999</v>
       </c>
       <c r="F99">
-        <v>120.571</v>
+        <v>121.814</v>
       </c>
       <c r="G99">
         <v>2.19</v>
@@ -9405,37 +9405,37 @@
         <v>11.34222222222222</v>
       </c>
       <c r="M99">
-        <v>28.4306418</v>
+        <v>28.7237412</v>
       </c>
       <c r="N99">
-        <v>-17.08841957777778</v>
+        <v>-17.38151897777778</v>
       </c>
       <c r="O99">
-        <v>-3.417683915555556</v>
+        <v>-3.476303795555555</v>
       </c>
       <c r="P99">
-        <v>-13.67073566222222</v>
+        <v>-13.90521518222222</v>
       </c>
       <c r="Q99">
-        <v>-9.790735662222223</v>
+        <v>-10.02521518222222</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.830615564074437</v>
+        <v>2.723023346111655</v>
       </c>
       <c r="T99">
-        <v>33.85729172033799</v>
+        <v>50.78593758050697</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.07978871741278963</v>
+        <v>0.07897454682694484</v>
       </c>
       <c r="W99">
-        <v>0.2169858204340642</v>
+        <v>0.2171778018582064</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9443,7 +9443,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.3989435870639481</v>
+        <v>0.3948727341347241</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9451,22 +9451,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2672947127432754</v>
+        <v>0.2691947127432754</v>
       </c>
       <c r="C100">
-        <v>-87.93622407902443</v>
+        <v>-89.4447094602376</v>
       </c>
       <c r="D100">
-        <v>31.68777592097556</v>
+        <v>31.4222905397624</v>
       </c>
       <c r="E100">
-        <v>85.11399999999999</v>
+        <v>86.357</v>
       </c>
       <c r="F100">
-        <v>121.814</v>
+        <v>123.057</v>
       </c>
       <c r="G100">
         <v>2.19</v>
@@ -9487,37 +9487,37 @@
         <v>11.34222222222222</v>
       </c>
       <c r="M100">
-        <v>28.7237412</v>
+        <v>29.0168406</v>
       </c>
       <c r="N100">
-        <v>-17.38151897777778</v>
+        <v>-17.67461837777778</v>
       </c>
       <c r="O100">
-        <v>-3.476303795555555</v>
+        <v>-3.534923675555556</v>
       </c>
       <c r="P100">
-        <v>-13.90521518222222</v>
+        <v>-14.13969470222222</v>
       </c>
       <c r="Q100">
-        <v>-10.02521518222222</v>
+        <v>-10.25969470222222</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>2.723023346111655</v>
+        <v>5.400246692223311</v>
       </c>
       <c r="T100">
-        <v>50.78593758050697</v>
+        <v>101.571875161014</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.07897454682694484</v>
+        <v>0.07817682413172317</v>
       </c>
       <c r="W100">
-        <v>0.2171778018582064</v>
+        <v>0.2173659048697397</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9525,91 +9525,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.3948727341347241</v>
+        <v>0.3908841206586158</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2691947127432754</v>
-      </c>
-      <c r="C101">
-        <v>-89.4447094602376</v>
-      </c>
-      <c r="D101">
-        <v>31.4222905397624</v>
-      </c>
-      <c r="E101">
-        <v>86.357</v>
-      </c>
-      <c r="F101">
-        <v>123.057</v>
-      </c>
-      <c r="G101">
-        <v>2.19</v>
-      </c>
-      <c r="H101">
-        <v>87.59999999999999</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>15.22222222222222</v>
-      </c>
-      <c r="K101">
-        <v>3.879999999999999</v>
-      </c>
-      <c r="L101">
-        <v>11.34222222222222</v>
-      </c>
-      <c r="M101">
-        <v>29.0168406</v>
-      </c>
-      <c r="N101">
-        <v>-17.67461837777778</v>
-      </c>
-      <c r="O101">
-        <v>-3.534923675555556</v>
-      </c>
-      <c r="P101">
-        <v>-14.13969470222222</v>
-      </c>
-      <c r="Q101">
-        <v>-10.25969470222222</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>5.400246692223311</v>
-      </c>
-      <c r="T101">
-        <v>101.571875161014</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.07817682413172317</v>
-      </c>
-      <c r="W101">
-        <v>0.2173659048697397</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.3908841206586158</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
